--- a/Pruebas_Homologacion_PS_3G_4G.xlsx
+++ b/Pruebas_Homologacion_PS_3G_4G.xlsx
@@ -2250,11 +2250,15 @@
       <c r="F21" s="41" t="n">
         <v>0.6069444444444444</v>
       </c>
-      <c r="G21" s="41" t="n">
-        <v>0.7625</v>
-      </c>
-      <c r="H21" s="41" t="n">
-        <v>0.7652777777777777</v>
+      <c r="G21" s="41" t="inlineStr">
+        <is>
+          <t>11:50 AM</t>
+        </is>
+      </c>
+      <c r="H21" s="41" t="inlineStr">
+        <is>
+          <t>11:51 AM</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
@@ -2531,11 +2535,13 @@
       </c>
       <c r="C36" s="51" t="inlineStr">
         <is>
-          <t>11:37 AM</t>
-        </is>
-      </c>
-      <c r="D36" s="51" t="n">
-        <v>0.5645833333333333</v>
+          <t>11:50 AM</t>
+        </is>
+      </c>
+      <c r="D36" s="51" t="inlineStr">
+        <is>
+          <t>11:51 AM</t>
+        </is>
       </c>
       <c r="E36" s="31" t="n"/>
       <c r="F36" s="1" t="n">

--- a/Pruebas_Homologacion_PS_3G_4G.xlsx
+++ b/Pruebas_Homologacion_PS_3G_4G.xlsx
@@ -2136,7 +2136,7 @@
     <row r="15" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B15" s="132" t="inlineStr">
         <is>
-          <t>Modelo: V2543</t>
+          <t>Modelo: V2537</t>
         </is>
       </c>
       <c r="C15" s="133" t="n"/>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B16" s="132" t="inlineStr">
         <is>
-          <t>Fecha de pruebas: 02/03/2026</t>
+          <t>Fecha de pruebas: 25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="133" t="n"/>
@@ -4979,7 +4979,7 @@
     <row r="15" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B15" s="132" t="inlineStr">
         <is>
-          <t>Modelo: V2543</t>
+          <t>Modelo: V2537</t>
         </is>
       </c>
       <c r="C15" s="133" t="n"/>
@@ -4999,7 +4999,7 @@
     <row r="16" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B16" s="132" t="inlineStr">
         <is>
-          <t>Fecha de pruebas: 02/03/2026</t>
+          <t>Fecha de pruebas: 25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="133" t="n"/>
@@ -5105,23 +5105,31 @@
           <t>MMS</t>
         </is>
       </c>
-      <c r="C21" s="42" t="n">
-        <v>0.4965277777777778</v>
-      </c>
-      <c r="D21" s="41" t="n">
-        <v>0.5097222222222222</v>
-      </c>
-      <c r="E21" s="42" t="n">
-        <v>0.6840277777777778</v>
-      </c>
-      <c r="F21" s="41" t="n">
-        <v>0.6972222222222222</v>
-      </c>
-      <c r="G21" s="41" t="n">
-        <v>0.6881944444444444</v>
-      </c>
-      <c r="H21" s="41" t="n">
-        <v>0.6909722222222222</v>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>11:41 AM</t>
+        </is>
+      </c>
+      <c r="D21" s="41" t="n"/>
+      <c r="E21" s="42" t="inlineStr">
+        <is>
+          <t>10:59 AM</t>
+        </is>
+      </c>
+      <c r="F21" s="41" t="inlineStr">
+        <is>
+          <t>11:03 AM</t>
+        </is>
+      </c>
+      <c r="G21" s="41" t="inlineStr">
+        <is>
+          <t>01:17 PM</t>
+        </is>
+      </c>
+      <c r="H21" s="41" t="inlineStr">
+        <is>
+          <t>01:21 PM</t>
+        </is>
       </c>
       <c r="O21" s="59" t="n"/>
       <c r="P21" s="60" t="n"/>
@@ -5147,11 +5155,15 @@
       <c r="F22" s="47" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="G22" s="47" t="n">
-        <v>0.6965277777777777</v>
-      </c>
-      <c r="H22" s="47" t="n">
-        <v>0.6986111111111111</v>
+      <c r="G22" s="47" t="inlineStr">
+        <is>
+          <t>01:28 PM</t>
+        </is>
+      </c>
+      <c r="H22" s="47" t="inlineStr">
+        <is>
+          <t>01:32 PM</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -5173,11 +5185,15 @@
       <c r="F23" s="40" t="n">
         <v>0.7201388888888889</v>
       </c>
-      <c r="G23" s="40" t="n">
-        <v>0.7041666666666667</v>
-      </c>
-      <c r="H23" s="40" t="n">
-        <v>0.7069444444444445</v>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>01:39 PM</t>
+        </is>
+      </c>
+      <c r="H23" s="40" t="inlineStr">
+        <is>
+          <t>01:43 PM</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -5199,11 +5215,15 @@
       <c r="F24" s="65" t="n">
         <v>0.7381944444444445</v>
       </c>
-      <c r="G24" s="47" t="n">
-        <v>0.8173611111111111</v>
-      </c>
-      <c r="H24" s="47" t="n">
-        <v>0.8201388888888889</v>
+      <c r="G24" s="47" t="inlineStr">
+        <is>
+          <t>01:46 PM</t>
+        </is>
+      </c>
+      <c r="H24" s="47" t="inlineStr">
+        <is>
+          <t>01:47 PM</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" thickBot="1">
@@ -5224,11 +5244,15 @@
       <c r="F25" s="66" t="n">
         <v>0.4423611111111111</v>
       </c>
-      <c r="G25" s="44" t="n">
-        <v>0.7125</v>
-      </c>
-      <c r="H25" s="40" t="n">
-        <v>0.7152777777777778</v>
+      <c r="G25" s="44" t="inlineStr">
+        <is>
+          <t>01:55 PM</t>
+        </is>
+      </c>
+      <c r="H25" s="40" t="inlineStr">
+        <is>
+          <t>01:59 PM</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
@@ -5250,11 +5274,15 @@
       <c r="F26" s="50" t="n">
         <v>0.4479166666666667</v>
       </c>
-      <c r="G26" s="50" t="n">
-        <v>0.4930555555555556</v>
-      </c>
-      <c r="H26" s="50" t="n">
-        <v>0.4958333333333333</v>
+      <c r="G26" s="50" t="inlineStr">
+        <is>
+          <t>02:07 PM</t>
+        </is>
+      </c>
+      <c r="H26" s="50" t="inlineStr">
+        <is>
+          <t>02:11 PM</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -5411,11 +5439,15 @@
       <c r="B36" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="51" t="n">
-        <v>0.4965277777777778</v>
-      </c>
-      <c r="D36" s="51" t="n">
-        <v>0.4972222222222222</v>
+      <c r="C36" s="51" t="inlineStr">
+        <is>
+          <t>11:41 AM</t>
+        </is>
+      </c>
+      <c r="D36" s="51" t="inlineStr">
+        <is>
+          <t>11:42 AM</t>
+        </is>
       </c>
       <c r="E36" s="31" t="n"/>
       <c r="F36" s="1" t="n">
@@ -5428,11 +5460,15 @@
       <c r="J36" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="51" t="n">
-        <v>0.6840277777777778</v>
-      </c>
-      <c r="L36" s="51" t="n">
-        <v>0.6847222222222222</v>
+      <c r="K36" s="51" t="inlineStr">
+        <is>
+          <t>10:59 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="51" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
       </c>
       <c r="M36" s="31" t="n"/>
       <c r="N36" s="1" t="n">
@@ -5445,8 +5481,10 @@
       <c r="S36" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T36" s="51" t="n">
-        <v>0.6881944444444444</v>
+      <c r="T36" s="51" t="inlineStr">
+        <is>
+          <t>01:17 PM</t>
+        </is>
       </c>
       <c r="V36" s="148" t="n"/>
       <c r="X36" s="149" t="n"/>
@@ -5455,11 +5493,15 @@
       <c r="B37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="52" t="n">
-        <v>0.4979166666666667</v>
-      </c>
-      <c r="D37" s="52" t="n">
-        <v>0.4986111111111111</v>
+      <c r="C37" s="52" t="inlineStr">
+        <is>
+          <t>11:43 AM</t>
+        </is>
+      </c>
+      <c r="D37" s="52" t="inlineStr">
+        <is>
+          <t>11:44 AM</t>
+        </is>
       </c>
       <c r="F37" s="15" t="n">
         <v>2</v>
@@ -5470,11 +5512,15 @@
       <c r="J37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="52" t="n">
-        <v>0.6854166666666667</v>
-      </c>
-      <c r="L37" s="52" t="n">
-        <v>0.6861111111111111</v>
+      <c r="K37" s="52" t="inlineStr">
+        <is>
+          <t>11:01 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="52" t="inlineStr">
+        <is>
+          <t>11:02 AM</t>
+        </is>
       </c>
       <c r="N37" s="15" t="n">
         <v>2</v>
@@ -5485,8 +5531,10 @@
       <c r="S37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T37" s="52" t="n">
-        <v>0.6888888888888889</v>
+      <c r="T37" s="52" t="inlineStr">
+        <is>
+          <t>01:18 PM</t>
+        </is>
       </c>
       <c r="V37" s="148" t="n"/>
       <c r="X37" s="149" t="n"/>
@@ -5495,11 +5543,15 @@
       <c r="B38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="51" t="n">
-        <v>0.4993055555555556</v>
-      </c>
-      <c r="D38" s="51" t="n">
-        <v>0.5</v>
+      <c r="C38" s="51" t="inlineStr">
+        <is>
+          <t>11:45 AM</t>
+        </is>
+      </c>
+      <c r="D38" s="51" t="inlineStr">
+        <is>
+          <t>11:46 AM</t>
+        </is>
       </c>
       <c r="F38" s="1" t="n">
         <v>3</v>
@@ -5510,8 +5562,10 @@
       <c r="J38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K38" s="51" t="n">
-        <v>0.6868055555555556</v>
+      <c r="K38" s="51" t="inlineStr">
+        <is>
+          <t>11:03 AM</t>
+        </is>
       </c>
       <c r="L38" s="51" t="n">
         <v>0.6875</v>
@@ -5525,8 +5579,10 @@
       <c r="S38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T38" s="51" t="n">
-        <v>0.6895833333333333</v>
+      <c r="T38" s="51" t="inlineStr">
+        <is>
+          <t>01:19 PM</t>
+        </is>
       </c>
       <c r="V38" s="148" t="n"/>
       <c r="X38" s="149" t="n"/>
@@ -5535,11 +5591,15 @@
       <c r="B39" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="52" t="n">
-        <v>0.5006944444444444</v>
-      </c>
-      <c r="D39" s="52" t="n">
-        <v>0.5013888888888889</v>
+      <c r="C39" s="52" t="inlineStr">
+        <is>
+          <t>11:47 AM</t>
+        </is>
+      </c>
+      <c r="D39" s="52" t="inlineStr">
+        <is>
+          <t>11:48 AM</t>
+        </is>
       </c>
       <c r="F39" s="15" t="n">
         <v>4</v>
@@ -5565,8 +5625,10 @@
       <c r="S39" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T39" s="52" t="n">
-        <v>0.6902777777777778</v>
+      <c r="T39" s="52" t="inlineStr">
+        <is>
+          <t>01:20 PM</t>
+        </is>
       </c>
       <c r="V39" s="148" t="n"/>
       <c r="X39" s="149" t="n"/>
@@ -5575,11 +5637,15 @@
       <c r="B40" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C40" s="51" t="n">
-        <v>0.5020833333333333</v>
-      </c>
-      <c r="D40" s="51" t="n">
-        <v>0.5027777777777778</v>
+      <c r="C40" s="51" t="inlineStr">
+        <is>
+          <t>11:49 AM</t>
+        </is>
+      </c>
+      <c r="D40" s="51" t="inlineStr">
+        <is>
+          <t>11:50 AM</t>
+        </is>
       </c>
       <c r="F40" s="1" t="n">
         <v>5</v>
@@ -5605,8 +5671,10 @@
       <c r="S40" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T40" s="51" t="n">
-        <v>0.6909722222222222</v>
+      <c r="T40" s="51" t="inlineStr">
+        <is>
+          <t>01:21 PM</t>
+        </is>
       </c>
       <c r="U40" s="31" t="n"/>
       <c r="V40" s="148" t="n"/>
@@ -5616,11 +5684,15 @@
       <c r="B41" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="52" t="n">
-        <v>0.5034722222222222</v>
-      </c>
-      <c r="D41" s="52" t="n">
-        <v>0.5041666666666667</v>
+      <c r="C41" s="52" t="inlineStr">
+        <is>
+          <t>11:51 AM</t>
+        </is>
+      </c>
+      <c r="D41" s="52" t="inlineStr">
+        <is>
+          <t>11:52 AM</t>
+        </is>
       </c>
       <c r="F41" s="15" t="n">
         <v>6</v>
@@ -6171,8 +6243,10 @@
       <c r="S56" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T56" s="51" t="n">
-        <v>0.6965277777777777</v>
+      <c r="T56" s="51" t="inlineStr">
+        <is>
+          <t>01:28 PM</t>
+        </is>
       </c>
       <c r="V56" s="148" t="n"/>
       <c r="X56" s="149" t="n"/>
@@ -6211,8 +6285,10 @@
       <c r="S57" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T57" s="52" t="n">
-        <v>0.6972222222222222</v>
+      <c r="T57" s="52" t="inlineStr">
+        <is>
+          <t>01:29 PM</t>
+        </is>
       </c>
       <c r="V57" s="148" t="n"/>
       <c r="X57" s="149" t="n"/>
@@ -6255,8 +6331,10 @@
       <c r="S58" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T58" s="51" t="n">
-        <v>0.6979166666666666</v>
+      <c r="T58" s="51" t="inlineStr">
+        <is>
+          <t>01:30 PM</t>
+        </is>
       </c>
       <c r="V58" s="148" t="n"/>
       <c r="X58" s="149" t="n"/>
@@ -6265,8 +6343,10 @@
       <c r="S59" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T59" s="52" t="n">
-        <v>0.6979166666666666</v>
+      <c r="T59" s="52" t="inlineStr">
+        <is>
+          <t>01:31 PM</t>
+        </is>
       </c>
       <c r="V59" s="148" t="n"/>
       <c r="X59" s="149" t="n"/>
@@ -6304,8 +6384,10 @@
       <c r="S60" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T60" s="51" t="n">
-        <v>0.6986111111111111</v>
+      <c r="T60" s="51" t="inlineStr">
+        <is>
+          <t>01:32 PM</t>
+        </is>
       </c>
       <c r="V60" s="148" t="n"/>
       <c r="X60" s="149" t="n"/>
@@ -6824,8 +6906,10 @@
       <c r="S76" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T76" s="51" t="n">
-        <v>0.7041666666666667</v>
+      <c r="T76" s="51" t="inlineStr">
+        <is>
+          <t>01:39 PM</t>
+        </is>
       </c>
       <c r="V76" s="148" t="n"/>
       <c r="X76" s="149" t="n"/>
@@ -6834,8 +6918,10 @@
       <c r="S77" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T77" s="53" t="n">
-        <v>0.7048611111111112</v>
+      <c r="T77" s="53" t="inlineStr">
+        <is>
+          <t>01:40 PM</t>
+        </is>
       </c>
       <c r="V77" s="148" t="n"/>
       <c r="X77" s="149" t="n"/>
@@ -6844,8 +6930,10 @@
       <c r="S78" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T78" s="51" t="n">
-        <v>0.7055555555555556</v>
+      <c r="T78" s="51" t="inlineStr">
+        <is>
+          <t>01:41 PM</t>
+        </is>
       </c>
       <c r="V78" s="148" t="n"/>
       <c r="X78" s="149" t="n"/>
@@ -6854,8 +6942,10 @@
       <c r="S79" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T79" s="53" t="n">
-        <v>0.70625</v>
+      <c r="T79" s="53" t="inlineStr">
+        <is>
+          <t>01:42 PM</t>
+        </is>
       </c>
       <c r="V79" s="148" t="n"/>
       <c r="X79" s="149" t="n"/>
@@ -6864,8 +6954,10 @@
       <c r="S80" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T80" s="51" t="n">
-        <v>0.7069444444444445</v>
+      <c r="T80" s="51" t="inlineStr">
+        <is>
+          <t>01:43 PM</t>
+        </is>
       </c>
       <c r="U80" s="32" t="n"/>
       <c r="V80" s="148" t="n"/>
@@ -6952,8 +7044,10 @@
       <c r="S96" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T96" s="51" t="n">
-        <v>0.8173611111111111</v>
+      <c r="T96" s="51" t="inlineStr">
+        <is>
+          <t>01:46 PM</t>
+        </is>
       </c>
       <c r="V96" s="148" t="n"/>
       <c r="X96" s="149" t="n"/>
@@ -6962,8 +7056,10 @@
       <c r="S97" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T97" s="53" t="n">
-        <v>0.8180555555555555</v>
+      <c r="T97" s="53" t="inlineStr">
+        <is>
+          <t>01:47 PM</t>
+        </is>
       </c>
       <c r="V97" s="148" t="n"/>
       <c r="X97" s="149" t="n"/>
@@ -7079,8 +7175,10 @@
       <c r="S116" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T116" s="51" t="n">
-        <v>0.7125</v>
+      <c r="T116" s="51" t="inlineStr">
+        <is>
+          <t>01:55 PM</t>
+        </is>
       </c>
       <c r="V116" s="148" t="n"/>
       <c r="X116" s="149" t="n"/>
@@ -7089,8 +7187,10 @@
       <c r="S117" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T117" s="53" t="n">
-        <v>0.7131944444444445</v>
+      <c r="T117" s="53" t="inlineStr">
+        <is>
+          <t>01:56 PM</t>
+        </is>
       </c>
       <c r="V117" s="148" t="n"/>
       <c r="X117" s="149" t="n"/>
@@ -7099,8 +7199,10 @@
       <c r="S118" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T118" s="51" t="n">
-        <v>0.7138888888888889</v>
+      <c r="T118" s="51" t="inlineStr">
+        <is>
+          <t>01:57 PM</t>
+        </is>
       </c>
       <c r="V118" s="148" t="n"/>
       <c r="X118" s="149" t="n"/>
@@ -7109,8 +7211,10 @@
       <c r="S119" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T119" s="53" t="n">
-        <v>0.7145833333333333</v>
+      <c r="T119" s="53" t="inlineStr">
+        <is>
+          <t>01:58 PM</t>
+        </is>
       </c>
       <c r="V119" s="148" t="n"/>
       <c r="X119" s="149" t="n"/>
@@ -7119,8 +7223,10 @@
       <c r="S120" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T120" s="51" t="n">
-        <v>0.7152777777777778</v>
+      <c r="T120" s="51" t="inlineStr">
+        <is>
+          <t>01:59 PM</t>
+        </is>
       </c>
       <c r="V120" s="148" t="n"/>
       <c r="X120" s="149" t="n"/>
@@ -7206,8 +7312,10 @@
       <c r="S136" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T136" s="51" t="n">
-        <v>0.4930555555555556</v>
+      <c r="T136" s="51" t="inlineStr">
+        <is>
+          <t>02:07 PM</t>
+        </is>
       </c>
       <c r="V136" s="148" t="n"/>
       <c r="X136" s="149" t="n"/>
@@ -7216,8 +7324,10 @@
       <c r="S137" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T137" s="53" t="n">
-        <v>0.49375</v>
+      <c r="T137" s="53" t="inlineStr">
+        <is>
+          <t>02:08 PM</t>
+        </is>
       </c>
       <c r="V137" s="148" t="n"/>
       <c r="X137" s="149" t="n"/>
@@ -7226,8 +7336,10 @@
       <c r="S138" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T138" s="51" t="n">
-        <v>0.4944444444444445</v>
+      <c r="T138" s="51" t="inlineStr">
+        <is>
+          <t>02:09 PM</t>
+        </is>
       </c>
       <c r="V138" s="148" t="n"/>
       <c r="X138" s="149" t="n"/>
@@ -7236,8 +7348,10 @@
       <c r="S139" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T139" s="53" t="n">
-        <v>0.4951388888888889</v>
+      <c r="T139" s="53" t="inlineStr">
+        <is>
+          <t>02:10 PM</t>
+        </is>
       </c>
       <c r="V139" s="148" t="n"/>
       <c r="X139" s="149" t="n"/>
@@ -7246,8 +7360,10 @@
       <c r="S140" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T140" s="51" t="n">
-        <v>0.4958333333333333</v>
+      <c r="T140" s="51" t="inlineStr">
+        <is>
+          <t>02:11 PM</t>
+        </is>
       </c>
       <c r="V140" s="148" t="n"/>
       <c r="X140" s="149" t="n"/>

--- a/Pruebas_Homologacion_PS_3G_4G.xlsx
+++ b/Pruebas_Homologacion_PS_3G_4G.xlsx
@@ -2127,7 +2127,7 @@
       <c r="D14" s="134" t="n"/>
       <c r="F14" s="74" t="inlineStr">
         <is>
-          <t>Línea Pospago: 5530760949</t>
+          <t>Línea Pospago: 5523427847</t>
         </is>
       </c>
       <c r="G14" s="133" t="n"/>
@@ -2136,7 +2136,7 @@
     <row r="15" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B15" s="132" t="inlineStr">
         <is>
-          <t>Modelo: V2543</t>
+          <t>Modelo: V2515</t>
         </is>
       </c>
       <c r="C15" s="133" t="n"/>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B16" s="132" t="inlineStr">
         <is>
-          <t>Fecha de pruebas: 02/03/2026</t>
+          <t>Fecha de pruebas: 25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="133" t="n"/>
@@ -2238,11 +2238,15 @@
           <t>MMS</t>
         </is>
       </c>
-      <c r="C21" s="42" t="n">
-        <v>0.5638888888888889</v>
-      </c>
-      <c r="D21" s="41" t="n">
-        <v>0.5770833333333333</v>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>01:18 PM</t>
+        </is>
+      </c>
+      <c r="D21" s="41" t="inlineStr">
+        <is>
+          <t>01:19 PM</t>
+        </is>
       </c>
       <c r="E21" s="42" t="n">
         <v>0.59375</v>
@@ -2535,12 +2539,12 @@
       </c>
       <c r="C36" s="51" t="inlineStr">
         <is>
-          <t>11:50 AM</t>
+          <t>01:18 PM</t>
         </is>
       </c>
       <c r="D36" s="51" t="inlineStr">
         <is>
-          <t>11:51 AM</t>
+          <t>01:19 PM</t>
         </is>
       </c>
       <c r="E36" s="31" t="n"/>

--- a/Pruebas_Homologacion_PS_3G_4G.xlsx
+++ b/Pruebas_Homologacion_PS_3G_4G.xlsx
@@ -2127,7 +2127,7 @@
       <c r="D14" s="134" t="n"/>
       <c r="F14" s="74" t="inlineStr">
         <is>
-          <t>Línea Pospago: 5530760949</t>
+          <t>Línea Pospago: 5523427847</t>
         </is>
       </c>
       <c r="G14" s="133" t="n"/>
@@ -2136,7 +2136,7 @@
     <row r="15" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B15" s="132" t="inlineStr">
         <is>
-          <t>Modelo: V2537</t>
+          <t>Modelo: V2515</t>
         </is>
       </c>
       <c r="C15" s="133" t="n"/>
@@ -2238,11 +2238,15 @@
           <t>MMS</t>
         </is>
       </c>
-      <c r="C21" s="42" t="n">
-        <v>0.5638888888888889</v>
-      </c>
-      <c r="D21" s="41" t="n">
-        <v>0.5770833333333333</v>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>01:18 PM</t>
+        </is>
+      </c>
+      <c r="D21" s="41" t="inlineStr">
+        <is>
+          <t>01:19 PM</t>
+        </is>
       </c>
       <c r="E21" s="42" t="n">
         <v>0.59375</v>
@@ -2535,12 +2539,12 @@
       </c>
       <c r="C36" s="51" t="inlineStr">
         <is>
-          <t>11:50 AM</t>
+          <t>01:18 PM</t>
         </is>
       </c>
       <c r="D36" s="51" t="inlineStr">
         <is>
-          <t>11:51 AM</t>
+          <t>01:19 PM</t>
         </is>
       </c>
       <c r="E36" s="31" t="n"/>
@@ -4979,7 +4983,7 @@
     <row r="15" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B15" s="132" t="inlineStr">
         <is>
-          <t>Modelo: V2537</t>
+          <t>Modelo: V2543</t>
         </is>
       </c>
       <c r="C15" s="133" t="n"/>
@@ -4999,7 +5003,7 @@
     <row r="16" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B16" s="132" t="inlineStr">
         <is>
-          <t>Fecha de pruebas: 25/05/2026</t>
+          <t>Fecha de pruebas: 02/03/2026</t>
         </is>
       </c>
       <c r="C16" s="133" t="n"/>
@@ -5105,31 +5109,23 @@
           <t>MMS</t>
         </is>
       </c>
-      <c r="C21" s="42" t="inlineStr">
-        <is>
-          <t>11:41 AM</t>
-        </is>
-      </c>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="42" t="inlineStr">
-        <is>
-          <t>10:59 AM</t>
-        </is>
-      </c>
-      <c r="F21" s="41" t="inlineStr">
-        <is>
-          <t>11:03 AM</t>
-        </is>
-      </c>
-      <c r="G21" s="41" t="inlineStr">
-        <is>
-          <t>01:17 PM</t>
-        </is>
-      </c>
-      <c r="H21" s="41" t="inlineStr">
-        <is>
-          <t>01:21 PM</t>
-        </is>
+      <c r="C21" s="42" t="n">
+        <v>0.4965277777777778</v>
+      </c>
+      <c r="D21" s="41" t="n">
+        <v>0.5097222222222222</v>
+      </c>
+      <c r="E21" s="42" t="n">
+        <v>0.6840277777777778</v>
+      </c>
+      <c r="F21" s="41" t="n">
+        <v>0.6972222222222222</v>
+      </c>
+      <c r="G21" s="41" t="n">
+        <v>0.6881944444444444</v>
+      </c>
+      <c r="H21" s="41" t="n">
+        <v>0.6909722222222222</v>
       </c>
       <c r="O21" s="59" t="n"/>
       <c r="P21" s="60" t="n"/>
@@ -5155,15 +5151,11 @@
       <c r="F22" s="47" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="G22" s="47" t="inlineStr">
-        <is>
-          <t>01:28 PM</t>
-        </is>
-      </c>
-      <c r="H22" s="47" t="inlineStr">
-        <is>
-          <t>01:32 PM</t>
-        </is>
+      <c r="G22" s="47" t="n">
+        <v>0.6965277777777777</v>
+      </c>
+      <c r="H22" s="47" t="n">
+        <v>0.6986111111111111</v>
       </c>
     </row>
     <row r="23">
@@ -5185,15 +5177,11 @@
       <c r="F23" s="40" t="n">
         <v>0.7201388888888889</v>
       </c>
-      <c r="G23" s="40" t="inlineStr">
-        <is>
-          <t>01:39 PM</t>
-        </is>
-      </c>
-      <c r="H23" s="40" t="inlineStr">
-        <is>
-          <t>01:43 PM</t>
-        </is>
+      <c r="G23" s="40" t="n">
+        <v>0.7041666666666667</v>
+      </c>
+      <c r="H23" s="40" t="n">
+        <v>0.7069444444444445</v>
       </c>
     </row>
     <row r="24">
@@ -5215,15 +5203,11 @@
       <c r="F24" s="65" t="n">
         <v>0.7381944444444445</v>
       </c>
-      <c r="G24" s="47" t="inlineStr">
-        <is>
-          <t>01:46 PM</t>
-        </is>
-      </c>
-      <c r="H24" s="47" t="inlineStr">
-        <is>
-          <t>01:47 PM</t>
-        </is>
+      <c r="G24" s="47" t="n">
+        <v>0.8173611111111111</v>
+      </c>
+      <c r="H24" s="47" t="n">
+        <v>0.8201388888888889</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" thickBot="1">
@@ -5244,15 +5228,11 @@
       <c r="F25" s="66" t="n">
         <v>0.4423611111111111</v>
       </c>
-      <c r="G25" s="44" t="inlineStr">
-        <is>
-          <t>01:55 PM</t>
-        </is>
-      </c>
-      <c r="H25" s="40" t="inlineStr">
-        <is>
-          <t>01:59 PM</t>
-        </is>
+      <c r="G25" s="44" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="H25" s="40" t="n">
+        <v>0.7152777777777778</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
@@ -5274,15 +5254,11 @@
       <c r="F26" s="50" t="n">
         <v>0.4479166666666667</v>
       </c>
-      <c r="G26" s="50" t="inlineStr">
-        <is>
-          <t>02:07 PM</t>
-        </is>
-      </c>
-      <c r="H26" s="50" t="inlineStr">
-        <is>
-          <t>02:11 PM</t>
-        </is>
+      <c r="G26" s="50" t="n">
+        <v>0.4930555555555556</v>
+      </c>
+      <c r="H26" s="50" t="n">
+        <v>0.4958333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -5439,15 +5415,11 @@
       <c r="B36" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="51" t="inlineStr">
-        <is>
-          <t>11:41 AM</t>
-        </is>
-      </c>
-      <c r="D36" s="51" t="inlineStr">
-        <is>
-          <t>11:42 AM</t>
-        </is>
+      <c r="C36" s="51" t="n">
+        <v>0.4965277777777778</v>
+      </c>
+      <c r="D36" s="51" t="n">
+        <v>0.4972222222222222</v>
       </c>
       <c r="E36" s="31" t="n"/>
       <c r="F36" s="1" t="n">
@@ -5460,15 +5432,11 @@
       <c r="J36" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="51" t="inlineStr">
-        <is>
-          <t>10:59 AM</t>
-        </is>
-      </c>
-      <c r="L36" s="51" t="inlineStr">
-        <is>
-          <t>11:00 AM</t>
-        </is>
+      <c r="K36" s="51" t="n">
+        <v>0.6840277777777778</v>
+      </c>
+      <c r="L36" s="51" t="n">
+        <v>0.6847222222222222</v>
       </c>
       <c r="M36" s="31" t="n"/>
       <c r="N36" s="1" t="n">
@@ -5481,10 +5449,8 @@
       <c r="S36" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T36" s="51" t="inlineStr">
-        <is>
-          <t>01:17 PM</t>
-        </is>
+      <c r="T36" s="51" t="n">
+        <v>0.6881944444444444</v>
       </c>
       <c r="V36" s="148" t="n"/>
       <c r="X36" s="149" t="n"/>
@@ -5493,15 +5459,11 @@
       <c r="B37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="52" t="inlineStr">
-        <is>
-          <t>11:43 AM</t>
-        </is>
-      </c>
-      <c r="D37" s="52" t="inlineStr">
-        <is>
-          <t>11:44 AM</t>
-        </is>
+      <c r="C37" s="52" t="n">
+        <v>0.4979166666666667</v>
+      </c>
+      <c r="D37" s="52" t="n">
+        <v>0.4986111111111111</v>
       </c>
       <c r="F37" s="15" t="n">
         <v>2</v>
@@ -5512,15 +5474,11 @@
       <c r="J37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="52" t="inlineStr">
-        <is>
-          <t>11:01 AM</t>
-        </is>
-      </c>
-      <c r="L37" s="52" t="inlineStr">
-        <is>
-          <t>11:02 AM</t>
-        </is>
+      <c r="K37" s="52" t="n">
+        <v>0.6854166666666667</v>
+      </c>
+      <c r="L37" s="52" t="n">
+        <v>0.6861111111111111</v>
       </c>
       <c r="N37" s="15" t="n">
         <v>2</v>
@@ -5531,10 +5489,8 @@
       <c r="S37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T37" s="52" t="inlineStr">
-        <is>
-          <t>01:18 PM</t>
-        </is>
+      <c r="T37" s="52" t="n">
+        <v>0.6888888888888889</v>
       </c>
       <c r="V37" s="148" t="n"/>
       <c r="X37" s="149" t="n"/>
@@ -5543,15 +5499,11 @@
       <c r="B38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="51" t="inlineStr">
-        <is>
-          <t>11:45 AM</t>
-        </is>
-      </c>
-      <c r="D38" s="51" t="inlineStr">
-        <is>
-          <t>11:46 AM</t>
-        </is>
+      <c r="C38" s="51" t="n">
+        <v>0.4993055555555556</v>
+      </c>
+      <c r="D38" s="51" t="n">
+        <v>0.5</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>3</v>
@@ -5562,10 +5514,8 @@
       <c r="J38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K38" s="51" t="inlineStr">
-        <is>
-          <t>11:03 AM</t>
-        </is>
+      <c r="K38" s="51" t="n">
+        <v>0.6868055555555556</v>
       </c>
       <c r="L38" s="51" t="n">
         <v>0.6875</v>
@@ -5579,10 +5529,8 @@
       <c r="S38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T38" s="51" t="inlineStr">
-        <is>
-          <t>01:19 PM</t>
-        </is>
+      <c r="T38" s="51" t="n">
+        <v>0.6895833333333333</v>
       </c>
       <c r="V38" s="148" t="n"/>
       <c r="X38" s="149" t="n"/>
@@ -5591,15 +5539,11 @@
       <c r="B39" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="52" t="inlineStr">
-        <is>
-          <t>11:47 AM</t>
-        </is>
-      </c>
-      <c r="D39" s="52" t="inlineStr">
-        <is>
-          <t>11:48 AM</t>
-        </is>
+      <c r="C39" s="52" t="n">
+        <v>0.5006944444444444</v>
+      </c>
+      <c r="D39" s="52" t="n">
+        <v>0.5013888888888889</v>
       </c>
       <c r="F39" s="15" t="n">
         <v>4</v>
@@ -5625,10 +5569,8 @@
       <c r="S39" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T39" s="52" t="inlineStr">
-        <is>
-          <t>01:20 PM</t>
-        </is>
+      <c r="T39" s="52" t="n">
+        <v>0.6902777777777778</v>
       </c>
       <c r="V39" s="148" t="n"/>
       <c r="X39" s="149" t="n"/>
@@ -5637,15 +5579,11 @@
       <c r="B40" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C40" s="51" t="inlineStr">
-        <is>
-          <t>11:49 AM</t>
-        </is>
-      </c>
-      <c r="D40" s="51" t="inlineStr">
-        <is>
-          <t>11:50 AM</t>
-        </is>
+      <c r="C40" s="51" t="n">
+        <v>0.5020833333333333</v>
+      </c>
+      <c r="D40" s="51" t="n">
+        <v>0.5027777777777778</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>5</v>
@@ -5671,10 +5609,8 @@
       <c r="S40" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T40" s="51" t="inlineStr">
-        <is>
-          <t>01:21 PM</t>
-        </is>
+      <c r="T40" s="51" t="n">
+        <v>0.6909722222222222</v>
       </c>
       <c r="U40" s="31" t="n"/>
       <c r="V40" s="148" t="n"/>
@@ -5684,15 +5620,11 @@
       <c r="B41" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="52" t="inlineStr">
-        <is>
-          <t>11:51 AM</t>
-        </is>
-      </c>
-      <c r="D41" s="52" t="inlineStr">
-        <is>
-          <t>11:52 AM</t>
-        </is>
+      <c r="C41" s="52" t="n">
+        <v>0.5034722222222222</v>
+      </c>
+      <c r="D41" s="52" t="n">
+        <v>0.5041666666666667</v>
       </c>
       <c r="F41" s="15" t="n">
         <v>6</v>
@@ -6243,10 +6175,8 @@
       <c r="S56" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T56" s="51" t="inlineStr">
-        <is>
-          <t>01:28 PM</t>
-        </is>
+      <c r="T56" s="51" t="n">
+        <v>0.6965277777777777</v>
       </c>
       <c r="V56" s="148" t="n"/>
       <c r="X56" s="149" t="n"/>
@@ -6285,10 +6215,8 @@
       <c r="S57" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T57" s="52" t="inlineStr">
-        <is>
-          <t>01:29 PM</t>
-        </is>
+      <c r="T57" s="52" t="n">
+        <v>0.6972222222222222</v>
       </c>
       <c r="V57" s="148" t="n"/>
       <c r="X57" s="149" t="n"/>
@@ -6331,10 +6259,8 @@
       <c r="S58" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T58" s="51" t="inlineStr">
-        <is>
-          <t>01:30 PM</t>
-        </is>
+      <c r="T58" s="51" t="n">
+        <v>0.6979166666666666</v>
       </c>
       <c r="V58" s="148" t="n"/>
       <c r="X58" s="149" t="n"/>
@@ -6343,10 +6269,8 @@
       <c r="S59" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T59" s="52" t="inlineStr">
-        <is>
-          <t>01:31 PM</t>
-        </is>
+      <c r="T59" s="52" t="n">
+        <v>0.6979166666666666</v>
       </c>
       <c r="V59" s="148" t="n"/>
       <c r="X59" s="149" t="n"/>
@@ -6384,10 +6308,8 @@
       <c r="S60" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T60" s="51" t="inlineStr">
-        <is>
-          <t>01:32 PM</t>
-        </is>
+      <c r="T60" s="51" t="n">
+        <v>0.6986111111111111</v>
       </c>
       <c r="V60" s="148" t="n"/>
       <c r="X60" s="149" t="n"/>
@@ -6906,10 +6828,8 @@
       <c r="S76" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T76" s="51" t="inlineStr">
-        <is>
-          <t>01:39 PM</t>
-        </is>
+      <c r="T76" s="51" t="n">
+        <v>0.7041666666666667</v>
       </c>
       <c r="V76" s="148" t="n"/>
       <c r="X76" s="149" t="n"/>
@@ -6918,10 +6838,8 @@
       <c r="S77" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T77" s="53" t="inlineStr">
-        <is>
-          <t>01:40 PM</t>
-        </is>
+      <c r="T77" s="53" t="n">
+        <v>0.7048611111111112</v>
       </c>
       <c r="V77" s="148" t="n"/>
       <c r="X77" s="149" t="n"/>
@@ -6930,10 +6848,8 @@
       <c r="S78" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T78" s="51" t="inlineStr">
-        <is>
-          <t>01:41 PM</t>
-        </is>
+      <c r="T78" s="51" t="n">
+        <v>0.7055555555555556</v>
       </c>
       <c r="V78" s="148" t="n"/>
       <c r="X78" s="149" t="n"/>
@@ -6942,10 +6858,8 @@
       <c r="S79" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T79" s="53" t="inlineStr">
-        <is>
-          <t>01:42 PM</t>
-        </is>
+      <c r="T79" s="53" t="n">
+        <v>0.70625</v>
       </c>
       <c r="V79" s="148" t="n"/>
       <c r="X79" s="149" t="n"/>
@@ -6954,10 +6868,8 @@
       <c r="S80" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T80" s="51" t="inlineStr">
-        <is>
-          <t>01:43 PM</t>
-        </is>
+      <c r="T80" s="51" t="n">
+        <v>0.7069444444444445</v>
       </c>
       <c r="U80" s="32" t="n"/>
       <c r="V80" s="148" t="n"/>
@@ -7044,10 +6956,8 @@
       <c r="S96" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T96" s="51" t="inlineStr">
-        <is>
-          <t>01:46 PM</t>
-        </is>
+      <c r="T96" s="51" t="n">
+        <v>0.8173611111111111</v>
       </c>
       <c r="V96" s="148" t="n"/>
       <c r="X96" s="149" t="n"/>
@@ -7056,10 +6966,8 @@
       <c r="S97" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T97" s="53" t="inlineStr">
-        <is>
-          <t>01:47 PM</t>
-        </is>
+      <c r="T97" s="53" t="n">
+        <v>0.8180555555555555</v>
       </c>
       <c r="V97" s="148" t="n"/>
       <c r="X97" s="149" t="n"/>
@@ -7175,10 +7083,8 @@
       <c r="S116" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T116" s="51" t="inlineStr">
-        <is>
-          <t>01:55 PM</t>
-        </is>
+      <c r="T116" s="51" t="n">
+        <v>0.7125</v>
       </c>
       <c r="V116" s="148" t="n"/>
       <c r="X116" s="149" t="n"/>
@@ -7187,10 +7093,8 @@
       <c r="S117" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T117" s="53" t="inlineStr">
-        <is>
-          <t>01:56 PM</t>
-        </is>
+      <c r="T117" s="53" t="n">
+        <v>0.7131944444444445</v>
       </c>
       <c r="V117" s="148" t="n"/>
       <c r="X117" s="149" t="n"/>
@@ -7199,10 +7103,8 @@
       <c r="S118" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T118" s="51" t="inlineStr">
-        <is>
-          <t>01:57 PM</t>
-        </is>
+      <c r="T118" s="51" t="n">
+        <v>0.7138888888888889</v>
       </c>
       <c r="V118" s="148" t="n"/>
       <c r="X118" s="149" t="n"/>
@@ -7211,10 +7113,8 @@
       <c r="S119" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T119" s="53" t="inlineStr">
-        <is>
-          <t>01:58 PM</t>
-        </is>
+      <c r="T119" s="53" t="n">
+        <v>0.7145833333333333</v>
       </c>
       <c r="V119" s="148" t="n"/>
       <c r="X119" s="149" t="n"/>
@@ -7223,10 +7123,8 @@
       <c r="S120" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T120" s="51" t="inlineStr">
-        <is>
-          <t>01:59 PM</t>
-        </is>
+      <c r="T120" s="51" t="n">
+        <v>0.7152777777777778</v>
       </c>
       <c r="V120" s="148" t="n"/>
       <c r="X120" s="149" t="n"/>
@@ -7312,10 +7210,8 @@
       <c r="S136" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T136" s="51" t="inlineStr">
-        <is>
-          <t>02:07 PM</t>
-        </is>
+      <c r="T136" s="51" t="n">
+        <v>0.4930555555555556</v>
       </c>
       <c r="V136" s="148" t="n"/>
       <c r="X136" s="149" t="n"/>
@@ -7324,10 +7220,8 @@
       <c r="S137" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T137" s="53" t="inlineStr">
-        <is>
-          <t>02:08 PM</t>
-        </is>
+      <c r="T137" s="53" t="n">
+        <v>0.49375</v>
       </c>
       <c r="V137" s="148" t="n"/>
       <c r="X137" s="149" t="n"/>
@@ -7336,10 +7230,8 @@
       <c r="S138" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T138" s="51" t="inlineStr">
-        <is>
-          <t>02:09 PM</t>
-        </is>
+      <c r="T138" s="51" t="n">
+        <v>0.4944444444444445</v>
       </c>
       <c r="V138" s="148" t="n"/>
       <c r="X138" s="149" t="n"/>
@@ -7348,10 +7240,8 @@
       <c r="S139" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T139" s="53" t="inlineStr">
-        <is>
-          <t>02:10 PM</t>
-        </is>
+      <c r="T139" s="53" t="n">
+        <v>0.4951388888888889</v>
       </c>
       <c r="V139" s="148" t="n"/>
       <c r="X139" s="149" t="n"/>
@@ -7360,10 +7250,8 @@
       <c r="S140" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T140" s="51" t="inlineStr">
-        <is>
-          <t>02:11 PM</t>
-        </is>
+      <c r="T140" s="51" t="n">
+        <v>0.4958333333333333</v>
       </c>
       <c r="V140" s="148" t="n"/>
       <c r="X140" s="149" t="n"/>

--- a/Pruebas_Homologacion_PS_3G_4G.xlsx
+++ b/Pruebas_Homologacion_PS_3G_4G.xlsx
@@ -4983,14 +4983,14 @@
     <row r="15" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B15" s="132" t="inlineStr">
         <is>
-          <t>Modelo: V2543</t>
+          <t>Modelo: V2537</t>
         </is>
       </c>
       <c r="C15" s="133" t="n"/>
       <c r="D15" s="134" t="n"/>
       <c r="F15" s="74" t="inlineStr">
         <is>
-          <t>Línea Prepago con saldo: 5549222015</t>
+          <t>Línea Prepago con saldo: 5545367869</t>
         </is>
       </c>
       <c r="G15" s="133" t="n"/>
@@ -5003,7 +5003,7 @@
     <row r="16" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B16" s="132" t="inlineStr">
         <is>
-          <t>Fecha de pruebas: 02/03/2026</t>
+          <t>Fecha de pruebas: 25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="133" t="n"/>
@@ -5151,11 +5151,15 @@
       <c r="F22" s="47" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="G22" s="47" t="n">
-        <v>0.6965277777777777</v>
-      </c>
-      <c r="H22" s="47" t="n">
-        <v>0.6986111111111111</v>
+      <c r="G22" s="47" t="inlineStr">
+        <is>
+          <t>04:29 PM</t>
+        </is>
+      </c>
+      <c r="H22" s="47" t="inlineStr">
+        <is>
+          <t>04:33 PM</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -6175,8 +6179,10 @@
       <c r="S56" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T56" s="51" t="n">
-        <v>0.6965277777777777</v>
+      <c r="T56" s="51" t="inlineStr">
+        <is>
+          <t>04:29 PM</t>
+        </is>
       </c>
       <c r="V56" s="148" t="n"/>
       <c r="X56" s="149" t="n"/>
@@ -6215,8 +6221,10 @@
       <c r="S57" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T57" s="52" t="n">
-        <v>0.6972222222222222</v>
+      <c r="T57" s="52" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
       </c>
       <c r="V57" s="148" t="n"/>
       <c r="X57" s="149" t="n"/>
@@ -6259,8 +6267,10 @@
       <c r="S58" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T58" s="51" t="n">
-        <v>0.6979166666666666</v>
+      <c r="T58" s="51" t="inlineStr">
+        <is>
+          <t>04:31 PM</t>
+        </is>
       </c>
       <c r="V58" s="148" t="n"/>
       <c r="X58" s="149" t="n"/>
@@ -6269,8 +6279,10 @@
       <c r="S59" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T59" s="52" t="n">
-        <v>0.6979166666666666</v>
+      <c r="T59" s="52" t="inlineStr">
+        <is>
+          <t>04:32 PM</t>
+        </is>
       </c>
       <c r="V59" s="148" t="n"/>
       <c r="X59" s="149" t="n"/>
@@ -6308,8 +6320,10 @@
       <c r="S60" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T60" s="51" t="n">
-        <v>0.6986111111111111</v>
+      <c r="T60" s="51" t="inlineStr">
+        <is>
+          <t>04:33 PM</t>
+        </is>
       </c>
       <c r="V60" s="148" t="n"/>
       <c r="X60" s="149" t="n"/>

--- a/Pruebas_Homologacion_PS_3G_4G.xlsx
+++ b/Pruebas_Homologacion_PS_3G_4G.xlsx
@@ -5003,14 +5003,14 @@
     <row r="16" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="B16" s="132" t="inlineStr">
         <is>
-          <t>Fecha de pruebas: 25/05/2026</t>
+          <t>Fecha de pruebas: 26/05/2026</t>
         </is>
       </c>
       <c r="C16" s="133" t="n"/>
       <c r="D16" s="134" t="n"/>
       <c r="F16" s="74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Línea Prepago sin saldo: 5549222015 </t>
+          <t>Línea Prepago sin saldo: 5545367869</t>
         </is>
       </c>
       <c r="G16" s="133" t="n"/>
@@ -5139,12 +5139,8 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="C22" s="46" t="n">
-        <v>0.7159722222222222</v>
-      </c>
-      <c r="D22" s="47" t="n">
-        <v>0.7222222222222222</v>
-      </c>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="47" t="n"/>
       <c r="E22" s="46" t="n">
         <v>0.7020833333333333</v>
       </c>
@@ -5153,12 +5149,12 @@
       </c>
       <c r="G22" s="47" t="inlineStr">
         <is>
-          <t>04:29 PM</t>
+          <t>11:11 AM</t>
         </is>
       </c>
       <c r="H22" s="47" t="inlineStr">
         <is>
-          <t>04:33 PM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
     </row>
@@ -5207,11 +5203,15 @@
       <c r="F24" s="65" t="n">
         <v>0.7381944444444445</v>
       </c>
-      <c r="G24" s="47" t="n">
-        <v>0.8173611111111111</v>
-      </c>
-      <c r="H24" s="47" t="n">
-        <v>0.8201388888888889</v>
+      <c r="G24" s="47" t="inlineStr">
+        <is>
+          <t>12:08 PM</t>
+        </is>
+      </c>
+      <c r="H24" s="47" t="inlineStr">
+        <is>
+          <t>12:12 PM</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" thickBot="1">
@@ -5472,8 +5472,10 @@
       <c r="F37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="53" t="n">
-        <v>0.7166666666666667</v>
+      <c r="G37" s="53" t="inlineStr">
+        <is>
+          <t>11:41 AM</t>
+        </is>
       </c>
       <c r="J37" s="15" t="n">
         <v>2</v>
@@ -5512,8 +5514,10 @@
       <c r="F38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="51" t="n">
-        <v>0.7173611111111111</v>
+      <c r="G38" s="51" t="inlineStr">
+        <is>
+          <t>11:42 AM</t>
+        </is>
       </c>
       <c r="J38" s="1" t="n">
         <v>3</v>
@@ -5552,8 +5556,10 @@
       <c r="F39" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="G39" s="52" t="n">
-        <v>0.7180555555555556</v>
+      <c r="G39" s="52" t="inlineStr">
+        <is>
+          <t>11:43 AM</t>
+        </is>
       </c>
       <c r="J39" s="15" t="n">
         <v>4</v>
@@ -5592,8 +5598,10 @@
       <c r="F40" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G40" s="51" t="n">
-        <v>0.71875</v>
+      <c r="G40" s="51" t="inlineStr">
+        <is>
+          <t>11:44 AM</t>
+        </is>
       </c>
       <c r="J40" s="1" t="n">
         <v>5</v>
@@ -5633,8 +5641,10 @@
       <c r="F41" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="G41" s="52" t="n">
-        <v>0.7194444444444444</v>
+      <c r="G41" s="52" t="inlineStr">
+        <is>
+          <t>11:45 AM</t>
+        </is>
       </c>
       <c r="J41" s="15" t="n">
         <v>6</v>
@@ -5667,8 +5677,10 @@
       <c r="F42" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G42" s="51" t="n">
-        <v>0.7201388888888889</v>
+      <c r="G42" s="51" t="inlineStr">
+        <is>
+          <t>11:46 AM</t>
+        </is>
       </c>
       <c r="J42" s="1" t="n">
         <v>7</v>
@@ -5701,8 +5713,10 @@
       <c r="F43" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="G43" s="53" t="n">
-        <v>0.7208333333333333</v>
+      <c r="G43" s="53" t="inlineStr">
+        <is>
+          <t>11:47 AM</t>
+        </is>
       </c>
       <c r="J43" s="15" t="n">
         <v>8</v>
@@ -5735,8 +5749,10 @@
       <c r="F44" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G44" s="51" t="n">
-        <v>0.7215277777777778</v>
+      <c r="G44" s="51" t="inlineStr">
+        <is>
+          <t>11:48 AM</t>
+        </is>
       </c>
       <c r="J44" s="1" t="n">
         <v>9</v>
@@ -6181,7 +6197,7 @@
       </c>
       <c r="T56" s="51" t="inlineStr">
         <is>
-          <t>04:29 PM</t>
+          <t>11:11 AM</t>
         </is>
       </c>
       <c r="V56" s="148" t="n"/>
@@ -6223,7 +6239,7 @@
       </c>
       <c r="T57" s="52" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>11:12 AM</t>
         </is>
       </c>
       <c r="V57" s="148" t="n"/>
@@ -6269,7 +6285,7 @@
       </c>
       <c r="T58" s="51" t="inlineStr">
         <is>
-          <t>04:31 PM</t>
+          <t>11:13 AM</t>
         </is>
       </c>
       <c r="V58" s="148" t="n"/>
@@ -6281,7 +6297,7 @@
       </c>
       <c r="T59" s="52" t="inlineStr">
         <is>
-          <t>04:32 PM</t>
+          <t>11:14 AM</t>
         </is>
       </c>
       <c r="V59" s="148" t="n"/>
@@ -6322,7 +6338,7 @@
       </c>
       <c r="T60" s="51" t="inlineStr">
         <is>
-          <t>04:33 PM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="V60" s="148" t="n"/>
@@ -6970,8 +6986,10 @@
       <c r="S96" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T96" s="51" t="n">
-        <v>0.8173611111111111</v>
+      <c r="T96" s="51" t="inlineStr">
+        <is>
+          <t>12:08 PM</t>
+        </is>
       </c>
       <c r="V96" s="148" t="n"/>
       <c r="X96" s="149" t="n"/>
@@ -6980,8 +6998,10 @@
       <c r="S97" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="T97" s="53" t="n">
-        <v>0.8180555555555555</v>
+      <c r="T97" s="53" t="inlineStr">
+        <is>
+          <t>12:09 PM</t>
+        </is>
       </c>
       <c r="V97" s="148" t="n"/>
       <c r="X97" s="149" t="n"/>
@@ -6990,8 +7010,10 @@
       <c r="S98" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T98" s="51" t="n">
-        <v>0.81875</v>
+      <c r="T98" s="51" t="inlineStr">
+        <is>
+          <t>12:10 PM</t>
+        </is>
       </c>
       <c r="V98" s="148" t="n"/>
       <c r="X98" s="149" t="n"/>
@@ -7000,8 +7022,10 @@
       <c r="S99" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="T99" s="53" t="n">
-        <v>0.8194444444444444</v>
+      <c r="T99" s="53" t="inlineStr">
+        <is>
+          <t>12:11 PM</t>
+        </is>
       </c>
       <c r="V99" s="148" t="n"/>
       <c r="X99" s="149" t="n"/>
@@ -7010,8 +7034,10 @@
       <c r="S100" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T100" s="51" t="n">
-        <v>0.8201388888888889</v>
+      <c r="T100" s="51" t="inlineStr">
+        <is>
+          <t>12:12 PM</t>
+        </is>
       </c>
       <c r="V100" s="148" t="n"/>
       <c r="X100" s="149" t="n"/>

--- a/Pruebas_Homologacion_PS_3G_4G.xlsx
+++ b/Pruebas_Homologacion_PS_3G_4G.xlsx
@@ -2333,11 +2333,15 @@
       <c r="F24" s="47" t="n">
         <v>0.6486111111111111</v>
       </c>
-      <c r="G24" s="62" t="n">
-        <v>0.8104166666666667</v>
-      </c>
-      <c r="H24" s="62" t="n">
-        <v>0.8131944444444444</v>
+      <c r="G24" s="62" t="inlineStr">
+        <is>
+          <t>03:19 PM</t>
+        </is>
+      </c>
+      <c r="H24" s="62" t="inlineStr">
+        <is>
+          <t>03:23 PM</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
@@ -4082,8 +4086,10 @@
       <c r="S96" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T96" s="41" t="n">
-        <v>0.8104166666666667</v>
+      <c r="T96" s="41" t="inlineStr">
+        <is>
+          <t>03:19 PM</t>
+        </is>
       </c>
       <c r="V96" s="148" t="n"/>
       <c r="X96" s="149" t="n"/>
@@ -4092,8 +4098,10 @@
       <c r="S97" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="T97" s="62" t="n">
-        <v>0.8111111111111111</v>
+      <c r="T97" s="62" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
       </c>
       <c r="V97" s="148" t="n"/>
       <c r="X97" s="149" t="n"/>
@@ -4102,8 +4110,10 @@
       <c r="S98" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T98" s="41" t="n">
-        <v>0.8118055555555556</v>
+      <c r="T98" s="41" t="inlineStr">
+        <is>
+          <t>03:21 PM</t>
+        </is>
       </c>
       <c r="V98" s="148" t="n"/>
       <c r="X98" s="149" t="n"/>
@@ -4112,8 +4122,10 @@
       <c r="S99" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="T99" s="62" t="n">
-        <v>0.8125</v>
+      <c r="T99" s="62" t="inlineStr">
+        <is>
+          <t>03:22 PM</t>
+        </is>
       </c>
       <c r="V99" s="148" t="n"/>
       <c r="X99" s="149" t="n"/>
@@ -4122,8 +4134,10 @@
       <c r="S100" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T100" s="41" t="n">
-        <v>0.8131944444444444</v>
+      <c r="T100" s="41" t="inlineStr">
+        <is>
+          <t>03:23 PM</t>
+        </is>
       </c>
       <c r="U100" s="31" t="n"/>
       <c r="V100" s="148" t="n"/>

--- a/Pruebas_Homologacion_PS_3G_4G.xlsx
+++ b/Pruebas_Homologacion_PS_3G_4G.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af84f4d10fd3b46f/Documentos/GitHub/Proyecto-AES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_6B0E68A4DEAD5569F8AD57E21A0C88C75B43593B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29F2F16E-5A92-4EB3-8DDD-0B4E7B500E70}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_38F80B146DD0B8FE5ECE89A6BF30B09AE7C46606" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EB74542-7D3D-40D3-B19C-79703430FD44}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="794" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Señalización_3G" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="94">
   <si>
     <t>PRUEBAS DE CALIDAD PACKET SWITCH</t>
   </si>
@@ -74,114 +74,105 @@
     <t>01:19 PM</t>
   </si>
   <si>
-    <t>02:04 PM</t>
+    <t>04:21 PM</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>04:28 PM</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>04:31 PM</t>
+  </si>
+  <si>
+    <t>Twitter</t>
+  </si>
+  <si>
+    <t>02:38 PM</t>
+  </si>
+  <si>
+    <t>02:42 PM</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>Correo</t>
+  </si>
+  <si>
+    <t>DETALLE DE LAS PRUEBAS</t>
+  </si>
+  <si>
+    <t>PRUEBAS DE PREPAGO CON SALDO</t>
+  </si>
+  <si>
+    <t>PRUEBAS DE PREPAGO SIN SALDO</t>
+  </si>
+  <si>
+    <t>IMÁGENES</t>
+  </si>
+  <si>
+    <t>Pruebas de MMS</t>
+  </si>
+  <si>
+    <t>Pruebas de Internet</t>
+  </si>
+  <si>
+    <t># Prueba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envío </t>
+  </si>
+  <si>
+    <t>Recepción</t>
+  </si>
+  <si>
+    <t>Acceso</t>
+  </si>
+  <si>
+    <t>02:06 PM</t>
+  </si>
+  <si>
+    <t>02:07 PM</t>
   </si>
   <si>
     <t>02:08 PM</t>
   </si>
   <si>
-    <t>Internet</t>
-  </si>
-  <si>
-    <t>02:15 PM</t>
+    <t>Pruebas de Youtube</t>
+  </si>
+  <si>
+    <t>Pruebas de twitter</t>
+  </si>
+  <si>
+    <t>02:17 PM</t>
+  </si>
+  <si>
+    <t>02:18 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pruebas de facebook </t>
+  </si>
+  <si>
+    <t>Pruebas de correo</t>
   </si>
   <si>
     <t>02:19 PM</t>
   </si>
   <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>02:27 PM</t>
+    <t>02:29 PM</t>
+  </si>
+  <si>
+    <t>02:30 PM</t>
   </si>
   <si>
     <t>02:31 PM</t>
   </si>
   <si>
-    <t>Twitter</t>
-  </si>
-  <si>
-    <t>02:38 PM</t>
-  </si>
-  <si>
-    <t>02:42 PM</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>Correo</t>
-  </si>
-  <si>
-    <t>DETALLE DE LAS PRUEBAS</t>
-  </si>
-  <si>
-    <t>PRUEBAS DE PREPAGO CON SALDO</t>
-  </si>
-  <si>
-    <t>PRUEBAS DE PREPAGO SIN SALDO</t>
-  </si>
-  <si>
-    <t>IMÁGENES</t>
-  </si>
-  <si>
-    <t>Pruebas de MMS</t>
-  </si>
-  <si>
-    <t>Pruebas de Internet</t>
-  </si>
-  <si>
-    <t># Prueba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Envío </t>
-  </si>
-  <si>
-    <t>Recepción</t>
-  </si>
-  <si>
-    <t>Acceso</t>
-  </si>
-  <si>
-    <t>02:05 PM</t>
-  </si>
-  <si>
-    <t>02:06 PM</t>
-  </si>
-  <si>
-    <t>02:07 PM</t>
-  </si>
-  <si>
-    <t>Pruebas de Youtube</t>
-  </si>
-  <si>
-    <t>Pruebas de twitter</t>
-  </si>
-  <si>
-    <t>02:16 PM</t>
-  </si>
-  <si>
-    <t>02:17 PM</t>
-  </si>
-  <si>
-    <t>02:18 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de facebook </t>
-  </si>
-  <si>
-    <t>Pruebas de correo</t>
-  </si>
-  <si>
-    <t>02:28 PM</t>
-  </si>
-  <si>
-    <t>02:29 PM</t>
-  </si>
-  <si>
-    <t>02:30 PM</t>
-  </si>
-  <si>
     <t>02:39 PM</t>
   </si>
   <si>
@@ -212,67 +203,67 @@
     <t>Línea Pospago: 5530760949</t>
   </si>
   <si>
-    <t>Modelo: V2537</t>
-  </si>
-  <si>
     <t>Línea Prepago con saldo: 5545367869</t>
   </si>
   <si>
-    <t>11:11 AM</t>
+    <t>04:35 PM</t>
+  </si>
+  <si>
+    <t>04:41 PM</t>
+  </si>
+  <si>
+    <t>04:42 PM</t>
+  </si>
+  <si>
+    <t>04:49 PM</t>
+  </si>
+  <si>
+    <t>04:52 PM</t>
+  </si>
+  <si>
+    <t>DETALLE DE PRUEBAS</t>
+  </si>
+  <si>
+    <t>11:41 AM</t>
+  </si>
+  <si>
+    <t>11:42 AM</t>
+  </si>
+  <si>
+    <t>11:43 AM</t>
+  </si>
+  <si>
+    <t>11:44 AM</t>
+  </si>
+  <si>
+    <t>11:45 AM</t>
+  </si>
+  <si>
+    <t>11:46 AM</t>
+  </si>
+  <si>
+    <t>11:47 AM</t>
+  </si>
+  <si>
+    <t>11:48 AM</t>
+  </si>
+  <si>
+    <t>11:13 AM</t>
+  </si>
+  <si>
+    <t>11:14 AM</t>
   </si>
   <si>
     <t>11:15 AM</t>
   </si>
   <si>
-    <t>12:08 PM</t>
+    <t>12:10 PM</t>
+  </si>
+  <si>
+    <t>12:11 PM</t>
   </si>
   <si>
     <t>12:12 PM</t>
-  </si>
-  <si>
-    <t>DETALLE DE PRUEBAS</t>
-  </si>
-  <si>
-    <t>11:41 AM</t>
-  </si>
-  <si>
-    <t>11:42 AM</t>
-  </si>
-  <si>
-    <t>11:43 AM</t>
-  </si>
-  <si>
-    <t>11:44 AM</t>
-  </si>
-  <si>
-    <t>11:45 AM</t>
-  </si>
-  <si>
-    <t>11:46 AM</t>
-  </si>
-  <si>
-    <t>11:47 AM</t>
-  </si>
-  <si>
-    <t>11:48 AM</t>
-  </si>
-  <si>
-    <t>11:12 AM</t>
-  </si>
-  <si>
-    <t>11:13 AM</t>
-  </si>
-  <si>
-    <t>11:14 AM</t>
-  </si>
-  <si>
-    <t>12:09 PM</t>
-  </si>
-  <si>
-    <t>12:10 PM</t>
-  </si>
-  <si>
-    <t>12:11 PM</t>
   </si>
   <si>
     <t>Throughput DL/UL Postpago 4G</t>
@@ -1447,12 +1438,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1581,9 +1572,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>250088</xdr:colOff>
+      <xdr:colOff>251358</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>98670</xdr:rowOff>
+      <xdr:rowOff>99940</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1642,6 +1633,114 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2381250" cy="3762375"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 3" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2381250" cy="3762375"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 4" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2381250" cy="3762375"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 5" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1765,6 +1864,78 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2381250" cy="3762375"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2381250" cy="3762375"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2136,40 +2307,40 @@
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="74"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="73"/>
       <c r="F14" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
     </row>
     <row r="15" spans="2:8" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="74"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="73"/>
       <c r="F15" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
     </row>
     <row r="16" spans="2:8" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="72" t="s">
+      <c r="B16" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="74"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="73"/>
       <c r="F16" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
     </row>
     <row r="17" spans="1:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2238,12 +2409,12 @@
         <v>16</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="46">
         <v>0.58194444444444449</v>
@@ -2258,15 +2429,15 @@
         <v>0.61597222222222225</v>
       </c>
       <c r="G22" s="62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H22" s="62" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="43">
         <v>0.59375</v>
@@ -2281,15 +2452,15 @@
         <v>0.62777777777777777</v>
       </c>
       <c r="G23" s="41" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H23" s="41" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="45" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C24" s="46">
         <v>0.60486111111111107</v>
@@ -2304,15 +2475,15 @@
         <v>0.64861111111111114</v>
       </c>
       <c r="G24" s="62" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C25" s="43">
         <v>0.62361111111111112</v>
@@ -2336,7 +2507,7 @@
     </row>
     <row r="26" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="48" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C26" s="49">
         <v>0.64236111111111116</v>
@@ -2360,7 +2531,7 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="B28" s="95" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C28" s="81"/>
     </row>
@@ -2371,16 +2542,16 @@
       </c>
       <c r="C32" s="70"/>
       <c r="J32" s="86" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K32" s="87"/>
       <c r="L32" s="87"/>
       <c r="S32" s="75" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T32" s="76"/>
       <c r="V32" s="75" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="W32" s="76"/>
       <c r="X32" s="76"/>
@@ -2388,25 +2559,25 @@
     <row r="33" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="71"/>
+        <v>30</v>
+      </c>
+      <c r="C34" s="74"/>
       <c r="D34" s="70"/>
       <c r="F34" s="69" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G34" s="70"/>
       <c r="J34" s="98" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K34" s="87"/>
       <c r="L34" s="87"/>
       <c r="N34" s="98" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O34" s="87"/>
       <c r="S34" s="75" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="T34" s="76"/>
       <c r="V34" s="77"/>
@@ -2415,40 +2586,40 @@
     </row>
     <row r="35" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F35" s="14" t="s">
+      <c r="J35" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="G35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="J35" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="K35" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L35" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="N35" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="O35" s="55" t="s">
-        <v>38</v>
-      </c>
       <c r="S35" s="17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="V35" s="80"/>
       <c r="W35" s="81"/>
@@ -2535,7 +2706,7 @@
         <v>2</v>
       </c>
       <c r="T37" s="52" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="V37" s="80"/>
       <c r="W37" s="81"/>
@@ -2576,7 +2747,7 @@
         <v>3</v>
       </c>
       <c r="T38" s="51" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="V38" s="80"/>
       <c r="W38" s="81"/>
@@ -2617,7 +2788,7 @@
         <v>4</v>
       </c>
       <c r="T39" s="52" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="V39" s="80"/>
       <c r="W39" s="81"/>
@@ -2658,7 +2829,7 @@
         <v>5</v>
       </c>
       <c r="T40" s="51" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="V40" s="80"/>
       <c r="W40" s="81"/>
@@ -2853,20 +3024,20 @@
     </row>
     <row r="47" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="69" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C47" s="70"/>
       <c r="F47" s="69" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" s="71"/>
+        <v>40</v>
+      </c>
+      <c r="G47" s="74"/>
       <c r="H47" s="70"/>
       <c r="J47" s="86" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K47" s="87"/>
       <c r="N47" s="86" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O47" s="87"/>
       <c r="P47" s="87"/>
@@ -2876,34 +3047,34 @@
     </row>
     <row r="48" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>38</v>
-      </c>
       <c r="F48" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="G48" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J48" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="K48" s="55" t="s">
-        <v>38</v>
-      </c>
       <c r="N48" s="16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O48" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P48" s="55" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="V48" s="80"/>
       <c r="W48" s="81"/>
@@ -3118,7 +3289,7 @@
         <v>0.6430555555555556</v>
       </c>
       <c r="S54" s="96" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="T54" s="76"/>
       <c r="V54" s="77"/>
@@ -3157,10 +3328,10 @@
         <v>0.64444444444444449</v>
       </c>
       <c r="S55" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="T55" s="61" t="s">
         <v>35</v>
-      </c>
-      <c r="T55" s="61" t="s">
-        <v>38</v>
       </c>
       <c r="V55" s="80"/>
       <c r="W55" s="81"/>
@@ -3201,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V56" s="80"/>
       <c r="W56" s="81"/>
@@ -3242,7 +3413,7 @@
         <v>2</v>
       </c>
       <c r="T57" s="52" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="V57" s="80"/>
       <c r="W57" s="81"/>
@@ -3287,7 +3458,7 @@
         <v>3</v>
       </c>
       <c r="T58" s="51" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="V58" s="80"/>
       <c r="W58" s="81"/>
@@ -3298,7 +3469,7 @@
         <v>4</v>
       </c>
       <c r="T59" s="52" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V59" s="80"/>
       <c r="W59" s="81"/>
@@ -3306,22 +3477,22 @@
     </row>
     <row r="60" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="69" t="s">
-        <v>47</v>
-      </c>
-      <c r="C60" s="71"/>
+        <v>43</v>
+      </c>
+      <c r="C60" s="74"/>
       <c r="D60" s="70"/>
       <c r="F60" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="G60" s="71"/>
+        <v>44</v>
+      </c>
+      <c r="G60" s="74"/>
       <c r="H60" s="70"/>
       <c r="J60" s="86" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K60" s="87"/>
       <c r="L60" s="87"/>
       <c r="N60" s="86" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O60" s="87"/>
       <c r="P60" s="87"/>
@@ -3330,7 +3501,7 @@
         <v>5</v>
       </c>
       <c r="T60" s="51" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="V60" s="80"/>
       <c r="W60" s="81"/>
@@ -3338,41 +3509,41 @@
     </row>
     <row r="61" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J61" s="16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K61" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L61" s="55" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M61" s="31"/>
       <c r="N61" s="16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O61" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P61" s="55" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="V61" s="80"/>
       <c r="W61" s="81"/>
@@ -3807,7 +3978,7 @@
     <row r="73" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:24" x14ac:dyDescent="0.35">
       <c r="S74" s="96" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="T74" s="76"/>
       <c r="V74" s="77"/>
@@ -3816,10 +3987,10 @@
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.35">
       <c r="S75" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="T75" s="61" t="s">
         <v>35</v>
-      </c>
-      <c r="T75" s="61" t="s">
-        <v>38</v>
       </c>
       <c r="V75" s="80"/>
       <c r="W75" s="81"/>
@@ -3831,7 +4002,7 @@
         <v>1</v>
       </c>
       <c r="T76" s="51" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V76" s="80"/>
       <c r="W76" s="81"/>
@@ -3842,7 +4013,7 @@
         <v>2</v>
       </c>
       <c r="T77" s="53" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="V77" s="80"/>
       <c r="W77" s="81"/>
@@ -3853,7 +4024,7 @@
         <v>3</v>
       </c>
       <c r="T78" s="51" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="V78" s="80"/>
       <c r="W78" s="81"/>
@@ -3864,7 +4035,7 @@
         <v>4</v>
       </c>
       <c r="T79" s="53" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="V79" s="80"/>
       <c r="W79" s="81"/>
@@ -3875,7 +4046,7 @@
         <v>5</v>
       </c>
       <c r="T80" s="51" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="U80" s="31"/>
       <c r="V80" s="80"/>
@@ -3945,7 +4116,7 @@
     <row r="93" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S94" s="96" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="T94" s="76"/>
       <c r="V94" s="77"/>
@@ -3954,10 +4125,10 @@
     </row>
     <row r="95" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S95" s="17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T95" s="17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="V95" s="80"/>
       <c r="W95" s="81"/>
@@ -3968,7 +4139,7 @@
         <v>1</v>
       </c>
       <c r="T96" s="41" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V96" s="80"/>
       <c r="W96" s="81"/>
@@ -3979,7 +4150,7 @@
         <v>2</v>
       </c>
       <c r="T97" s="62" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="V97" s="80"/>
       <c r="W97" s="81"/>
@@ -3990,7 +4161,7 @@
         <v>3</v>
       </c>
       <c r="T98" s="41" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="V98" s="80"/>
       <c r="W98" s="81"/>
@@ -4001,7 +4172,7 @@
         <v>4</v>
       </c>
       <c r="T99" s="62" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="V99" s="80"/>
       <c r="W99" s="81"/>
@@ -4012,7 +4183,7 @@
         <v>5</v>
       </c>
       <c r="T100" s="41" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U100" s="31"/>
       <c r="V100" s="80"/>
@@ -4082,7 +4253,7 @@
     <row r="113" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="114" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S114" s="75" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T114" s="76"/>
       <c r="V114" s="77"/>
@@ -4091,10 +4262,10 @@
     </row>
     <row r="115" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S115" s="17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T115" s="17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="V115" s="80"/>
       <c r="W115" s="81"/>
@@ -4219,7 +4390,7 @@
     <row r="133" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="134" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S134" s="75" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T134" s="76"/>
       <c r="V134" s="77"/>
@@ -4228,10 +4399,10 @@
     </row>
     <row r="135" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S135" s="17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T135" s="17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="V135" s="80"/>
       <c r="W135" s="81"/>
@@ -4380,14 +4551,14 @@
     <mergeCell ref="J47:K47"/>
     <mergeCell ref="S114:T114"/>
     <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B14:D14"/>
     <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B14:D14"/>
     <mergeCell ref="S134:T134"/>
     <mergeCell ref="V54:X72"/>
     <mergeCell ref="V74:X92"/>
     <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="F47:H47"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="V32:X32"/>
@@ -4433,58 +4604,58 @@
     <row r="13" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="107" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C14" s="104"/>
       <c r="F14" s="107" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G14" s="104"/>
     </row>
     <row r="15" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="105" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C15" s="104"/>
       <c r="F15" s="105" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G15" s="104"/>
     </row>
     <row r="16" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="103" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C16" s="104"/>
       <c r="F16" s="103" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G16" s="104"/>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="108" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C17" s="104"/>
       <c r="F17" s="108" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G17" s="104"/>
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C19" s="106" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" s="104"/>
       <c r="F19" s="18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G19" s="106" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H19" s="104"/>
     </row>
@@ -4782,8 +4953,8 @@
     <mergeCell ref="C26:D31"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="F20:F25"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B38:B43"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="G26:H31"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="G20:H25"/>
@@ -4858,16 +5029,16 @@
       <c r="Q13" s="58"/>
     </row>
     <row r="14" spans="2:17" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="74"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="73"/>
       <c r="F14" s="94" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
+        <v>58</v>
+      </c>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
       <c r="I14" s="109"/>
       <c r="J14" s="81"/>
       <c r="K14" s="81"/>
@@ -4876,16 +5047,16 @@
       <c r="Q14" s="58"/>
     </row>
     <row r="15" spans="2:17" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="72" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="74"/>
+      <c r="B15" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="72"/>
+      <c r="D15" s="73"/>
       <c r="F15" s="94" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
+        <v>59</v>
+      </c>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
       <c r="I15" s="109"/>
       <c r="J15" s="81"/>
       <c r="K15" s="81"/>
@@ -4894,16 +5065,16 @@
       <c r="Q15" s="58"/>
     </row>
     <row r="16" spans="2:17" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="72" t="s">
+      <c r="B16" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="74"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="73"/>
       <c r="F16" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
       <c r="I16" s="109"/>
       <c r="J16" s="81"/>
       <c r="K16" s="81"/>
@@ -4990,11 +5161,11 @@
       <c r="F21" s="41">
         <v>0.69722222222222219</v>
       </c>
-      <c r="G21" s="41">
-        <v>0.68819444444444444</v>
-      </c>
-      <c r="H21" s="41">
-        <v>0.69097222222222221</v>
+      <c r="G21" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="O21" s="59"/>
       <c r="P21" s="60"/>
@@ -5004,7 +5175,7 @@
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" s="33"/>
       <c r="B22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="47"/>
@@ -5015,16 +5186,16 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G22" s="47" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H22" s="47" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" s="33"/>
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="43">
         <v>0.51527777777777772</v>
@@ -5038,17 +5209,17 @@
       <c r="F23" s="40">
         <v>0.72013888888888888</v>
       </c>
-      <c r="G23" s="40">
-        <v>0.70416666666666672</v>
-      </c>
-      <c r="H23" s="40">
-        <v>0.70694444444444449</v>
+      <c r="G23" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" s="33"/>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C24" s="46">
         <v>0.52708333333333335</v>
@@ -5063,15 +5234,15 @@
         <v>0.73819444444444449</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H24" s="47" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C25" s="43">
         <v>0.54513888888888884</v>
@@ -5095,7 +5266,7 @@
     <row r="26" spans="1:25" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="33"/>
       <c r="B26" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C26" s="49">
         <v>0.56388888888888888</v>
@@ -5118,7 +5289,7 @@
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B28" s="95" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C28" s="81"/>
     </row>
@@ -5137,16 +5308,16 @@
       </c>
       <c r="C32" s="70"/>
       <c r="J32" s="86" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K32" s="87"/>
       <c r="L32" s="87"/>
       <c r="S32" s="75" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T32" s="76"/>
       <c r="V32" s="75" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="W32" s="76"/>
       <c r="X32" s="76"/>
@@ -5154,25 +5325,25 @@
     <row r="33" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="71"/>
+        <v>30</v>
+      </c>
+      <c r="C34" s="74"/>
       <c r="D34" s="70"/>
       <c r="F34" s="69" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G34" s="70"/>
       <c r="J34" s="86" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K34" s="87"/>
       <c r="L34" s="87"/>
       <c r="N34" s="86" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O34" s="87"/>
       <c r="S34" s="75" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="T34" s="76"/>
       <c r="V34" s="77" t="e">
@@ -5184,40 +5355,40 @@
     <row r="35" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="33"/>
       <c r="B35" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F35" s="14" t="s">
+      <c r="J35" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="G35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="J35" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="K35" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L35" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="N35" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="O35" s="55" t="s">
-        <v>38</v>
-      </c>
       <c r="S35" s="17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="V35" s="80"/>
       <c r="W35" s="81"/>
@@ -5262,8 +5433,8 @@
       <c r="S36" s="1">
         <v>1</v>
       </c>
-      <c r="T36" s="51">
-        <v>0.68819444444444444</v>
+      <c r="T36" s="51" t="s">
+        <v>60</v>
       </c>
       <c r="V36" s="80"/>
       <c r="W36" s="81"/>
@@ -5283,7 +5454,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="53" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J37" s="15">
         <v>2</v>
@@ -5303,8 +5474,8 @@
       <c r="S37" s="15">
         <v>2</v>
       </c>
-      <c r="T37" s="52">
-        <v>0.68888888888888888</v>
+      <c r="T37" s="52" t="s">
+        <v>60</v>
       </c>
       <c r="V37" s="80"/>
       <c r="W37" s="81"/>
@@ -5324,7 +5495,7 @@
         <v>3</v>
       </c>
       <c r="G38" s="51" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J38" s="1">
         <v>3</v>
@@ -5365,7 +5536,7 @@
         <v>4</v>
       </c>
       <c r="G39" s="52" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J39" s="15">
         <v>4</v>
@@ -5406,7 +5577,7 @@
         <v>5</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J40" s="1">
         <v>5</v>
@@ -5448,7 +5619,7 @@
         <v>6</v>
       </c>
       <c r="G41" s="52" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J41" s="15">
         <v>6</v>
@@ -5483,7 +5654,7 @@
         <v>7</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J42" s="1">
         <v>7</v>
@@ -5518,7 +5689,7 @@
         <v>8</v>
       </c>
       <c r="G43" s="53" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J43" s="15">
         <v>8</v>
@@ -5553,7 +5724,7 @@
         <v>9</v>
       </c>
       <c r="G44" s="51" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J44" s="1">
         <v>9</v>
@@ -5622,20 +5793,20 @@
     <row r="47" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="34"/>
       <c r="B47" s="69" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C47" s="70"/>
       <c r="F47" s="69" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" s="71"/>
+        <v>40</v>
+      </c>
+      <c r="G47" s="74"/>
       <c r="H47" s="70"/>
       <c r="J47" s="86" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K47" s="87"/>
       <c r="N47" s="86" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O47" s="87"/>
       <c r="P47" s="87"/>
@@ -5645,34 +5816,34 @@
     </row>
     <row r="48" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>38</v>
-      </c>
       <c r="F48" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="G48" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J48" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="K48" s="55" t="s">
-        <v>38</v>
-      </c>
       <c r="N48" s="16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O48" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P48" s="55" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="V48" s="80"/>
       <c r="W48" s="81"/>
@@ -5887,7 +6058,7 @@
         <v>0.73263888888888884</v>
       </c>
       <c r="S54" s="75" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="T54" s="76"/>
       <c r="V54" s="77" t="e">
@@ -5928,10 +6099,10 @@
         <v>0.73402777777777772</v>
       </c>
       <c r="S55" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="T55" s="61" t="s">
         <v>35</v>
-      </c>
-      <c r="T55" s="61" t="s">
-        <v>38</v>
       </c>
       <c r="V55" s="80"/>
       <c r="W55" s="81"/>
@@ -5972,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="51" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="V56" s="80"/>
       <c r="W56" s="81"/>
@@ -6013,7 +6184,7 @@
         <v>2</v>
       </c>
       <c r="T57" s="52" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="V57" s="80"/>
       <c r="W57" s="81"/>
@@ -6058,7 +6229,7 @@
         <v>3</v>
       </c>
       <c r="T58" s="51" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="V58" s="80"/>
       <c r="W58" s="81"/>
@@ -6069,7 +6240,7 @@
         <v>4</v>
       </c>
       <c r="T59" s="52" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="V59" s="80"/>
       <c r="W59" s="81"/>
@@ -6077,22 +6248,22 @@
     </row>
     <row r="60" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="69" t="s">
-        <v>47</v>
-      </c>
-      <c r="C60" s="71"/>
+        <v>43</v>
+      </c>
+      <c r="C60" s="74"/>
       <c r="D60" s="70"/>
       <c r="F60" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="G60" s="71"/>
+        <v>44</v>
+      </c>
+      <c r="G60" s="74"/>
       <c r="H60" s="70"/>
       <c r="J60" s="86" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K60" s="87"/>
       <c r="L60" s="87"/>
       <c r="N60" s="86" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O60" s="87"/>
       <c r="P60" s="87"/>
@@ -6101,7 +6272,7 @@
         <v>5</v>
       </c>
       <c r="T60" s="51" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="V60" s="80"/>
       <c r="W60" s="81"/>
@@ -6109,41 +6280,41 @@
     </row>
     <row r="61" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E61" s="33"/>
       <c r="F61" s="14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J61" s="16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K61" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L61" s="55" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N61" s="16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O61" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P61" s="55" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="V61" s="80"/>
       <c r="W61" s="81"/>
@@ -6578,7 +6749,7 @@
     <row r="73" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:24" x14ac:dyDescent="0.35">
       <c r="S74" s="75" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="T74" s="76"/>
       <c r="V74" s="77" t="e">
@@ -6589,10 +6760,10 @@
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.35">
       <c r="S75" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="T75" s="61" t="s">
         <v>35</v>
-      </c>
-      <c r="T75" s="61" t="s">
-        <v>38</v>
       </c>
       <c r="V75" s="80"/>
       <c r="W75" s="81"/>
@@ -6603,8 +6774,8 @@
       <c r="S76" s="1">
         <v>1</v>
       </c>
-      <c r="T76" s="51">
-        <v>0.70416666666666672</v>
+      <c r="T76" s="51" t="s">
+        <v>63</v>
       </c>
       <c r="V76" s="80"/>
       <c r="W76" s="81"/>
@@ -6614,8 +6785,8 @@
       <c r="S77" s="15">
         <v>2</v>
       </c>
-      <c r="T77" s="53">
-        <v>0.70486111111111116</v>
+      <c r="T77" s="53" t="s">
+        <v>63</v>
       </c>
       <c r="V77" s="80"/>
       <c r="W77" s="81"/>
@@ -6718,7 +6889,7 @@
     <row r="93" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S94" s="96" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="T94" s="76"/>
       <c r="V94" s="77" t="e">
@@ -6729,10 +6900,10 @@
     </row>
     <row r="95" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S95" s="17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T95" s="17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="V95" s="80"/>
       <c r="W95" s="81"/>
@@ -6743,7 +6914,7 @@
         <v>1</v>
       </c>
       <c r="T96" s="51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="V96" s="80"/>
       <c r="W96" s="81"/>
@@ -6754,7 +6925,7 @@
         <v>2</v>
       </c>
       <c r="T97" s="53" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="V97" s="80"/>
       <c r="W97" s="81"/>
@@ -6765,7 +6936,7 @@
         <v>3</v>
       </c>
       <c r="T98" s="51" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="V98" s="80"/>
       <c r="W98" s="81"/>
@@ -6776,7 +6947,7 @@
         <v>4</v>
       </c>
       <c r="T99" s="53" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="V99" s="80"/>
       <c r="W99" s="81"/>
@@ -6787,7 +6958,7 @@
         <v>5</v>
       </c>
       <c r="T100" s="51" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="V100" s="80"/>
       <c r="W100" s="81"/>
@@ -6856,7 +7027,7 @@
     <row r="113" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="114" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S114" s="96" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="T114" s="76"/>
       <c r="V114" s="77" t="e">
@@ -6867,10 +7038,10 @@
     </row>
     <row r="115" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S115" s="17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T115" s="17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="V115" s="80"/>
       <c r="W115" s="81"/>
@@ -6994,7 +7165,7 @@
     <row r="133" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="134" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S134" s="75" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="T134" s="76"/>
       <c r="V134" s="77" t="e">
@@ -7005,10 +7176,10 @@
     </row>
     <row r="135" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S135" s="17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T135" s="17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="V135" s="80"/>
       <c r="W135" s="81"/>
@@ -7134,47 +7305,47 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="I15:K15"/>
     <mergeCell ref="F16:H16"/>
+    <mergeCell ref="V94:X112"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="S94:T94"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="S54:T54"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="V34:X52"/>
+    <mergeCell ref="J34:L34"/>
     <mergeCell ref="F15:H15"/>
+    <mergeCell ref="V114:X132"/>
+    <mergeCell ref="N60:P60"/>
+    <mergeCell ref="B15:D15"/>
     <mergeCell ref="V134:X152"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="S34:T34"/>
     <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F14:H14"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="S74:T74"/>
     <mergeCell ref="J47:K47"/>
-    <mergeCell ref="V94:X112"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="I15:K15"/>
     <mergeCell ref="S114:T114"/>
-    <mergeCell ref="S94:T94"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="S54:T54"/>
+    <mergeCell ref="S134:T134"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="V74:X92"/>
+    <mergeCell ref="V54:X72"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E19:F19"/>
     <mergeCell ref="V32:X32"/>
     <mergeCell ref="G19:H19"/>
-    <mergeCell ref="V114:X132"/>
-    <mergeCell ref="N60:P60"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="V34:X52"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="V74:X92"/>
-    <mergeCell ref="V54:X72"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="S134:T134"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="F14:H14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7208,58 +7379,58 @@
     <row r="13" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="107" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C14" s="104"/>
       <c r="F14" s="107" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G14" s="104"/>
     </row>
     <row r="15" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="105" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C15" s="104"/>
       <c r="F15" s="105" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G15" s="104"/>
     </row>
     <row r="16" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="103" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C16" s="104"/>
       <c r="F16" s="103" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G16" s="104"/>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="108" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C17" s="104"/>
       <c r="F17" s="108" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G17" s="104"/>
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C19" s="106" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" s="104"/>
       <c r="F19" s="18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G19" s="106" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H19" s="104"/>
     </row>
@@ -7557,8 +7728,8 @@
     <mergeCell ref="C26:D31"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="F20:F25"/>
+    <mergeCell ref="B38:B43"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B38:B43"/>
     <mergeCell ref="G26:H31"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="G20:H25"/>
@@ -7603,35 +7774,35 @@
     <row r="1" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="F2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="G2" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>88</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>91</v>
       </c>
       <c r="M2" s="31"/>
       <c r="N2" s="31"/>
     </row>
     <row r="3" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="120" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D3" s="28">
         <v>46090</v>
@@ -7652,22 +7823,22 @@
     <row r="4" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="101"/>
       <c r="C4" s="26" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D4" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>88</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>91</v>
       </c>
       <c r="M4" s="36"/>
       <c r="N4" s="36"/>
@@ -7676,7 +7847,7 @@
     <row r="5" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="101"/>
       <c r="C5" s="27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" s="28">
         <v>46090</v>
@@ -7697,22 +7868,22 @@
     <row r="6" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="101"/>
       <c r="C6" s="26" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D6" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="H6" s="26" t="s">
         <v>88</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>91</v>
       </c>
       <c r="M6" s="36"/>
       <c r="N6" s="36"/>
@@ -7721,7 +7892,7 @@
     <row r="7" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="101"/>
       <c r="C7" s="27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D7" s="28">
         <v>46090</v>
@@ -7745,10 +7916,10 @@
     <row r="9" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:15" ht="29.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="29" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C10" s="111" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D10" s="112"/>
       <c r="E10" s="112"/>

--- a/Pruebas_Homologacion_PS_3G_4G.xlsx
+++ b/Pruebas_Homologacion_PS_3G_4G.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af84f4d10fd3b46f/Documentos/GitHub/Proyecto-AES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_2ECE65741E38F25F0CB6100BD974CFFD91828F43" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00383962-1B99-4481-962C-47558A438AB5}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_CBAD75752E4E683D41551FDD62BCCC4CAACBFF99" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EB72863-B7C6-4791-AE71-1B188B6CA96D}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="794" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Señalización_3G" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="105">
   <si>
     <t>PRUEBAS DE CALIDAD PACKET SWITCH</t>
   </si>
@@ -32,40 +32,193 @@
     <t>Marca: vivo</t>
   </si>
   <si>
+    <t>Línea Pospago: 5530760949</t>
+  </si>
+  <si>
+    <t>Modelo: V2515</t>
+  </si>
+  <si>
+    <t>Línea Prepago con saldo: 5545367869</t>
+  </si>
+  <si>
+    <t>Fecha de pruebas: 27/05/2026</t>
+  </si>
+  <si>
+    <t>Línea Prepago sin saldo: 5545367869</t>
+  </si>
+  <si>
+    <t>Prueba</t>
+  </si>
+  <si>
+    <t>PRUEBAS DE POS PAGO</t>
+  </si>
+  <si>
+    <t>PRUEBAS DE PCS</t>
+  </si>
+  <si>
+    <t>PRUEBAS DE PSS</t>
+  </si>
+  <si>
+    <t>Hora de inicio</t>
+  </si>
+  <si>
+    <t>Hora de término</t>
+  </si>
+  <si>
+    <t>MMS</t>
+  </si>
+  <si>
+    <t>05:49 PM</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>11:11 AM</t>
+  </si>
+  <si>
+    <t>11:15 AM</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>Twitter</t>
+  </si>
+  <si>
+    <t>01:22 PM</t>
+  </si>
+  <si>
+    <t>01:26 PM</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>11:00 AM</t>
+  </si>
+  <si>
+    <t>11:04 AM</t>
+  </si>
+  <si>
+    <t>Correo</t>
+  </si>
+  <si>
+    <t>01:12 PM</t>
+  </si>
+  <si>
+    <t>01:16 PM</t>
+  </si>
+  <si>
+    <t>DETALLE DE PRUEBAS</t>
+  </si>
+  <si>
+    <t>PRUEBAS DE PREPAGO CON SALDO</t>
+  </si>
+  <si>
+    <t>PRUEBAS DE PREPAGO SIN SALDO</t>
+  </si>
+  <si>
+    <t>IMÁGENES</t>
+  </si>
+  <si>
+    <t>Pruebas de MMS</t>
+  </si>
+  <si>
+    <t>Pruebas de Internet</t>
+  </si>
+  <si>
+    <t># Prueba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envío </t>
+  </si>
+  <si>
+    <t>Recepción</t>
+  </si>
+  <si>
+    <t>Acceso</t>
+  </si>
+  <si>
+    <t>11:41 AM</t>
+  </si>
+  <si>
+    <t>11:42 AM</t>
+  </si>
+  <si>
+    <t>11:43 AM</t>
+  </si>
+  <si>
+    <t>11:44 AM</t>
+  </si>
+  <si>
+    <t>11:45 AM</t>
+  </si>
+  <si>
+    <t>11:46 AM</t>
+  </si>
+  <si>
+    <t>11:47 AM</t>
+  </si>
+  <si>
+    <t>11:48 AM</t>
+  </si>
+  <si>
+    <t>Pruebas de Youtube</t>
+  </si>
+  <si>
+    <t>Pruebas de twitter</t>
+  </si>
+  <si>
+    <t>11:12 AM</t>
+  </si>
+  <si>
+    <t>11:13 AM</t>
+  </si>
+  <si>
+    <t>11:14 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pruebas de facebook </t>
+  </si>
+  <si>
+    <t>Pruebas de correo</t>
+  </si>
+  <si>
+    <t>01:23 PM</t>
+  </si>
+  <si>
+    <t>01:24 PM</t>
+  </si>
+  <si>
+    <t>01:25 PM</t>
+  </si>
+  <si>
+    <t>11:01 AM</t>
+  </si>
+  <si>
+    <t>11:02 AM</t>
+  </si>
+  <si>
+    <t>11:03 AM</t>
+  </si>
+  <si>
+    <t>01:13 PM</t>
+  </si>
+  <si>
+    <t>01:14 PM</t>
+  </si>
+  <si>
+    <t>01:15 PM</t>
+  </si>
+  <si>
     <t>Línea Pospago: 5523427847</t>
   </si>
   <si>
-    <t>Modelo: V2515</t>
-  </si>
-  <si>
     <t>Línea Prepago con saldo: 5549222015</t>
   </si>
   <si>
-    <t>Fecha de pruebas: 25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Línea Prepago sin saldo: 5549222015 </t>
-  </si>
-  <si>
-    <t>Prueba</t>
-  </si>
-  <si>
-    <t>PRUEBAS DE POS PAGO</t>
-  </si>
-  <si>
-    <t>PRUEBAS DE PCS</t>
-  </si>
-  <si>
-    <t>PRUEBAS DE PSS</t>
-  </si>
-  <si>
-    <t>Hora de inicio</t>
-  </si>
-  <si>
-    <t>Hora de término</t>
-  </si>
-  <si>
-    <t>MMS</t>
+    <t>P</t>
   </si>
   <si>
     <t>01:18 PM</t>
@@ -80,69 +233,27 @@
     <t>11:51 AM</t>
   </si>
   <si>
-    <t>Internet</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>Twitter</t>
-  </si>
-  <si>
     <t>05:37 PM</t>
   </si>
   <si>
     <t>05:38 PM</t>
   </si>
   <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>Correo</t>
+    <t>10:37 AM</t>
+  </si>
+  <si>
+    <t>10:41 AM</t>
+  </si>
+  <si>
+    <t>10:49 AM</t>
+  </si>
+  <si>
+    <t>10:53 AM</t>
   </si>
   <si>
     <t>DETALLE DE LAS PRUEBAS</t>
   </si>
   <si>
-    <t>PRUEBAS DE PREPAGO CON SALDO</t>
-  </si>
-  <si>
-    <t>PRUEBAS DE PREPAGO SIN SALDO</t>
-  </si>
-  <si>
-    <t>IMÁGENES</t>
-  </si>
-  <si>
-    <t>Pruebas de MMS</t>
-  </si>
-  <si>
-    <t>Pruebas de Internet</t>
-  </si>
-  <si>
-    <t># Prueba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Envío </t>
-  </si>
-  <si>
-    <t>Recepción</t>
-  </si>
-  <si>
-    <t>Acceso</t>
-  </si>
-  <si>
-    <t>Pruebas de Youtube</t>
-  </si>
-  <si>
-    <t>Pruebas de twitter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de facebook </t>
-  </si>
-  <si>
-    <t>Pruebas de correo</t>
-  </si>
-  <si>
     <t>05:20 PM</t>
   </si>
   <si>
@@ -152,6 +263,24 @@
     <t>05:22 PM</t>
   </si>
   <si>
+    <t>10:38 AM</t>
+  </si>
+  <si>
+    <t>10:39 AM</t>
+  </si>
+  <si>
+    <t>10:40 AM</t>
+  </si>
+  <si>
+    <t>10:50 AM</t>
+  </si>
+  <si>
+    <t>10:51 AM</t>
+  </si>
+  <si>
+    <t>10:52 AM</t>
+  </si>
+  <si>
     <t>Throughput DL/UL Postpago 3G</t>
   </si>
   <si>
@@ -168,78 +297,6 @@
   </si>
   <si>
     <t>Imagen</t>
-  </si>
-  <si>
-    <t>Línea Pospago: 5530760949</t>
-  </si>
-  <si>
-    <t>Línea Prepago con saldo: 5545367869</t>
-  </si>
-  <si>
-    <t>Fecha de pruebas: 26/05/2026</t>
-  </si>
-  <si>
-    <t>Línea Prepago sin saldo: 5545367869</t>
-  </si>
-  <si>
-    <t>05:49 PM</t>
-  </si>
-  <si>
-    <t>11:11 AM</t>
-  </si>
-  <si>
-    <t>11:15 AM</t>
-  </si>
-  <si>
-    <t>12:08 PM</t>
-  </si>
-  <si>
-    <t>12:12 PM</t>
-  </si>
-  <si>
-    <t>DETALLE DE PRUEBAS</t>
-  </si>
-  <si>
-    <t>11:41 AM</t>
-  </si>
-  <si>
-    <t>11:42 AM</t>
-  </si>
-  <si>
-    <t>11:43 AM</t>
-  </si>
-  <si>
-    <t>11:44 AM</t>
-  </si>
-  <si>
-    <t>11:45 AM</t>
-  </si>
-  <si>
-    <t>11:46 AM</t>
-  </si>
-  <si>
-    <t>11:47 AM</t>
-  </si>
-  <si>
-    <t>11:48 AM</t>
-  </si>
-  <si>
-    <t>11:12 AM</t>
-  </si>
-  <si>
-    <t>11:13 AM</t>
-  </si>
-  <si>
-    <t>11:14 AM</t>
-  </si>
-  <si>
-    <t>12:09 PM</t>
-  </si>
-  <si>
-    <t>12:10 PM</t>
-  </si>
-  <si>
-    <t>12:11 PM</t>
   </si>
   <si>
     <t>Throughput DL/UL Postpago 4G</t>
@@ -1410,6 +1467,10 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1430,7 +1491,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1457,16 +1517,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1489,12 +1552,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1548,9 +1605,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>248818</xdr:colOff>
+      <xdr:colOff>251358</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>97400</xdr:rowOff>
+      <xdr:rowOff>99940</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1656,9 +1713,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>975621</xdr:colOff>
+      <xdr:colOff>973081</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>97420</xdr:rowOff>
+      <xdr:rowOff>101230</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2060,47 +2117,47 @@
       <c r="B9" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:8" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="74"/>
-      <c r="F14" s="94" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="76"/>
+      <c r="F14" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
     </row>
     <row r="15" spans="2:8" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="74"/>
-      <c r="F15" s="94" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="76"/>
+      <c r="F15" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
     </row>
     <row r="16" spans="2:8" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="72" t="s">
+      <c r="B16" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="74"/>
-      <c r="F16" s="94" t="s">
+      <c r="C16" s="75"/>
+      <c r="D16" s="76"/>
+      <c r="F16" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
     </row>
     <row r="17" spans="1:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2108,28 +2165,31 @@
       <c r="E18" s="33"/>
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
+      <c r="I18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="19" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
-      <c r="B19" s="92" t="s">
+      <c r="B19" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="99" t="s">
+      <c r="C19" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="70"/>
-      <c r="E19" s="88" t="s">
+      <c r="D19" s="72"/>
+      <c r="E19" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="89"/>
-      <c r="G19" s="90" t="s">
+      <c r="F19" s="90"/>
+      <c r="G19" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="91"/>
+      <c r="H19" s="92"/>
     </row>
     <row r="20" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
-      <c r="B20" s="93"/>
+      <c r="B20" s="94"/>
       <c r="C20" s="21" t="s">
         <v>11</v>
       </c>
@@ -2154,10 +2214,10 @@
         <v>13</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="E21" s="42">
         <v>0.59375</v>
@@ -2166,15 +2226,15 @@
         <v>0.6069444444444444</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="45" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C22" s="46">
         <v>0.58194444444444449</v>
@@ -2197,7 +2257,7 @@
     </row>
     <row r="23" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="43">
         <v>0.59375</v>
@@ -2220,7 +2280,7 @@
     </row>
     <row r="24" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" s="46">
         <v>0.60486111111111107</v>
@@ -2235,15 +2295,15 @@
         <v>0.64861111111111114</v>
       </c>
       <c r="G24" s="62" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="43">
         <v>0.62361111111111112</v>
@@ -2257,17 +2317,17 @@
       <c r="F25" s="40">
         <v>0.67222222222222228</v>
       </c>
-      <c r="G25" s="41">
-        <v>0.78680555555555554</v>
-      </c>
-      <c r="H25" s="41">
-        <v>0.7895833333333333</v>
+      <c r="G25" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>72</v>
       </c>
       <c r="K25" s="67"/>
     </row>
     <row r="26" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" s="49">
         <v>0.64236111111111116</v>
@@ -2281,111 +2341,109 @@
       <c r="F26" s="50">
         <v>0.69027777777777777</v>
       </c>
-      <c r="G26" s="63">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="H26" s="63">
-        <v>0.79791666666666672</v>
+      <c r="G26" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="H26" s="63" t="s">
+        <v>74</v>
       </c>
       <c r="K26" s="67"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="B28" s="95" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="81"/>
+      <c r="B28" s="96" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="70"/>
     </row>
     <row r="31" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="32" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="70"/>
-      <c r="J32" s="86" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" s="87"/>
-      <c r="L32" s="87"/>
-      <c r="S32" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="T32" s="76"/>
-      <c r="V32" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="W32" s="76"/>
-      <c r="X32" s="76"/>
+      <c r="C32" s="72"/>
+      <c r="J32" s="87" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="88"/>
+      <c r="L32" s="88"/>
+      <c r="S32" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="T32" s="78"/>
+      <c r="V32" s="77" t="s">
+        <v>31</v>
+      </c>
+      <c r="W32" s="78"/>
+      <c r="X32" s="78"/>
     </row>
     <row r="33" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="70"/>
-      <c r="F34" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="G34" s="70"/>
-      <c r="J34" s="98" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="87"/>
-      <c r="L34" s="87"/>
-      <c r="N34" s="98" t="s">
-        <v>30</v>
-      </c>
-      <c r="O34" s="87"/>
-      <c r="S34" s="75" t="s">
-        <v>29</v>
-      </c>
-      <c r="T34" s="76"/>
-      <c r="V34" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W34" s="78"/>
-      <c r="X34" s="79"/>
+      <c r="B34" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="73"/>
+      <c r="D34" s="72"/>
+      <c r="F34" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="72"/>
+      <c r="J34" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" s="88"/>
+      <c r="L34" s="88"/>
+      <c r="N34" s="101" t="s">
+        <v>33</v>
+      </c>
+      <c r="O34" s="88"/>
+      <c r="S34" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="T34" s="78"/>
+      <c r="V34" s="79"/>
+      <c r="W34" s="80"/>
+      <c r="X34" s="81"/>
     </row>
     <row r="35" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G35" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J35" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J35" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="K35" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L35" s="55" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O35" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="S35" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="S35" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="T35" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="V35" s="80"/>
-      <c r="W35" s="81"/>
-      <c r="X35" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="V35" s="82"/>
+      <c r="W35" s="70"/>
+      <c r="X35" s="83"/>
     </row>
     <row r="36" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="31"/>
@@ -2393,10 +2451,10 @@
         <v>1</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="E36" s="31"/>
       <c r="F36" s="1">
@@ -2429,9 +2487,9 @@
       <c r="T36" s="51">
         <v>0.76249999999999996</v>
       </c>
-      <c r="V36" s="80"/>
-      <c r="W36" s="81"/>
-      <c r="X36" s="82"/>
+      <c r="V36" s="82"/>
+      <c r="W36" s="70"/>
+      <c r="X36" s="83"/>
     </row>
     <row r="37" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="15">
@@ -2470,9 +2528,9 @@
       <c r="T37" s="52">
         <v>0.7631944444444444</v>
       </c>
-      <c r="V37" s="80"/>
-      <c r="W37" s="81"/>
-      <c r="X37" s="82"/>
+      <c r="V37" s="82"/>
+      <c r="W37" s="70"/>
+      <c r="X37" s="83"/>
     </row>
     <row r="38" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="1">
@@ -2511,9 +2569,9 @@
       <c r="T38" s="51">
         <v>0.76388888888888884</v>
       </c>
-      <c r="V38" s="80"/>
-      <c r="W38" s="81"/>
-      <c r="X38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="70"/>
+      <c r="X38" s="83"/>
     </row>
     <row r="39" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="15">
@@ -2552,9 +2610,9 @@
       <c r="T39" s="52">
         <v>0.76458333333333328</v>
       </c>
-      <c r="V39" s="80"/>
-      <c r="W39" s="81"/>
-      <c r="X39" s="82"/>
+      <c r="V39" s="82"/>
+      <c r="W39" s="70"/>
+      <c r="X39" s="83"/>
     </row>
     <row r="40" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="1">
@@ -2593,9 +2651,9 @@
       <c r="T40" s="51">
         <v>0.76527777777777772</v>
       </c>
-      <c r="V40" s="80"/>
-      <c r="W40" s="81"/>
-      <c r="X40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="70"/>
+      <c r="X40" s="83"/>
     </row>
     <row r="41" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="15">
@@ -2628,9 +2686,9 @@
       <c r="O41" s="52">
         <v>0.61319444444444449</v>
       </c>
-      <c r="V41" s="80"/>
-      <c r="W41" s="81"/>
-      <c r="X41" s="82"/>
+      <c r="V41" s="82"/>
+      <c r="W41" s="70"/>
+      <c r="X41" s="83"/>
     </row>
     <row r="42" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="1">
@@ -2663,9 +2721,9 @@
       <c r="O42" s="51">
         <v>0.61388888888888893</v>
       </c>
-      <c r="V42" s="80"/>
-      <c r="W42" s="81"/>
-      <c r="X42" s="82"/>
+      <c r="V42" s="82"/>
+      <c r="W42" s="70"/>
+      <c r="X42" s="83"/>
     </row>
     <row r="43" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="15">
@@ -2698,9 +2756,9 @@
       <c r="O43" s="53">
         <v>0.61458333333333337</v>
       </c>
-      <c r="V43" s="80"/>
-      <c r="W43" s="81"/>
-      <c r="X43" s="82"/>
+      <c r="V43" s="82"/>
+      <c r="W43" s="70"/>
+      <c r="X43" s="83"/>
     </row>
     <row r="44" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B44" s="1">
@@ -2734,9 +2792,9 @@
         <v>0.61527777777777781</v>
       </c>
       <c r="R44" s="31"/>
-      <c r="V44" s="80"/>
-      <c r="W44" s="81"/>
-      <c r="X44" s="82"/>
+      <c r="V44" s="82"/>
+      <c r="W44" s="70"/>
+      <c r="X44" s="83"/>
     </row>
     <row r="45" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="15">
@@ -2773,74 +2831,74 @@
         <v>0.61597222222222225</v>
       </c>
       <c r="P45" s="31"/>
-      <c r="V45" s="80"/>
-      <c r="W45" s="81"/>
-      <c r="X45" s="82"/>
+      <c r="V45" s="82"/>
+      <c r="W45" s="70"/>
+      <c r="X45" s="83"/>
     </row>
     <row r="46" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D46" s="31"/>
       <c r="L46" s="31"/>
-      <c r="V46" s="80"/>
-      <c r="W46" s="81"/>
-      <c r="X46" s="82"/>
+      <c r="V46" s="82"/>
+      <c r="W46" s="70"/>
+      <c r="X46" s="83"/>
     </row>
     <row r="47" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="69" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="70"/>
-      <c r="F47" s="69" t="s">
-        <v>36</v>
-      </c>
-      <c r="G47" s="71"/>
-      <c r="H47" s="70"/>
-      <c r="J47" s="86" t="s">
-        <v>35</v>
-      </c>
-      <c r="K47" s="87"/>
-      <c r="N47" s="86" t="s">
-        <v>36</v>
-      </c>
-      <c r="O47" s="87"/>
-      <c r="P47" s="87"/>
-      <c r="V47" s="80"/>
-      <c r="W47" s="81"/>
-      <c r="X47" s="82"/>
+      <c r="B47" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="72"/>
+      <c r="F47" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="G47" s="73"/>
+      <c r="H47" s="72"/>
+      <c r="J47" s="87" t="s">
+        <v>46</v>
+      </c>
+      <c r="K47" s="88"/>
+      <c r="N47" s="87" t="s">
+        <v>47</v>
+      </c>
+      <c r="O47" s="88"/>
+      <c r="P47" s="88"/>
+      <c r="V47" s="82"/>
+      <c r="W47" s="70"/>
+      <c r="X47" s="83"/>
     </row>
     <row r="48" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C48" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F48" s="14" t="s">
-        <v>31</v>
-      </c>
       <c r="G48" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J48" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K48" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="N48" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="O48" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P48" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="V48" s="80"/>
-      <c r="W48" s="81"/>
-      <c r="X48" s="82"/>
+        <v>36</v>
+      </c>
+      <c r="V48" s="82"/>
+      <c r="W48" s="70"/>
+      <c r="X48" s="83"/>
     </row>
     <row r="49" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="31"/>
@@ -2877,9 +2935,9 @@
       <c r="P49" s="51">
         <v>0.63611111111111107</v>
       </c>
-      <c r="V49" s="80"/>
-      <c r="W49" s="81"/>
-      <c r="X49" s="82"/>
+      <c r="V49" s="82"/>
+      <c r="W49" s="70"/>
+      <c r="X49" s="83"/>
     </row>
     <row r="50" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="15">
@@ -2912,9 +2970,9 @@
       <c r="P50" s="53">
         <v>0.63749999999999996</v>
       </c>
-      <c r="V50" s="80"/>
-      <c r="W50" s="81"/>
-      <c r="X50" s="82"/>
+      <c r="V50" s="82"/>
+      <c r="W50" s="70"/>
+      <c r="X50" s="83"/>
     </row>
     <row r="51" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="1">
@@ -2947,9 +3005,9 @@
       <c r="P51" s="51">
         <v>0.63888888888888884</v>
       </c>
-      <c r="V51" s="80"/>
-      <c r="W51" s="81"/>
-      <c r="X51" s="82"/>
+      <c r="V51" s="82"/>
+      <c r="W51" s="70"/>
+      <c r="X51" s="83"/>
     </row>
     <row r="52" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="15">
@@ -2983,9 +3041,9 @@
         <v>0.64027777777777772</v>
       </c>
       <c r="R52" s="31"/>
-      <c r="V52" s="83"/>
-      <c r="W52" s="84"/>
-      <c r="X52" s="85"/>
+      <c r="V52" s="84"/>
+      <c r="W52" s="85"/>
+      <c r="X52" s="86"/>
     </row>
     <row r="53" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="1">
@@ -3050,15 +3108,13 @@
       <c r="P54" s="52">
         <v>0.6430555555555556</v>
       </c>
-      <c r="S54" s="96" t="s">
-        <v>30</v>
-      </c>
-      <c r="T54" s="76"/>
-      <c r="V54" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W54" s="78"/>
-      <c r="X54" s="79"/>
+      <c r="S54" s="99" t="s">
+        <v>33</v>
+      </c>
+      <c r="T54" s="78"/>
+      <c r="V54" s="79"/>
+      <c r="W54" s="80"/>
+      <c r="X54" s="81"/>
     </row>
     <row r="55" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="1">
@@ -3092,14 +3148,14 @@
         <v>0.64444444444444449</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T55" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="V55" s="80"/>
-      <c r="W55" s="81"/>
-      <c r="X55" s="82"/>
+        <v>37</v>
+      </c>
+      <c r="V55" s="82"/>
+      <c r="W55" s="70"/>
+      <c r="X55" s="83"/>
     </row>
     <row r="56" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="15">
@@ -3138,9 +3194,9 @@
       <c r="T56" s="51">
         <v>0.77013888888888893</v>
       </c>
-      <c r="V56" s="80"/>
-      <c r="W56" s="81"/>
-      <c r="X56" s="82"/>
+      <c r="V56" s="82"/>
+      <c r="W56" s="70"/>
+      <c r="X56" s="83"/>
     </row>
     <row r="57" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="1">
@@ -3179,9 +3235,9 @@
       <c r="T57" s="52">
         <v>0.77083333333333337</v>
       </c>
-      <c r="V57" s="80"/>
-      <c r="W57" s="81"/>
-      <c r="X57" s="82"/>
+      <c r="V57" s="82"/>
+      <c r="W57" s="70"/>
+      <c r="X57" s="83"/>
     </row>
     <row r="58" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="15">
@@ -3224,9 +3280,9 @@
       <c r="T58" s="51">
         <v>0.77152777777777781</v>
       </c>
-      <c r="V58" s="80"/>
-      <c r="W58" s="81"/>
-      <c r="X58" s="82"/>
+      <c r="V58" s="82"/>
+      <c r="W58" s="70"/>
+      <c r="X58" s="83"/>
     </row>
     <row r="59" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S59" s="54">
@@ -3235,31 +3291,31 @@
       <c r="T59" s="52">
         <v>0.77222222222222225</v>
       </c>
-      <c r="V59" s="80"/>
-      <c r="W59" s="81"/>
-      <c r="X59" s="82"/>
+      <c r="V59" s="82"/>
+      <c r="W59" s="70"/>
+      <c r="X59" s="83"/>
     </row>
     <row r="60" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="71"/>
-      <c r="D60" s="70"/>
-      <c r="F60" s="69" t="s">
-        <v>38</v>
-      </c>
-      <c r="G60" s="71"/>
-      <c r="H60" s="70"/>
-      <c r="J60" s="86" t="s">
-        <v>37</v>
-      </c>
-      <c r="K60" s="87"/>
-      <c r="L60" s="87"/>
-      <c r="N60" s="86" t="s">
-        <v>38</v>
-      </c>
-      <c r="O60" s="87"/>
-      <c r="P60" s="87"/>
+      <c r="B60" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60" s="73"/>
+      <c r="D60" s="72"/>
+      <c r="F60" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="G60" s="73"/>
+      <c r="H60" s="72"/>
+      <c r="J60" s="87" t="s">
+        <v>51</v>
+      </c>
+      <c r="K60" s="88"/>
+      <c r="L60" s="88"/>
+      <c r="N60" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="O60" s="88"/>
+      <c r="P60" s="88"/>
       <c r="R60" s="31"/>
       <c r="S60" s="1">
         <v>5</v>
@@ -3267,51 +3323,51 @@
       <c r="T60" s="51">
         <v>0.7729166666666667</v>
       </c>
-      <c r="V60" s="80"/>
-      <c r="W60" s="81"/>
-      <c r="X60" s="82"/>
+      <c r="V60" s="82"/>
+      <c r="W60" s="70"/>
+      <c r="X60" s="83"/>
     </row>
     <row r="61" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J61" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K61" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L61" s="55" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M61" s="31"/>
       <c r="N61" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O61" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P61" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="V61" s="80"/>
-      <c r="W61" s="81"/>
-      <c r="X61" s="82"/>
+        <v>36</v>
+      </c>
+      <c r="V61" s="82"/>
+      <c r="W61" s="70"/>
+      <c r="X61" s="83"/>
     </row>
     <row r="62" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="31"/>
@@ -3353,9 +3409,9 @@
       <c r="P62" s="51">
         <v>0.67777777777777781</v>
       </c>
-      <c r="V62" s="80"/>
-      <c r="W62" s="81"/>
-      <c r="X62" s="82"/>
+      <c r="V62" s="82"/>
+      <c r="W62" s="70"/>
+      <c r="X62" s="83"/>
     </row>
     <row r="63" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="54">
@@ -3394,9 +3450,9 @@
       <c r="P63" s="53">
         <v>0.6791666666666667</v>
       </c>
-      <c r="V63" s="80"/>
-      <c r="W63" s="81"/>
-      <c r="X63" s="82"/>
+      <c r="V63" s="82"/>
+      <c r="W63" s="70"/>
+      <c r="X63" s="83"/>
     </row>
     <row r="64" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="1">
@@ -3436,9 +3492,9 @@
         <v>0.68055555555555558</v>
       </c>
       <c r="U64" s="31"/>
-      <c r="V64" s="80"/>
-      <c r="W64" s="81"/>
-      <c r="X64" s="82"/>
+      <c r="V64" s="82"/>
+      <c r="W64" s="70"/>
+      <c r="X64" s="83"/>
     </row>
     <row r="65" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="54">
@@ -3477,9 +3533,9 @@
       <c r="P65" s="52">
         <v>0.68194444444444446</v>
       </c>
-      <c r="V65" s="80"/>
-      <c r="W65" s="81"/>
-      <c r="X65" s="82"/>
+      <c r="V65" s="82"/>
+      <c r="W65" s="70"/>
+      <c r="X65" s="83"/>
     </row>
     <row r="66" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B66" s="1">
@@ -3518,9 +3574,9 @@
       <c r="P66" s="51">
         <v>0.68333333333333335</v>
       </c>
-      <c r="V66" s="80"/>
-      <c r="W66" s="81"/>
-      <c r="X66" s="82"/>
+      <c r="V66" s="82"/>
+      <c r="W66" s="70"/>
+      <c r="X66" s="83"/>
     </row>
     <row r="67" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="54">
@@ -3559,9 +3615,9 @@
       <c r="P67" s="52">
         <v>0.68472222222222223</v>
       </c>
-      <c r="V67" s="80"/>
-      <c r="W67" s="81"/>
-      <c r="X67" s="82"/>
+      <c r="V67" s="82"/>
+      <c r="W67" s="70"/>
+      <c r="X67" s="83"/>
     </row>
     <row r="68" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B68" s="1">
@@ -3601,9 +3657,9 @@
         <v>0.68611111111111112</v>
       </c>
       <c r="R68" s="31"/>
-      <c r="V68" s="80"/>
-      <c r="W68" s="81"/>
-      <c r="X68" s="82"/>
+      <c r="V68" s="82"/>
+      <c r="W68" s="70"/>
+      <c r="X68" s="83"/>
     </row>
     <row r="69" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B69" s="54">
@@ -3642,9 +3698,9 @@
       <c r="P69" s="53">
         <v>0.6875</v>
       </c>
-      <c r="V69" s="80"/>
-      <c r="W69" s="81"/>
-      <c r="X69" s="82"/>
+      <c r="V69" s="82"/>
+      <c r="W69" s="70"/>
+      <c r="X69" s="83"/>
     </row>
     <row r="70" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B70" s="1">
@@ -3683,9 +3739,9 @@
       <c r="P70" s="51">
         <v>0.68888888888888888</v>
       </c>
-      <c r="V70" s="80"/>
-      <c r="W70" s="81"/>
-      <c r="X70" s="82"/>
+      <c r="V70" s="82"/>
+      <c r="W70" s="70"/>
+      <c r="X70" s="83"/>
     </row>
     <row r="71" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="54">
@@ -3725,9 +3781,9 @@
       <c r="P71" s="52">
         <v>0.69027777777777777</v>
       </c>
-      <c r="V71" s="80"/>
-      <c r="W71" s="81"/>
-      <c r="X71" s="82"/>
+      <c r="V71" s="82"/>
+      <c r="W71" s="70"/>
+      <c r="X71" s="83"/>
     </row>
     <row r="72" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D72" s="31"/>
@@ -3735,32 +3791,30 @@
       <c r="L72" s="31"/>
       <c r="P72" s="31"/>
       <c r="U72" s="31"/>
-      <c r="V72" s="83"/>
-      <c r="W72" s="84"/>
-      <c r="X72" s="85"/>
+      <c r="V72" s="84"/>
+      <c r="W72" s="85"/>
+      <c r="X72" s="86"/>
     </row>
     <row r="73" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="S74" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="T74" s="76"/>
-      <c r="V74" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W74" s="78"/>
-      <c r="X74" s="79"/>
+      <c r="S74" s="99" t="s">
+        <v>46</v>
+      </c>
+      <c r="T74" s="78"/>
+      <c r="V74" s="79"/>
+      <c r="W74" s="80"/>
+      <c r="X74" s="81"/>
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.35">
       <c r="S75" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T75" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="V75" s="80"/>
-      <c r="W75" s="81"/>
-      <c r="X75" s="82"/>
+        <v>37</v>
+      </c>
+      <c r="V75" s="82"/>
+      <c r="W75" s="70"/>
+      <c r="X75" s="83"/>
     </row>
     <row r="76" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="R76" s="31"/>
@@ -3770,9 +3824,9 @@
       <c r="T76" s="51">
         <v>0.77847222222222223</v>
       </c>
-      <c r="V76" s="80"/>
-      <c r="W76" s="81"/>
-      <c r="X76" s="82"/>
+      <c r="V76" s="82"/>
+      <c r="W76" s="70"/>
+      <c r="X76" s="83"/>
     </row>
     <row r="77" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S77" s="54">
@@ -3781,9 +3835,9 @@
       <c r="T77" s="53">
         <v>0.77916666666666667</v>
       </c>
-      <c r="V77" s="80"/>
-      <c r="W77" s="81"/>
-      <c r="X77" s="82"/>
+      <c r="V77" s="82"/>
+      <c r="W77" s="70"/>
+      <c r="X77" s="83"/>
     </row>
     <row r="78" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S78" s="1">
@@ -3792,9 +3846,9 @@
       <c r="T78" s="51">
         <v>0.77986111111111112</v>
       </c>
-      <c r="V78" s="80"/>
-      <c r="W78" s="81"/>
-      <c r="X78" s="82"/>
+      <c r="V78" s="82"/>
+      <c r="W78" s="70"/>
+      <c r="X78" s="83"/>
     </row>
     <row r="79" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S79" s="54">
@@ -3803,9 +3857,9 @@
       <c r="T79" s="53">
         <v>0.78055555555555556</v>
       </c>
-      <c r="V79" s="80"/>
-      <c r="W79" s="81"/>
-      <c r="X79" s="82"/>
+      <c r="V79" s="82"/>
+      <c r="W79" s="70"/>
+      <c r="X79" s="83"/>
     </row>
     <row r="80" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S80" s="1">
@@ -3815,486 +3869,480 @@
         <v>0.78125</v>
       </c>
       <c r="U80" s="31"/>
-      <c r="V80" s="80"/>
-      <c r="W80" s="81"/>
-      <c r="X80" s="82"/>
+      <c r="V80" s="82"/>
+      <c r="W80" s="70"/>
+      <c r="X80" s="83"/>
     </row>
     <row r="81" spans="19:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="V81" s="80"/>
-      <c r="W81" s="81"/>
-      <c r="X81" s="82"/>
+      <c r="V81" s="82"/>
+      <c r="W81" s="70"/>
+      <c r="X81" s="83"/>
     </row>
     <row r="82" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V82" s="80"/>
-      <c r="W82" s="81"/>
-      <c r="X82" s="82"/>
+      <c r="V82" s="82"/>
+      <c r="W82" s="70"/>
+      <c r="X82" s="83"/>
     </row>
     <row r="83" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V83" s="80"/>
-      <c r="W83" s="81"/>
-      <c r="X83" s="82"/>
+      <c r="V83" s="82"/>
+      <c r="W83" s="70"/>
+      <c r="X83" s="83"/>
     </row>
     <row r="84" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V84" s="80"/>
-      <c r="W84" s="81"/>
-      <c r="X84" s="82"/>
+      <c r="V84" s="82"/>
+      <c r="W84" s="70"/>
+      <c r="X84" s="83"/>
     </row>
     <row r="85" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V85" s="80"/>
-      <c r="W85" s="81"/>
-      <c r="X85" s="82"/>
+      <c r="V85" s="82"/>
+      <c r="W85" s="70"/>
+      <c r="X85" s="83"/>
     </row>
     <row r="86" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V86" s="80"/>
-      <c r="W86" s="81"/>
-      <c r="X86" s="82"/>
+      <c r="V86" s="82"/>
+      <c r="W86" s="70"/>
+      <c r="X86" s="83"/>
     </row>
     <row r="87" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V87" s="80"/>
-      <c r="W87" s="81"/>
-      <c r="X87" s="82"/>
+      <c r="V87" s="82"/>
+      <c r="W87" s="70"/>
+      <c r="X87" s="83"/>
     </row>
     <row r="88" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V88" s="80"/>
-      <c r="W88" s="81"/>
-      <c r="X88" s="82"/>
+      <c r="V88" s="82"/>
+      <c r="W88" s="70"/>
+      <c r="X88" s="83"/>
     </row>
     <row r="89" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V89" s="80"/>
-      <c r="W89" s="81"/>
-      <c r="X89" s="82"/>
+      <c r="V89" s="82"/>
+      <c r="W89" s="70"/>
+      <c r="X89" s="83"/>
     </row>
     <row r="90" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V90" s="80"/>
-      <c r="W90" s="81"/>
-      <c r="X90" s="82"/>
+      <c r="V90" s="82"/>
+      <c r="W90" s="70"/>
+      <c r="X90" s="83"/>
     </row>
     <row r="91" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V91" s="80"/>
-      <c r="W91" s="81"/>
-      <c r="X91" s="82"/>
+      <c r="V91" s="82"/>
+      <c r="W91" s="70"/>
+      <c r="X91" s="83"/>
     </row>
     <row r="92" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="V92" s="83"/>
-      <c r="W92" s="84"/>
-      <c r="X92" s="85"/>
+      <c r="V92" s="84"/>
+      <c r="W92" s="85"/>
+      <c r="X92" s="86"/>
     </row>
     <row r="93" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="S94" s="96" t="s">
-        <v>36</v>
-      </c>
-      <c r="T94" s="76"/>
-      <c r="V94" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W94" s="78"/>
-      <c r="X94" s="79"/>
+      <c r="S94" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="T94" s="78"/>
+      <c r="V94" s="79"/>
+      <c r="W94" s="80"/>
+      <c r="X94" s="81"/>
     </row>
     <row r="95" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S95" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T95" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="V95" s="80"/>
-      <c r="W95" s="81"/>
-      <c r="X95" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="V95" s="82"/>
+      <c r="W95" s="70"/>
+      <c r="X95" s="83"/>
     </row>
     <row r="96" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S96" s="1">
         <v>1</v>
       </c>
       <c r="T96" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="V96" s="80"/>
-      <c r="W96" s="81"/>
-      <c r="X96" s="82"/>
+        <v>69</v>
+      </c>
+      <c r="V96" s="82"/>
+      <c r="W96" s="70"/>
+      <c r="X96" s="83"/>
     </row>
     <row r="97" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S97" s="54">
         <v>2</v>
       </c>
       <c r="T97" s="62" t="s">
-        <v>22</v>
-      </c>
-      <c r="V97" s="80"/>
-      <c r="W97" s="81"/>
-      <c r="X97" s="82"/>
+        <v>70</v>
+      </c>
+      <c r="V97" s="82"/>
+      <c r="W97" s="70"/>
+      <c r="X97" s="83"/>
     </row>
     <row r="98" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S98" s="1">
         <v>3</v>
       </c>
       <c r="T98" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="V98" s="80"/>
-      <c r="W98" s="81"/>
-      <c r="X98" s="82"/>
+        <v>76</v>
+      </c>
+      <c r="V98" s="82"/>
+      <c r="W98" s="70"/>
+      <c r="X98" s="83"/>
     </row>
     <row r="99" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S99" s="54">
         <v>4</v>
       </c>
       <c r="T99" s="62" t="s">
-        <v>40</v>
-      </c>
-      <c r="V99" s="80"/>
-      <c r="W99" s="81"/>
-      <c r="X99" s="82"/>
+        <v>77</v>
+      </c>
+      <c r="V99" s="82"/>
+      <c r="W99" s="70"/>
+      <c r="X99" s="83"/>
     </row>
     <row r="100" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S100" s="1">
         <v>5</v>
       </c>
       <c r="T100" s="41" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="U100" s="31"/>
-      <c r="V100" s="80"/>
-      <c r="W100" s="81"/>
-      <c r="X100" s="82"/>
+      <c r="V100" s="82"/>
+      <c r="W100" s="70"/>
+      <c r="X100" s="83"/>
     </row>
     <row r="101" spans="19:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="V101" s="80"/>
-      <c r="W101" s="81"/>
-      <c r="X101" s="82"/>
+      <c r="V101" s="82"/>
+      <c r="W101" s="70"/>
+      <c r="X101" s="83"/>
     </row>
     <row r="102" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V102" s="80"/>
-      <c r="W102" s="81"/>
-      <c r="X102" s="82"/>
+      <c r="V102" s="82"/>
+      <c r="W102" s="70"/>
+      <c r="X102" s="83"/>
     </row>
     <row r="103" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V103" s="80"/>
-      <c r="W103" s="81"/>
-      <c r="X103" s="82"/>
+      <c r="V103" s="82"/>
+      <c r="W103" s="70"/>
+      <c r="X103" s="83"/>
     </row>
     <row r="104" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V104" s="80"/>
-      <c r="W104" s="81"/>
-      <c r="X104" s="82"/>
+      <c r="V104" s="82"/>
+      <c r="W104" s="70"/>
+      <c r="X104" s="83"/>
     </row>
     <row r="105" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V105" s="80"/>
-      <c r="W105" s="81"/>
-      <c r="X105" s="82"/>
+      <c r="V105" s="82"/>
+      <c r="W105" s="70"/>
+      <c r="X105" s="83"/>
     </row>
     <row r="106" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V106" s="80"/>
-      <c r="W106" s="81"/>
-      <c r="X106" s="82"/>
+      <c r="V106" s="82"/>
+      <c r="W106" s="70"/>
+      <c r="X106" s="83"/>
     </row>
     <row r="107" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V107" s="80"/>
-      <c r="W107" s="81"/>
-      <c r="X107" s="82"/>
+      <c r="V107" s="82"/>
+      <c r="W107" s="70"/>
+      <c r="X107" s="83"/>
     </row>
     <row r="108" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V108" s="80"/>
-      <c r="W108" s="81"/>
-      <c r="X108" s="82"/>
+      <c r="V108" s="82"/>
+      <c r="W108" s="70"/>
+      <c r="X108" s="83"/>
     </row>
     <row r="109" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V109" s="80"/>
-      <c r="W109" s="81"/>
-      <c r="X109" s="82"/>
+      <c r="V109" s="82"/>
+      <c r="W109" s="70"/>
+      <c r="X109" s="83"/>
     </row>
     <row r="110" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V110" s="80"/>
-      <c r="W110" s="81"/>
-      <c r="X110" s="82"/>
+      <c r="V110" s="82"/>
+      <c r="W110" s="70"/>
+      <c r="X110" s="83"/>
     </row>
     <row r="111" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V111" s="80"/>
-      <c r="W111" s="81"/>
-      <c r="X111" s="82"/>
+      <c r="V111" s="82"/>
+      <c r="W111" s="70"/>
+      <c r="X111" s="83"/>
     </row>
     <row r="112" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="V112" s="83"/>
-      <c r="W112" s="84"/>
-      <c r="X112" s="85"/>
+      <c r="V112" s="84"/>
+      <c r="W112" s="85"/>
+      <c r="X112" s="86"/>
     </row>
     <row r="113" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="114" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="S114" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="T114" s="76"/>
-      <c r="V114" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W114" s="78"/>
-      <c r="X114" s="79"/>
+      <c r="S114" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="T114" s="78"/>
+      <c r="V114" s="79"/>
+      <c r="W114" s="80"/>
+      <c r="X114" s="81"/>
     </row>
     <row r="115" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S115" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T115" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="V115" s="80"/>
-      <c r="W115" s="81"/>
-      <c r="X115" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="V115" s="82"/>
+      <c r="W115" s="70"/>
+      <c r="X115" s="83"/>
     </row>
     <row r="116" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S116" s="1">
         <v>1</v>
       </c>
-      <c r="T116" s="51">
-        <v>0.78680555555555554</v>
-      </c>
-      <c r="V116" s="80"/>
-      <c r="W116" s="81"/>
-      <c r="X116" s="82"/>
+      <c r="T116" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="V116" s="82"/>
+      <c r="W116" s="70"/>
+      <c r="X116" s="83"/>
     </row>
     <row r="117" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S117" s="54">
         <v>2</v>
       </c>
-      <c r="T117" s="53">
-        <v>0.78749999999999998</v>
-      </c>
-      <c r="V117" s="80"/>
-      <c r="W117" s="81"/>
-      <c r="X117" s="82"/>
+      <c r="T117" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="V117" s="82"/>
+      <c r="W117" s="70"/>
+      <c r="X117" s="83"/>
     </row>
     <row r="118" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S118" s="1">
         <v>3</v>
       </c>
-      <c r="T118" s="51">
-        <v>0.78819444444444442</v>
-      </c>
-      <c r="V118" s="80"/>
-      <c r="W118" s="81"/>
-      <c r="X118" s="82"/>
+      <c r="T118" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="V118" s="82"/>
+      <c r="W118" s="70"/>
+      <c r="X118" s="83"/>
     </row>
     <row r="119" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S119" s="54">
         <v>4</v>
       </c>
-      <c r="T119" s="53">
-        <v>0.78888888888888886</v>
-      </c>
-      <c r="V119" s="80"/>
-      <c r="W119" s="81"/>
-      <c r="X119" s="82"/>
+      <c r="T119" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="V119" s="82"/>
+      <c r="W119" s="70"/>
+      <c r="X119" s="83"/>
     </row>
     <row r="120" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S120" s="1">
         <v>5</v>
       </c>
-      <c r="T120" s="51">
-        <v>0.7895833333333333</v>
+      <c r="T120" s="51" t="s">
+        <v>72</v>
       </c>
       <c r="U120" s="31"/>
-      <c r="V120" s="80"/>
-      <c r="W120" s="81"/>
-      <c r="X120" s="82"/>
+      <c r="V120" s="82"/>
+      <c r="W120" s="70"/>
+      <c r="X120" s="83"/>
     </row>
     <row r="121" spans="19:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="V121" s="80"/>
-      <c r="W121" s="81"/>
-      <c r="X121" s="82"/>
+      <c r="V121" s="82"/>
+      <c r="W121" s="70"/>
+      <c r="X121" s="83"/>
     </row>
     <row r="122" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V122" s="80"/>
-      <c r="W122" s="81"/>
-      <c r="X122" s="82"/>
+      <c r="V122" s="82"/>
+      <c r="W122" s="70"/>
+      <c r="X122" s="83"/>
     </row>
     <row r="123" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V123" s="80"/>
-      <c r="W123" s="81"/>
-      <c r="X123" s="82"/>
+      <c r="V123" s="82"/>
+      <c r="W123" s="70"/>
+      <c r="X123" s="83"/>
     </row>
     <row r="124" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V124" s="80"/>
-      <c r="W124" s="81"/>
-      <c r="X124" s="82"/>
+      <c r="V124" s="82"/>
+      <c r="W124" s="70"/>
+      <c r="X124" s="83"/>
     </row>
     <row r="125" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V125" s="80"/>
-      <c r="W125" s="81"/>
-      <c r="X125" s="82"/>
+      <c r="V125" s="82"/>
+      <c r="W125" s="70"/>
+      <c r="X125" s="83"/>
     </row>
     <row r="126" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V126" s="80"/>
-      <c r="W126" s="81"/>
-      <c r="X126" s="82"/>
+      <c r="V126" s="82"/>
+      <c r="W126" s="70"/>
+      <c r="X126" s="83"/>
     </row>
     <row r="127" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V127" s="80"/>
-      <c r="W127" s="81"/>
-      <c r="X127" s="82"/>
+      <c r="V127" s="82"/>
+      <c r="W127" s="70"/>
+      <c r="X127" s="83"/>
     </row>
     <row r="128" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V128" s="80"/>
-      <c r="W128" s="81"/>
-      <c r="X128" s="82"/>
+      <c r="V128" s="82"/>
+      <c r="W128" s="70"/>
+      <c r="X128" s="83"/>
     </row>
     <row r="129" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V129" s="80"/>
-      <c r="W129" s="81"/>
-      <c r="X129" s="82"/>
+      <c r="V129" s="82"/>
+      <c r="W129" s="70"/>
+      <c r="X129" s="83"/>
     </row>
     <row r="130" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V130" s="80"/>
-      <c r="W130" s="81"/>
-      <c r="X130" s="82"/>
+      <c r="V130" s="82"/>
+      <c r="W130" s="70"/>
+      <c r="X130" s="83"/>
     </row>
     <row r="131" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V131" s="80"/>
-      <c r="W131" s="81"/>
-      <c r="X131" s="82"/>
+      <c r="V131" s="82"/>
+      <c r="W131" s="70"/>
+      <c r="X131" s="83"/>
     </row>
     <row r="132" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="V132" s="83"/>
-      <c r="W132" s="84"/>
-      <c r="X132" s="85"/>
+      <c r="V132" s="84"/>
+      <c r="W132" s="85"/>
+      <c r="X132" s="86"/>
     </row>
     <row r="133" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="134" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="S134" s="75" t="s">
-        <v>38</v>
-      </c>
-      <c r="T134" s="76"/>
-      <c r="V134" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W134" s="78"/>
-      <c r="X134" s="79"/>
+      <c r="S134" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="T134" s="78"/>
+      <c r="V134" s="79"/>
+      <c r="W134" s="80"/>
+      <c r="X134" s="81"/>
     </row>
     <row r="135" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S135" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T135" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="V135" s="80"/>
-      <c r="W135" s="81"/>
-      <c r="X135" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="V135" s="82"/>
+      <c r="W135" s="70"/>
+      <c r="X135" s="83"/>
     </row>
     <row r="136" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S136" s="1">
         <v>1</v>
       </c>
-      <c r="T136" s="51">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="V136" s="80"/>
-      <c r="W136" s="81"/>
-      <c r="X136" s="82"/>
+      <c r="T136" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="V136" s="82"/>
+      <c r="W136" s="70"/>
+      <c r="X136" s="83"/>
     </row>
     <row r="137" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S137" s="15">
         <v>2</v>
       </c>
-      <c r="T137" s="53">
-        <v>0.79583333333333328</v>
-      </c>
-      <c r="V137" s="80"/>
-      <c r="W137" s="81"/>
-      <c r="X137" s="82"/>
+      <c r="T137" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="V137" s="82"/>
+      <c r="W137" s="70"/>
+      <c r="X137" s="83"/>
     </row>
     <row r="138" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S138" s="1">
         <v>3</v>
       </c>
-      <c r="T138" s="51">
-        <v>0.79652777777777772</v>
-      </c>
-      <c r="V138" s="80"/>
-      <c r="W138" s="81"/>
-      <c r="X138" s="82"/>
+      <c r="T138" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="V138" s="82"/>
+      <c r="W138" s="70"/>
+      <c r="X138" s="83"/>
     </row>
     <row r="139" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S139" s="15">
         <v>4</v>
       </c>
-      <c r="T139" s="53">
-        <v>0.79722222222222228</v>
-      </c>
-      <c r="V139" s="80"/>
-      <c r="W139" s="81"/>
-      <c r="X139" s="82"/>
+      <c r="T139" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="V139" s="82"/>
+      <c r="W139" s="70"/>
+      <c r="X139" s="83"/>
     </row>
     <row r="140" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S140" s="1">
         <v>5</v>
       </c>
-      <c r="T140" s="51">
-        <v>0.79791666666666672</v>
+      <c r="T140" s="51" t="s">
+        <v>74</v>
       </c>
       <c r="U140" s="31"/>
-      <c r="V140" s="80"/>
-      <c r="W140" s="81"/>
-      <c r="X140" s="82"/>
+      <c r="V140" s="82"/>
+      <c r="W140" s="70"/>
+      <c r="X140" s="83"/>
     </row>
     <row r="141" spans="19:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="V141" s="80"/>
-      <c r="W141" s="81"/>
-      <c r="X141" s="82"/>
+      <c r="V141" s="82"/>
+      <c r="W141" s="70"/>
+      <c r="X141" s="83"/>
     </row>
     <row r="142" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V142" s="80"/>
-      <c r="W142" s="81"/>
-      <c r="X142" s="82"/>
+      <c r="V142" s="82"/>
+      <c r="W142" s="70"/>
+      <c r="X142" s="83"/>
     </row>
     <row r="143" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V143" s="80"/>
-      <c r="W143" s="81"/>
-      <c r="X143" s="82"/>
+      <c r="V143" s="82"/>
+      <c r="W143" s="70"/>
+      <c r="X143" s="83"/>
     </row>
     <row r="144" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V144" s="80"/>
-      <c r="W144" s="81"/>
-      <c r="X144" s="82"/>
+      <c r="V144" s="82"/>
+      <c r="W144" s="70"/>
+      <c r="X144" s="83"/>
     </row>
     <row r="145" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V145" s="80"/>
-      <c r="W145" s="81"/>
-      <c r="X145" s="82"/>
+      <c r="V145" s="82"/>
+      <c r="W145" s="70"/>
+      <c r="X145" s="83"/>
     </row>
     <row r="146" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V146" s="80"/>
-      <c r="W146" s="81"/>
-      <c r="X146" s="82"/>
+      <c r="V146" s="82"/>
+      <c r="W146" s="70"/>
+      <c r="X146" s="83"/>
     </row>
     <row r="147" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V147" s="80"/>
-      <c r="W147" s="81"/>
-      <c r="X147" s="82"/>
+      <c r="V147" s="82"/>
+      <c r="W147" s="70"/>
+      <c r="X147" s="83"/>
     </row>
     <row r="148" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V148" s="80"/>
-      <c r="W148" s="81"/>
-      <c r="X148" s="82"/>
+      <c r="V148" s="82"/>
+      <c r="W148" s="70"/>
+      <c r="X148" s="83"/>
     </row>
     <row r="149" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V149" s="80"/>
-      <c r="W149" s="81"/>
-      <c r="X149" s="82"/>
+      <c r="V149" s="82"/>
+      <c r="W149" s="70"/>
+      <c r="X149" s="83"/>
     </row>
     <row r="150" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V150" s="80"/>
-      <c r="W150" s="81"/>
-      <c r="X150" s="82"/>
+      <c r="V150" s="82"/>
+      <c r="W150" s="70"/>
+      <c r="X150" s="83"/>
     </row>
     <row r="151" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V151" s="80"/>
-      <c r="W151" s="81"/>
-      <c r="X151" s="82"/>
+      <c r="V151" s="82"/>
+      <c r="W151" s="70"/>
+      <c r="X151" s="83"/>
     </row>
     <row r="152" spans="22:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="V152" s="83"/>
-      <c r="W152" s="84"/>
-      <c r="X152" s="85"/>
+      <c r="V152" s="84"/>
+      <c r="W152" s="85"/>
+      <c r="X152" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="40">
@@ -4368,348 +4416,348 @@
       <c r="B9" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
     </row>
     <row r="13" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="104"/>
-      <c r="F14" s="107" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="104"/>
+      <c r="B14" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="106"/>
+      <c r="F14" s="109" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="106"/>
     </row>
     <row r="15" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="105" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="104"/>
-      <c r="F15" s="105" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="104"/>
+      <c r="B15" s="107" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="106"/>
+      <c r="F15" s="107" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="106"/>
     </row>
     <row r="16" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="104"/>
-      <c r="F16" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="104"/>
+      <c r="B16" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="106"/>
+      <c r="F16" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="106"/>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="108" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="104"/>
-      <c r="F17" s="108" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="104"/>
+      <c r="B17" s="110" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="106"/>
+      <c r="F17" s="110" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="106"/>
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="106" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="104"/>
+        <v>34</v>
+      </c>
+      <c r="C19" s="108" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="106"/>
       <c r="F19" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="106" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="104"/>
+        <v>34</v>
+      </c>
+      <c r="G19" s="108" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" s="106"/>
     </row>
     <row r="20" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="100">
+      <c r="B20" s="102">
         <v>1</v>
       </c>
-      <c r="C20" s="77" t="e">
+      <c r="C20" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="F20" s="100">
+      <c r="D20" s="81"/>
+      <c r="F20" s="102">
         <v>1</v>
       </c>
-      <c r="G20" s="77" t="e">
+      <c r="G20" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H20" s="79"/>
+      <c r="H20" s="81"/>
     </row>
     <row r="21" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="101"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="82"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="82"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="83"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="83"/>
     </row>
     <row r="22" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="101"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="82"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="82"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="83"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="83"/>
     </row>
     <row r="23" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="101"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="82"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="82"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="83"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="83"/>
     </row>
     <row r="24" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="101"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="82"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="82"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="83"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="83"/>
     </row>
     <row r="25" spans="2:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="102"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="85"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="85"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="86"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="86"/>
     </row>
     <row r="26" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="100">
+      <c r="B26" s="102">
         <v>2</v>
       </c>
-      <c r="C26" s="77" t="e">
+      <c r="C26" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D26" s="79"/>
-      <c r="F26" s="100">
+      <c r="D26" s="81"/>
+      <c r="F26" s="102">
         <v>2</v>
       </c>
-      <c r="G26" s="77" t="e">
+      <c r="G26" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H26" s="79"/>
+      <c r="H26" s="81"/>
     </row>
     <row r="27" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="101"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="82"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="82"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="83"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="83"/>
     </row>
     <row r="28" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="101"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="82"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="82"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="83"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="83"/>
     </row>
     <row r="29" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="101"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="82"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="82"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="83"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="83"/>
     </row>
     <row r="30" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="101"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="82"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="82"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="83"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="83"/>
     </row>
     <row r="31" spans="2:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="102"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="85"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="85"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="86"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="86"/>
     </row>
     <row r="32" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="100">
+      <c r="B32" s="102">
         <v>3</v>
       </c>
-      <c r="C32" s="77" t="e">
+      <c r="C32" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="79"/>
-      <c r="F32" s="100">
+      <c r="D32" s="81"/>
+      <c r="F32" s="102">
         <v>3</v>
       </c>
-      <c r="G32" s="77" t="e">
+      <c r="G32" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H32" s="79"/>
+      <c r="H32" s="81"/>
     </row>
     <row r="33" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="101"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="82"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="82"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="83"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="83"/>
     </row>
     <row r="34" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="101"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="82"/>
-      <c r="F34" s="101"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="82"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="83"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="83"/>
     </row>
     <row r="35" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="101"/>
-      <c r="C35" s="80"/>
-      <c r="D35" s="82"/>
-      <c r="F35" s="101"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="82"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="83"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="83"/>
     </row>
     <row r="36" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="101"/>
-      <c r="C36" s="80"/>
-      <c r="D36" s="82"/>
-      <c r="F36" s="101"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="82"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="83"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="83"/>
     </row>
     <row r="37" spans="2:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="102"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="85"/>
-      <c r="F37" s="102"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="85"/>
+      <c r="B37" s="104"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="86"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="86"/>
     </row>
     <row r="38" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="100">
+      <c r="B38" s="102">
         <v>4</v>
       </c>
-      <c r="C38" s="77" t="e">
+      <c r="C38" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D38" s="79"/>
-      <c r="F38" s="100">
+      <c r="D38" s="81"/>
+      <c r="F38" s="102">
         <v>4</v>
       </c>
-      <c r="G38" s="77" t="e">
+      <c r="G38" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H38" s="79"/>
+      <c r="H38" s="81"/>
     </row>
     <row r="39" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="101"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="82"/>
-      <c r="F39" s="101"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="82"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="83"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="83"/>
     </row>
     <row r="40" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="101"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="82"/>
-      <c r="F40" s="101"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="82"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="83"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="83"/>
     </row>
     <row r="41" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="101"/>
-      <c r="C41" s="80"/>
-      <c r="D41" s="82"/>
-      <c r="F41" s="101"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="82"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="83"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="83"/>
     </row>
     <row r="42" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="101"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="82"/>
-      <c r="F42" s="101"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="82"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="82"/>
+      <c r="D42" s="83"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="83"/>
     </row>
     <row r="43" spans="2:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="102"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="85"/>
-      <c r="F43" s="102"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="85"/>
+      <c r="B43" s="104"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="86"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="86"/>
     </row>
     <row r="44" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="100">
+      <c r="B44" s="102">
         <v>5</v>
       </c>
-      <c r="C44" s="77" t="e">
+      <c r="C44" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D44" s="79"/>
-      <c r="F44" s="100">
+      <c r="D44" s="81"/>
+      <c r="F44" s="102">
         <v>5</v>
       </c>
-      <c r="G44" s="77" t="e">
+      <c r="G44" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H44" s="79"/>
+      <c r="H44" s="81"/>
     </row>
     <row r="45" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="101"/>
-      <c r="C45" s="80"/>
-      <c r="D45" s="82"/>
-      <c r="F45" s="101"/>
-      <c r="G45" s="80"/>
-      <c r="H45" s="82"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="82"/>
+      <c r="D45" s="83"/>
+      <c r="F45" s="103"/>
+      <c r="G45" s="82"/>
+      <c r="H45" s="83"/>
     </row>
     <row r="46" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="101"/>
-      <c r="C46" s="80"/>
-      <c r="D46" s="82"/>
-      <c r="F46" s="101"/>
-      <c r="G46" s="80"/>
-      <c r="H46" s="82"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="82"/>
+      <c r="D46" s="83"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="82"/>
+      <c r="H46" s="83"/>
     </row>
     <row r="47" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="101"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="82"/>
-      <c r="F47" s="101"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="82"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="82"/>
+      <c r="D47" s="83"/>
+      <c r="F47" s="103"/>
+      <c r="G47" s="82"/>
+      <c r="H47" s="83"/>
     </row>
     <row r="48" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="101"/>
-      <c r="C48" s="80"/>
-      <c r="D48" s="82"/>
-      <c r="F48" s="101"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="82"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="82"/>
+      <c r="D48" s="83"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="82"/>
+      <c r="H48" s="83"/>
     </row>
     <row r="49" spans="2:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="102"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="85"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="85"/>
+      <c r="B49" s="104"/>
+      <c r="C49" s="84"/>
+      <c r="D49" s="86"/>
+      <c r="F49" s="104"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -4773,15 +4821,15 @@
       <c r="B9" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="O10" s="110"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
+      <c r="O10" s="98"/>
+      <c r="P10" s="70"/>
+      <c r="Q10" s="70"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.35">
       <c r="N11" s="33"/>
@@ -4801,55 +4849,55 @@
       <c r="Q13" s="58"/>
     </row>
     <row r="14" spans="2:17" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="74"/>
-      <c r="F14" s="94" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="109"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="76"/>
+      <c r="F14" s="95" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
       <c r="O14" s="57"/>
       <c r="P14" s="58"/>
       <c r="Q14" s="58"/>
     </row>
     <row r="15" spans="2:17" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="74"/>
-      <c r="F15" s="94" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="76"/>
+      <c r="F15" s="95" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
       <c r="O15" s="57"/>
       <c r="P15" s="58"/>
       <c r="Q15" s="58"/>
     </row>
     <row r="16" spans="2:17" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="72" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="74"/>
-      <c r="F16" s="94" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
+      <c r="B16" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="75"/>
+      <c r="D16" s="76"/>
+      <c r="F16" s="95" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
       <c r="O16" s="57"/>
       <c r="P16" s="58"/>
       <c r="Q16" s="58"/>
@@ -4872,28 +4920,28 @@
     </row>
     <row r="19" spans="1:25" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
-      <c r="B19" s="92" t="s">
+      <c r="B19" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="99" t="s">
+      <c r="C19" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="70"/>
-      <c r="E19" s="88" t="s">
+      <c r="D19" s="72"/>
+      <c r="E19" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="89"/>
-      <c r="G19" s="90" t="s">
+      <c r="F19" s="90"/>
+      <c r="G19" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="91"/>
+      <c r="H19" s="92"/>
       <c r="O19" s="57"/>
       <c r="P19" s="58"/>
       <c r="Q19" s="58"/>
     </row>
     <row r="20" spans="1:25" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
-      <c r="B20" s="93"/>
+      <c r="B20" s="94"/>
       <c r="C20" s="7" t="s">
         <v>11</v>
       </c>
@@ -4934,10 +4982,10 @@
         <v>0.69722222222222219</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="O21" s="59"/>
       <c r="P21" s="60"/>
@@ -4947,7 +4995,7 @@
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" s="33"/>
       <c r="B22" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="47"/>
@@ -4958,16 +5006,16 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G22" s="47" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="H22" s="47" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" s="33"/>
       <c r="B23" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="43">
         <v>0.51527777777777772</v>
@@ -4991,7 +5039,7 @@
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" s="33"/>
       <c r="B24" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" s="46">
         <v>0.52708333333333335</v>
@@ -5006,15 +5054,15 @@
         <v>0.73819444444444449</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H24" s="47" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="43">
         <v>0.54513888888888884</v>
@@ -5028,17 +5076,17 @@
       <c r="F25" s="66">
         <v>0.44236111111111109</v>
       </c>
-      <c r="G25" s="44">
-        <v>0.71250000000000002</v>
-      </c>
-      <c r="H25" s="40">
-        <v>0.71527777777777779</v>
+      <c r="G25" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="40" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="33"/>
       <c r="B26" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" s="49">
         <v>0.56388888888888888</v>
@@ -5052,18 +5100,18 @@
       <c r="F26" s="50">
         <v>0.44791666666666669</v>
       </c>
-      <c r="G26" s="50">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="H26" s="50">
-        <v>0.49583333333333329</v>
+      <c r="G26" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B28" s="95" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="81"/>
+      <c r="B28" s="96" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="70"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="T29" s="39"/>
@@ -5075,96 +5123,94 @@
     </row>
     <row r="31" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="32" spans="1:25" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="70"/>
-      <c r="J32" s="86" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" s="87"/>
-      <c r="L32" s="87"/>
-      <c r="S32" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="T32" s="76"/>
-      <c r="V32" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="W32" s="76"/>
-      <c r="X32" s="76"/>
+      <c r="C32" s="72"/>
+      <c r="J32" s="87" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="88"/>
+      <c r="L32" s="88"/>
+      <c r="S32" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="T32" s="78"/>
+      <c r="V32" s="77" t="s">
+        <v>31</v>
+      </c>
+      <c r="W32" s="78"/>
+      <c r="X32" s="78"/>
     </row>
     <row r="33" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="70"/>
-      <c r="F34" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="G34" s="70"/>
-      <c r="J34" s="86" t="s">
-        <v>29</v>
-      </c>
-      <c r="K34" s="87"/>
-      <c r="L34" s="87"/>
-      <c r="N34" s="86" t="s">
-        <v>30</v>
-      </c>
-      <c r="O34" s="87"/>
-      <c r="S34" s="75" t="s">
-        <v>29</v>
-      </c>
-      <c r="T34" s="76"/>
-      <c r="V34" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W34" s="78"/>
-      <c r="X34" s="79"/>
+      <c r="B34" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="73"/>
+      <c r="D34" s="72"/>
+      <c r="F34" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="72"/>
+      <c r="J34" s="87" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" s="88"/>
+      <c r="L34" s="88"/>
+      <c r="N34" s="87" t="s">
+        <v>33</v>
+      </c>
+      <c r="O34" s="88"/>
+      <c r="S34" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="T34" s="78"/>
+      <c r="V34" s="79"/>
+      <c r="W34" s="80"/>
+      <c r="X34" s="81"/>
     </row>
     <row r="35" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="33"/>
       <c r="B35" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G35" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J35" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J35" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="K35" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L35" s="55" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O35" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="S35" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="S35" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="T35" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="V35" s="80"/>
-      <c r="W35" s="81"/>
-      <c r="X35" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="V35" s="82"/>
+      <c r="W35" s="70"/>
+      <c r="X35" s="83"/>
     </row>
     <row r="36" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="31"/>
@@ -5206,11 +5252,11 @@
         <v>1</v>
       </c>
       <c r="T36" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="V36" s="80"/>
-      <c r="W36" s="81"/>
-      <c r="X36" s="82"/>
+        <v>14</v>
+      </c>
+      <c r="V36" s="82"/>
+      <c r="W36" s="70"/>
+      <c r="X36" s="83"/>
     </row>
     <row r="37" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="15">
@@ -5226,7 +5272,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="53" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="J37" s="15">
         <v>2</v>
@@ -5247,11 +5293,11 @@
         <v>2</v>
       </c>
       <c r="T37" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="V37" s="80"/>
-      <c r="W37" s="81"/>
-      <c r="X37" s="82"/>
+        <v>14</v>
+      </c>
+      <c r="V37" s="82"/>
+      <c r="W37" s="70"/>
+      <c r="X37" s="83"/>
     </row>
     <row r="38" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B38" s="1">
@@ -5267,7 +5313,7 @@
         <v>3</v>
       </c>
       <c r="G38" s="51" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="J38" s="1">
         <v>3</v>
@@ -5290,9 +5336,9 @@
       <c r="T38" s="51">
         <v>0.68958333333333333</v>
       </c>
-      <c r="V38" s="80"/>
-      <c r="W38" s="81"/>
-      <c r="X38" s="82"/>
+      <c r="V38" s="82"/>
+      <c r="W38" s="70"/>
+      <c r="X38" s="83"/>
     </row>
     <row r="39" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B39" s="15">
@@ -5308,7 +5354,7 @@
         <v>4</v>
       </c>
       <c r="G39" s="52" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J39" s="15">
         <v>4</v>
@@ -5331,9 +5377,9 @@
       <c r="T39" s="52">
         <v>0.69027777777777777</v>
       </c>
-      <c r="V39" s="80"/>
-      <c r="W39" s="81"/>
-      <c r="X39" s="82"/>
+      <c r="V39" s="82"/>
+      <c r="W39" s="70"/>
+      <c r="X39" s="83"/>
     </row>
     <row r="40" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B40" s="1">
@@ -5349,7 +5395,7 @@
         <v>5</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="J40" s="1">
         <v>5</v>
@@ -5373,9 +5419,9 @@
         <v>0.69097222222222221</v>
       </c>
       <c r="U40" s="31"/>
-      <c r="V40" s="80"/>
-      <c r="W40" s="81"/>
-      <c r="X40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="70"/>
+      <c r="X40" s="83"/>
     </row>
     <row r="41" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B41" s="15">
@@ -5391,7 +5437,7 @@
         <v>6</v>
       </c>
       <c r="G41" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J41" s="15">
         <v>6</v>
@@ -5408,9 +5454,9 @@
       <c r="O41" s="52">
         <v>0.7055555555555556</v>
       </c>
-      <c r="V41" s="80"/>
-      <c r="W41" s="81"/>
-      <c r="X41" s="82"/>
+      <c r="V41" s="82"/>
+      <c r="W41" s="70"/>
+      <c r="X41" s="83"/>
     </row>
     <row r="42" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="1">
@@ -5426,7 +5472,7 @@
         <v>7</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="J42" s="1">
         <v>7</v>
@@ -5443,9 +5489,9 @@
       <c r="O42" s="51">
         <v>0.70625000000000004</v>
       </c>
-      <c r="V42" s="80"/>
-      <c r="W42" s="81"/>
-      <c r="X42" s="82"/>
+      <c r="V42" s="82"/>
+      <c r="W42" s="70"/>
+      <c r="X42" s="83"/>
     </row>
     <row r="43" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="15">
@@ -5461,7 +5507,7 @@
         <v>8</v>
       </c>
       <c r="G43" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="J43" s="15">
         <v>8</v>
@@ -5478,9 +5524,9 @@
       <c r="O43" s="52">
         <v>0.70694444444444449</v>
       </c>
-      <c r="V43" s="80"/>
-      <c r="W43" s="81"/>
-      <c r="X43" s="82"/>
+      <c r="V43" s="82"/>
+      <c r="W43" s="70"/>
+      <c r="X43" s="83"/>
     </row>
     <row r="44" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B44" s="1">
@@ -5496,7 +5542,7 @@
         <v>9</v>
       </c>
       <c r="G44" s="51" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="J44" s="1">
         <v>9</v>
@@ -5514,9 +5560,9 @@
         <v>0.70763888888888893</v>
       </c>
       <c r="R44" s="31"/>
-      <c r="V44" s="80"/>
-      <c r="W44" s="81"/>
-      <c r="X44" s="82"/>
+      <c r="V44" s="82"/>
+      <c r="W44" s="70"/>
+      <c r="X44" s="83"/>
     </row>
     <row r="45" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="15">
@@ -5551,75 +5597,75 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="P45" s="32"/>
-      <c r="V45" s="80"/>
-      <c r="W45" s="81"/>
-      <c r="X45" s="82"/>
+      <c r="V45" s="82"/>
+      <c r="W45" s="70"/>
+      <c r="X45" s="83"/>
     </row>
     <row r="46" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D46" s="31"/>
       <c r="L46" s="31"/>
-      <c r="V46" s="80"/>
-      <c r="W46" s="81"/>
-      <c r="X46" s="82"/>
+      <c r="V46" s="82"/>
+      <c r="W46" s="70"/>
+      <c r="X46" s="83"/>
     </row>
     <row r="47" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="34"/>
-      <c r="B47" s="69" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="70"/>
-      <c r="F47" s="69" t="s">
-        <v>36</v>
-      </c>
-      <c r="G47" s="71"/>
-      <c r="H47" s="70"/>
-      <c r="J47" s="86" t="s">
-        <v>35</v>
-      </c>
-      <c r="K47" s="87"/>
-      <c r="N47" s="86" t="s">
-        <v>36</v>
-      </c>
-      <c r="O47" s="87"/>
-      <c r="P47" s="87"/>
-      <c r="V47" s="80"/>
-      <c r="W47" s="81"/>
-      <c r="X47" s="82"/>
+      <c r="B47" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="72"/>
+      <c r="F47" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="G47" s="73"/>
+      <c r="H47" s="72"/>
+      <c r="J47" s="87" t="s">
+        <v>46</v>
+      </c>
+      <c r="K47" s="88"/>
+      <c r="N47" s="87" t="s">
+        <v>47</v>
+      </c>
+      <c r="O47" s="88"/>
+      <c r="P47" s="88"/>
+      <c r="V47" s="82"/>
+      <c r="W47" s="70"/>
+      <c r="X47" s="83"/>
     </row>
     <row r="48" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C48" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F48" s="14" t="s">
-        <v>31</v>
-      </c>
       <c r="G48" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J48" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K48" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="N48" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="N48" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="O48" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P48" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="V48" s="80"/>
-      <c r="W48" s="81"/>
-      <c r="X48" s="82"/>
+        <v>36</v>
+      </c>
+      <c r="V48" s="82"/>
+      <c r="W48" s="70"/>
+      <c r="X48" s="83"/>
     </row>
     <row r="49" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="31"/>
@@ -5656,9 +5702,9 @@
       <c r="P49" s="51">
         <v>0.72569444444444442</v>
       </c>
-      <c r="V49" s="80"/>
-      <c r="W49" s="81"/>
-      <c r="X49" s="82"/>
+      <c r="V49" s="82"/>
+      <c r="W49" s="70"/>
+      <c r="X49" s="83"/>
     </row>
     <row r="50" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="15">
@@ -5691,9 +5737,9 @@
       <c r="P50" s="53">
         <v>0.7270833333333333</v>
       </c>
-      <c r="V50" s="80"/>
-      <c r="W50" s="81"/>
-      <c r="X50" s="82"/>
+      <c r="V50" s="82"/>
+      <c r="W50" s="70"/>
+      <c r="X50" s="83"/>
     </row>
     <row r="51" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="1">
@@ -5726,9 +5772,9 @@
       <c r="P51" s="51">
         <v>0.72847222222222219</v>
       </c>
-      <c r="V51" s="80"/>
-      <c r="W51" s="81"/>
-      <c r="X51" s="82"/>
+      <c r="V51" s="82"/>
+      <c r="W51" s="70"/>
+      <c r="X51" s="83"/>
     </row>
     <row r="52" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="15">
@@ -5762,9 +5808,9 @@
         <v>0.72986111111111107</v>
       </c>
       <c r="R52" s="31"/>
-      <c r="V52" s="83"/>
-      <c r="W52" s="84"/>
-      <c r="X52" s="85"/>
+      <c r="V52" s="84"/>
+      <c r="W52" s="85"/>
+      <c r="X52" s="86"/>
     </row>
     <row r="53" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="1">
@@ -5829,15 +5875,13 @@
       <c r="P54" s="52">
         <v>0.73263888888888884</v>
       </c>
-      <c r="S54" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="T54" s="76"/>
-      <c r="V54" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W54" s="78"/>
-      <c r="X54" s="79"/>
+      <c r="S54" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="T54" s="78"/>
+      <c r="V54" s="79"/>
+      <c r="W54" s="80"/>
+      <c r="X54" s="81"/>
     </row>
     <row r="55" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B55" s="1">
@@ -5871,14 +5915,14 @@
         <v>0.73402777777777772</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T55" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="V55" s="80"/>
-      <c r="W55" s="81"/>
-      <c r="X55" s="82"/>
+        <v>37</v>
+      </c>
+      <c r="V55" s="82"/>
+      <c r="W55" s="70"/>
+      <c r="X55" s="83"/>
     </row>
     <row r="56" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="15">
@@ -5915,11 +5959,11 @@
         <v>1</v>
       </c>
       <c r="T56" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="V56" s="80"/>
-      <c r="W56" s="81"/>
-      <c r="X56" s="82"/>
+        <v>16</v>
+      </c>
+      <c r="V56" s="82"/>
+      <c r="W56" s="70"/>
+      <c r="X56" s="83"/>
     </row>
     <row r="57" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="1">
@@ -5956,11 +6000,11 @@
         <v>2</v>
       </c>
       <c r="T57" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="V57" s="80"/>
-      <c r="W57" s="81"/>
-      <c r="X57" s="82"/>
+        <v>48</v>
+      </c>
+      <c r="V57" s="82"/>
+      <c r="W57" s="70"/>
+      <c r="X57" s="83"/>
     </row>
     <row r="58" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="15">
@@ -6001,96 +6045,96 @@
         <v>3</v>
       </c>
       <c r="T58" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="V58" s="80"/>
-      <c r="W58" s="81"/>
-      <c r="X58" s="82"/>
+        <v>49</v>
+      </c>
+      <c r="V58" s="82"/>
+      <c r="W58" s="70"/>
+      <c r="X58" s="83"/>
     </row>
     <row r="59" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S59" s="15">
         <v>4</v>
       </c>
       <c r="T59" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="V59" s="80"/>
-      <c r="W59" s="81"/>
-      <c r="X59" s="82"/>
+        <v>50</v>
+      </c>
+      <c r="V59" s="82"/>
+      <c r="W59" s="70"/>
+      <c r="X59" s="83"/>
     </row>
     <row r="60" spans="1:24" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="71"/>
-      <c r="D60" s="70"/>
-      <c r="F60" s="69" t="s">
-        <v>38</v>
-      </c>
-      <c r="G60" s="71"/>
-      <c r="H60" s="70"/>
-      <c r="J60" s="86" t="s">
-        <v>37</v>
-      </c>
-      <c r="K60" s="87"/>
-      <c r="L60" s="87"/>
-      <c r="N60" s="86" t="s">
-        <v>38</v>
-      </c>
-      <c r="O60" s="87"/>
-      <c r="P60" s="87"/>
+      <c r="B60" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60" s="73"/>
+      <c r="D60" s="72"/>
+      <c r="F60" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="G60" s="73"/>
+      <c r="H60" s="72"/>
+      <c r="J60" s="87" t="s">
+        <v>51</v>
+      </c>
+      <c r="K60" s="88"/>
+      <c r="L60" s="88"/>
+      <c r="N60" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="O60" s="88"/>
+      <c r="P60" s="88"/>
       <c r="R60" s="31"/>
       <c r="S60" s="1">
         <v>5</v>
       </c>
       <c r="T60" s="51" t="s">
-        <v>54</v>
-      </c>
-      <c r="V60" s="80"/>
-      <c r="W60" s="81"/>
-      <c r="X60" s="82"/>
+        <v>17</v>
+      </c>
+      <c r="V60" s="82"/>
+      <c r="W60" s="70"/>
+      <c r="X60" s="83"/>
     </row>
     <row r="61" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E61" s="33"/>
       <c r="F61" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J61" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K61" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L61" s="55" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N61" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O61" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P61" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="V61" s="80"/>
-      <c r="W61" s="81"/>
-      <c r="X61" s="82"/>
+        <v>36</v>
+      </c>
+      <c r="V61" s="82"/>
+      <c r="W61" s="70"/>
+      <c r="X61" s="83"/>
     </row>
     <row r="62" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="31"/>
@@ -6133,9 +6177,9 @@
       <c r="P62" s="51">
         <v>0.44861111111111113</v>
       </c>
-      <c r="V62" s="80"/>
-      <c r="W62" s="81"/>
-      <c r="X62" s="82"/>
+      <c r="V62" s="82"/>
+      <c r="W62" s="70"/>
+      <c r="X62" s="83"/>
     </row>
     <row r="63" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="15">
@@ -6174,9 +6218,9 @@
       <c r="P63" s="53">
         <v>0.45</v>
       </c>
-      <c r="V63" s="80"/>
-      <c r="W63" s="81"/>
-      <c r="X63" s="82"/>
+      <c r="V63" s="82"/>
+      <c r="W63" s="70"/>
+      <c r="X63" s="83"/>
     </row>
     <row r="64" spans="1:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="1">
@@ -6216,9 +6260,9 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="U64" s="32"/>
-      <c r="V64" s="80"/>
-      <c r="W64" s="81"/>
-      <c r="X64" s="82"/>
+      <c r="V64" s="82"/>
+      <c r="W64" s="70"/>
+      <c r="X64" s="83"/>
     </row>
     <row r="65" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="15">
@@ -6257,9 +6301,9 @@
       <c r="P65" s="52">
         <v>0.45277777777777778</v>
       </c>
-      <c r="V65" s="80"/>
-      <c r="W65" s="81"/>
-      <c r="X65" s="82"/>
+      <c r="V65" s="82"/>
+      <c r="W65" s="70"/>
+      <c r="X65" s="83"/>
     </row>
     <row r="66" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B66" s="1">
@@ -6298,9 +6342,9 @@
       <c r="P66" s="51">
         <v>0.45416666666666672</v>
       </c>
-      <c r="V66" s="80"/>
-      <c r="W66" s="81"/>
-      <c r="X66" s="82"/>
+      <c r="V66" s="82"/>
+      <c r="W66" s="70"/>
+      <c r="X66" s="83"/>
     </row>
     <row r="67" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B67" s="15">
@@ -6339,9 +6383,9 @@
       <c r="P67" s="52">
         <v>0.45555555555555549</v>
       </c>
-      <c r="V67" s="80"/>
-      <c r="W67" s="81"/>
-      <c r="X67" s="82"/>
+      <c r="V67" s="82"/>
+      <c r="W67" s="70"/>
+      <c r="X67" s="83"/>
     </row>
     <row r="68" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B68" s="1">
@@ -6381,9 +6425,9 @@
         <v>0.45694444444444438</v>
       </c>
       <c r="R68" s="31"/>
-      <c r="V68" s="80"/>
-      <c r="W68" s="81"/>
-      <c r="X68" s="82"/>
+      <c r="V68" s="82"/>
+      <c r="W68" s="70"/>
+      <c r="X68" s="83"/>
     </row>
     <row r="69" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B69" s="15">
@@ -6422,9 +6466,9 @@
       <c r="P69" s="53">
         <v>0.45833333333333331</v>
       </c>
-      <c r="V69" s="80"/>
-      <c r="W69" s="81"/>
-      <c r="X69" s="82"/>
+      <c r="V69" s="82"/>
+      <c r="W69" s="70"/>
+      <c r="X69" s="83"/>
     </row>
     <row r="70" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B70" s="1">
@@ -6463,9 +6507,9 @@
       <c r="P70" s="51">
         <v>0.4597222222222222</v>
       </c>
-      <c r="V70" s="80"/>
-      <c r="W70" s="81"/>
-      <c r="X70" s="82"/>
+      <c r="V70" s="82"/>
+      <c r="W70" s="70"/>
+      <c r="X70" s="83"/>
     </row>
     <row r="71" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B71" s="15">
@@ -6504,9 +6548,9 @@
       <c r="P71" s="52">
         <v>0.44791666666666669</v>
       </c>
-      <c r="V71" s="80"/>
-      <c r="W71" s="81"/>
-      <c r="X71" s="82"/>
+      <c r="V71" s="82"/>
+      <c r="W71" s="70"/>
+      <c r="X71" s="83"/>
     </row>
     <row r="72" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D72" s="31"/>
@@ -6514,32 +6558,30 @@
       <c r="L72" s="31"/>
       <c r="P72" s="31"/>
       <c r="U72" s="32"/>
-      <c r="V72" s="83"/>
-      <c r="W72" s="84"/>
-      <c r="X72" s="85"/>
+      <c r="V72" s="84"/>
+      <c r="W72" s="85"/>
+      <c r="X72" s="86"/>
     </row>
     <row r="73" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="74" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="S74" s="75" t="s">
-        <v>35</v>
-      </c>
-      <c r="T74" s="76"/>
-      <c r="V74" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W74" s="78"/>
-      <c r="X74" s="79"/>
+      <c r="S74" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="T74" s="78"/>
+      <c r="V74" s="79"/>
+      <c r="W74" s="80"/>
+      <c r="X74" s="81"/>
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.35">
       <c r="S75" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T75" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="V75" s="80"/>
-      <c r="W75" s="81"/>
-      <c r="X75" s="82"/>
+        <v>37</v>
+      </c>
+      <c r="V75" s="82"/>
+      <c r="W75" s="70"/>
+      <c r="X75" s="83"/>
     </row>
     <row r="76" spans="2:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="R76" s="31"/>
@@ -6549,9 +6591,9 @@
       <c r="T76" s="51">
         <v>0.70416666666666672</v>
       </c>
-      <c r="V76" s="80"/>
-      <c r="W76" s="81"/>
-      <c r="X76" s="82"/>
+      <c r="V76" s="82"/>
+      <c r="W76" s="70"/>
+      <c r="X76" s="83"/>
     </row>
     <row r="77" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S77" s="15">
@@ -6560,9 +6602,9 @@
       <c r="T77" s="53">
         <v>0.70486111111111116</v>
       </c>
-      <c r="V77" s="80"/>
-      <c r="W77" s="81"/>
-      <c r="X77" s="82"/>
+      <c r="V77" s="82"/>
+      <c r="W77" s="70"/>
+      <c r="X77" s="83"/>
     </row>
     <row r="78" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S78" s="1">
@@ -6571,9 +6613,9 @@
       <c r="T78" s="51">
         <v>0.7055555555555556</v>
       </c>
-      <c r="V78" s="80"/>
-      <c r="W78" s="81"/>
-      <c r="X78" s="82"/>
+      <c r="V78" s="82"/>
+      <c r="W78" s="70"/>
+      <c r="X78" s="83"/>
     </row>
     <row r="79" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S79" s="15">
@@ -6582,9 +6624,9 @@
       <c r="T79" s="53">
         <v>0.70625000000000004</v>
       </c>
-      <c r="V79" s="80"/>
-      <c r="W79" s="81"/>
-      <c r="X79" s="82"/>
+      <c r="V79" s="82"/>
+      <c r="W79" s="70"/>
+      <c r="X79" s="83"/>
     </row>
     <row r="80" spans="2:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S80" s="1">
@@ -6594,483 +6636,477 @@
         <v>0.70694444444444449</v>
       </c>
       <c r="U80" s="32"/>
-      <c r="V80" s="80"/>
-      <c r="W80" s="81"/>
-      <c r="X80" s="82"/>
+      <c r="V80" s="82"/>
+      <c r="W80" s="70"/>
+      <c r="X80" s="83"/>
     </row>
     <row r="81" spans="19:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="V81" s="80"/>
-      <c r="W81" s="81"/>
-      <c r="X81" s="82"/>
+      <c r="V81" s="82"/>
+      <c r="W81" s="70"/>
+      <c r="X81" s="83"/>
     </row>
     <row r="82" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V82" s="80"/>
-      <c r="W82" s="81"/>
-      <c r="X82" s="82"/>
+      <c r="V82" s="82"/>
+      <c r="W82" s="70"/>
+      <c r="X82" s="83"/>
     </row>
     <row r="83" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V83" s="80"/>
-      <c r="W83" s="81"/>
-      <c r="X83" s="82"/>
+      <c r="V83" s="82"/>
+      <c r="W83" s="70"/>
+      <c r="X83" s="83"/>
     </row>
     <row r="84" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V84" s="80"/>
-      <c r="W84" s="81"/>
-      <c r="X84" s="82"/>
+      <c r="V84" s="82"/>
+      <c r="W84" s="70"/>
+      <c r="X84" s="83"/>
     </row>
     <row r="85" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V85" s="80"/>
-      <c r="W85" s="81"/>
-      <c r="X85" s="82"/>
+      <c r="V85" s="82"/>
+      <c r="W85" s="70"/>
+      <c r="X85" s="83"/>
     </row>
     <row r="86" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V86" s="80"/>
-      <c r="W86" s="81"/>
-      <c r="X86" s="82"/>
+      <c r="V86" s="82"/>
+      <c r="W86" s="70"/>
+      <c r="X86" s="83"/>
     </row>
     <row r="87" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V87" s="80"/>
-      <c r="W87" s="81"/>
-      <c r="X87" s="82"/>
+      <c r="V87" s="82"/>
+      <c r="W87" s="70"/>
+      <c r="X87" s="83"/>
     </row>
     <row r="88" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V88" s="80"/>
-      <c r="W88" s="81"/>
-      <c r="X88" s="82"/>
+      <c r="V88" s="82"/>
+      <c r="W88" s="70"/>
+      <c r="X88" s="83"/>
     </row>
     <row r="89" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V89" s="80"/>
-      <c r="W89" s="81"/>
-      <c r="X89" s="82"/>
+      <c r="V89" s="82"/>
+      <c r="W89" s="70"/>
+      <c r="X89" s="83"/>
     </row>
     <row r="90" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V90" s="80"/>
-      <c r="W90" s="81"/>
-      <c r="X90" s="82"/>
+      <c r="V90" s="82"/>
+      <c r="W90" s="70"/>
+      <c r="X90" s="83"/>
     </row>
     <row r="91" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V91" s="80"/>
-      <c r="W91" s="81"/>
-      <c r="X91" s="82"/>
+      <c r="V91" s="82"/>
+      <c r="W91" s="70"/>
+      <c r="X91" s="83"/>
     </row>
     <row r="92" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="V92" s="83"/>
-      <c r="W92" s="84"/>
-      <c r="X92" s="85"/>
+      <c r="V92" s="84"/>
+      <c r="W92" s="85"/>
+      <c r="X92" s="86"/>
     </row>
     <row r="93" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="94" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="S94" s="96" t="s">
-        <v>36</v>
-      </c>
-      <c r="T94" s="76"/>
-      <c r="V94" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W94" s="78"/>
-      <c r="X94" s="79"/>
+      <c r="S94" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="T94" s="78"/>
+      <c r="V94" s="79"/>
+      <c r="W94" s="80"/>
+      <c r="X94" s="81"/>
     </row>
     <row r="95" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S95" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T95" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="V95" s="80"/>
-      <c r="W95" s="81"/>
-      <c r="X95" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="V95" s="82"/>
+      <c r="W95" s="70"/>
+      <c r="X95" s="83"/>
     </row>
     <row r="96" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S96" s="1">
         <v>1</v>
       </c>
       <c r="T96" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="V96" s="80"/>
-      <c r="W96" s="81"/>
-      <c r="X96" s="82"/>
+        <v>20</v>
+      </c>
+      <c r="V96" s="82"/>
+      <c r="W96" s="70"/>
+      <c r="X96" s="83"/>
     </row>
     <row r="97" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S97" s="15">
         <v>2</v>
       </c>
       <c r="T97" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="V97" s="80"/>
-      <c r="W97" s="81"/>
-      <c r="X97" s="82"/>
+        <v>53</v>
+      </c>
+      <c r="V97" s="82"/>
+      <c r="W97" s="70"/>
+      <c r="X97" s="83"/>
     </row>
     <row r="98" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S98" s="1">
         <v>3</v>
       </c>
       <c r="T98" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="V98" s="80"/>
-      <c r="W98" s="81"/>
-      <c r="X98" s="82"/>
+        <v>54</v>
+      </c>
+      <c r="V98" s="82"/>
+      <c r="W98" s="70"/>
+      <c r="X98" s="83"/>
     </row>
     <row r="99" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S99" s="15">
         <v>4</v>
       </c>
       <c r="T99" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="V99" s="80"/>
-      <c r="W99" s="81"/>
-      <c r="X99" s="82"/>
+        <v>55</v>
+      </c>
+      <c r="V99" s="82"/>
+      <c r="W99" s="70"/>
+      <c r="X99" s="83"/>
     </row>
     <row r="100" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S100" s="1">
         <v>5</v>
       </c>
       <c r="T100" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="V100" s="80"/>
-      <c r="W100" s="81"/>
-      <c r="X100" s="82"/>
+        <v>21</v>
+      </c>
+      <c r="V100" s="82"/>
+      <c r="W100" s="70"/>
+      <c r="X100" s="83"/>
     </row>
     <row r="101" spans="19:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="V101" s="80"/>
-      <c r="W101" s="81"/>
-      <c r="X101" s="82"/>
+      <c r="V101" s="82"/>
+      <c r="W101" s="70"/>
+      <c r="X101" s="83"/>
     </row>
     <row r="102" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V102" s="80"/>
-      <c r="W102" s="81"/>
-      <c r="X102" s="82"/>
+      <c r="V102" s="82"/>
+      <c r="W102" s="70"/>
+      <c r="X102" s="83"/>
     </row>
     <row r="103" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V103" s="80"/>
-      <c r="W103" s="81"/>
-      <c r="X103" s="82"/>
+      <c r="V103" s="82"/>
+      <c r="W103" s="70"/>
+      <c r="X103" s="83"/>
     </row>
     <row r="104" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V104" s="80"/>
-      <c r="W104" s="81"/>
-      <c r="X104" s="82"/>
+      <c r="V104" s="82"/>
+      <c r="W104" s="70"/>
+      <c r="X104" s="83"/>
     </row>
     <row r="105" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V105" s="80"/>
-      <c r="W105" s="81"/>
-      <c r="X105" s="82"/>
+      <c r="V105" s="82"/>
+      <c r="W105" s="70"/>
+      <c r="X105" s="83"/>
     </row>
     <row r="106" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V106" s="80"/>
-      <c r="W106" s="81"/>
-      <c r="X106" s="82"/>
+      <c r="V106" s="82"/>
+      <c r="W106" s="70"/>
+      <c r="X106" s="83"/>
     </row>
     <row r="107" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V107" s="80"/>
-      <c r="W107" s="81"/>
-      <c r="X107" s="82"/>
+      <c r="V107" s="82"/>
+      <c r="W107" s="70"/>
+      <c r="X107" s="83"/>
     </row>
     <row r="108" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V108" s="80"/>
-      <c r="W108" s="81"/>
-      <c r="X108" s="82"/>
+      <c r="V108" s="82"/>
+      <c r="W108" s="70"/>
+      <c r="X108" s="83"/>
     </row>
     <row r="109" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V109" s="80"/>
-      <c r="W109" s="81"/>
-      <c r="X109" s="82"/>
+      <c r="V109" s="82"/>
+      <c r="W109" s="70"/>
+      <c r="X109" s="83"/>
     </row>
     <row r="110" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V110" s="80"/>
-      <c r="W110" s="81"/>
-      <c r="X110" s="82"/>
+      <c r="V110" s="82"/>
+      <c r="W110" s="70"/>
+      <c r="X110" s="83"/>
     </row>
     <row r="111" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V111" s="80"/>
-      <c r="W111" s="81"/>
-      <c r="X111" s="82"/>
+      <c r="V111" s="82"/>
+      <c r="W111" s="70"/>
+      <c r="X111" s="83"/>
     </row>
     <row r="112" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="V112" s="83"/>
-      <c r="W112" s="84"/>
-      <c r="X112" s="85"/>
+      <c r="V112" s="84"/>
+      <c r="W112" s="85"/>
+      <c r="X112" s="86"/>
     </row>
     <row r="113" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="114" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="S114" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="T114" s="76"/>
-      <c r="V114" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W114" s="78"/>
-      <c r="X114" s="79"/>
+      <c r="S114" s="99" t="s">
+        <v>51</v>
+      </c>
+      <c r="T114" s="78"/>
+      <c r="V114" s="79"/>
+      <c r="W114" s="80"/>
+      <c r="X114" s="81"/>
     </row>
     <row r="115" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S115" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T115" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="V115" s="80"/>
-      <c r="W115" s="81"/>
-      <c r="X115" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="V115" s="82"/>
+      <c r="W115" s="70"/>
+      <c r="X115" s="83"/>
     </row>
     <row r="116" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S116" s="1">
         <v>1</v>
       </c>
-      <c r="T116" s="51">
-        <v>0.71250000000000002</v>
-      </c>
-      <c r="V116" s="80"/>
-      <c r="W116" s="81"/>
-      <c r="X116" s="82"/>
+      <c r="T116" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="V116" s="82"/>
+      <c r="W116" s="70"/>
+      <c r="X116" s="83"/>
     </row>
     <row r="117" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S117" s="15">
         <v>2</v>
       </c>
-      <c r="T117" s="53">
-        <v>0.71319444444444446</v>
-      </c>
-      <c r="V117" s="80"/>
-      <c r="W117" s="81"/>
-      <c r="X117" s="82"/>
+      <c r="T117" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="V117" s="82"/>
+      <c r="W117" s="70"/>
+      <c r="X117" s="83"/>
     </row>
     <row r="118" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S118" s="1">
         <v>3</v>
       </c>
-      <c r="T118" s="51">
-        <v>0.71388888888888891</v>
-      </c>
-      <c r="V118" s="80"/>
-      <c r="W118" s="81"/>
-      <c r="X118" s="82"/>
+      <c r="T118" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="V118" s="82"/>
+      <c r="W118" s="70"/>
+      <c r="X118" s="83"/>
     </row>
     <row r="119" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S119" s="15">
         <v>4</v>
       </c>
-      <c r="T119" s="53">
-        <v>0.71458333333333335</v>
-      </c>
-      <c r="V119" s="80"/>
-      <c r="W119" s="81"/>
-      <c r="X119" s="82"/>
+      <c r="T119" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="V119" s="82"/>
+      <c r="W119" s="70"/>
+      <c r="X119" s="83"/>
     </row>
     <row r="120" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S120" s="1">
         <v>5</v>
       </c>
-      <c r="T120" s="51">
-        <v>0.71527777777777779</v>
-      </c>
-      <c r="V120" s="80"/>
-      <c r="W120" s="81"/>
-      <c r="X120" s="82"/>
+      <c r="T120" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="V120" s="82"/>
+      <c r="W120" s="70"/>
+      <c r="X120" s="83"/>
     </row>
     <row r="121" spans="19:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="V121" s="80"/>
-      <c r="W121" s="81"/>
-      <c r="X121" s="82"/>
+      <c r="V121" s="82"/>
+      <c r="W121" s="70"/>
+      <c r="X121" s="83"/>
     </row>
     <row r="122" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V122" s="80"/>
-      <c r="W122" s="81"/>
-      <c r="X122" s="82"/>
+      <c r="V122" s="82"/>
+      <c r="W122" s="70"/>
+      <c r="X122" s="83"/>
     </row>
     <row r="123" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V123" s="80"/>
-      <c r="W123" s="81"/>
-      <c r="X123" s="82"/>
+      <c r="V123" s="82"/>
+      <c r="W123" s="70"/>
+      <c r="X123" s="83"/>
     </row>
     <row r="124" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V124" s="80"/>
-      <c r="W124" s="81"/>
-      <c r="X124" s="82"/>
+      <c r="V124" s="82"/>
+      <c r="W124" s="70"/>
+      <c r="X124" s="83"/>
     </row>
     <row r="125" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V125" s="80"/>
-      <c r="W125" s="81"/>
-      <c r="X125" s="82"/>
+      <c r="V125" s="82"/>
+      <c r="W125" s="70"/>
+      <c r="X125" s="83"/>
     </row>
     <row r="126" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V126" s="80"/>
-      <c r="W126" s="81"/>
-      <c r="X126" s="82"/>
+      <c r="V126" s="82"/>
+      <c r="W126" s="70"/>
+      <c r="X126" s="83"/>
     </row>
     <row r="127" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V127" s="80"/>
-      <c r="W127" s="81"/>
-      <c r="X127" s="82"/>
+      <c r="V127" s="82"/>
+      <c r="W127" s="70"/>
+      <c r="X127" s="83"/>
     </row>
     <row r="128" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V128" s="80"/>
-      <c r="W128" s="81"/>
-      <c r="X128" s="82"/>
+      <c r="V128" s="82"/>
+      <c r="W128" s="70"/>
+      <c r="X128" s="83"/>
     </row>
     <row r="129" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V129" s="80"/>
-      <c r="W129" s="81"/>
-      <c r="X129" s="82"/>
+      <c r="V129" s="82"/>
+      <c r="W129" s="70"/>
+      <c r="X129" s="83"/>
     </row>
     <row r="130" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V130" s="80"/>
-      <c r="W130" s="81"/>
-      <c r="X130" s="82"/>
+      <c r="V130" s="82"/>
+      <c r="W130" s="70"/>
+      <c r="X130" s="83"/>
     </row>
     <row r="131" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V131" s="80"/>
-      <c r="W131" s="81"/>
-      <c r="X131" s="82"/>
+      <c r="V131" s="82"/>
+      <c r="W131" s="70"/>
+      <c r="X131" s="83"/>
     </row>
     <row r="132" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="V132" s="83"/>
-      <c r="W132" s="84"/>
-      <c r="X132" s="85"/>
+      <c r="V132" s="84"/>
+      <c r="W132" s="85"/>
+      <c r="X132" s="86"/>
     </row>
     <row r="133" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="134" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="S134" s="75" t="s">
-        <v>38</v>
-      </c>
-      <c r="T134" s="76"/>
-      <c r="V134" s="77" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="W134" s="78"/>
-      <c r="X134" s="79"/>
+      <c r="S134" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="T134" s="78"/>
+      <c r="V134" s="79"/>
+      <c r="W134" s="80"/>
+      <c r="X134" s="81"/>
     </row>
     <row r="135" spans="19:24" x14ac:dyDescent="0.35">
       <c r="S135" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T135" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="V135" s="80"/>
-      <c r="W135" s="81"/>
-      <c r="X135" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="V135" s="82"/>
+      <c r="W135" s="70"/>
+      <c r="X135" s="83"/>
     </row>
     <row r="136" spans="19:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S136" s="1">
         <v>1</v>
       </c>
-      <c r="T136" s="51">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="V136" s="80"/>
-      <c r="W136" s="81"/>
-      <c r="X136" s="82"/>
+      <c r="T136" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="V136" s="82"/>
+      <c r="W136" s="70"/>
+      <c r="X136" s="83"/>
     </row>
     <row r="137" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S137" s="15">
         <v>2</v>
       </c>
-      <c r="T137" s="53">
-        <v>0.49375000000000002</v>
-      </c>
-      <c r="V137" s="80"/>
-      <c r="W137" s="81"/>
-      <c r="X137" s="82"/>
+      <c r="T137" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="V137" s="82"/>
+      <c r="W137" s="70"/>
+      <c r="X137" s="83"/>
     </row>
     <row r="138" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S138" s="1">
         <v>3</v>
       </c>
-      <c r="T138" s="51">
-        <v>0.49444444444444452</v>
-      </c>
-      <c r="V138" s="80"/>
-      <c r="W138" s="81"/>
-      <c r="X138" s="82"/>
+      <c r="T138" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="V138" s="82"/>
+      <c r="W138" s="70"/>
+      <c r="X138" s="83"/>
     </row>
     <row r="139" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S139" s="15">
         <v>4</v>
       </c>
-      <c r="T139" s="53">
-        <v>0.49513888888888891</v>
-      </c>
-      <c r="V139" s="80"/>
-      <c r="W139" s="81"/>
-      <c r="X139" s="82"/>
+      <c r="T139" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="V139" s="82"/>
+      <c r="W139" s="70"/>
+      <c r="X139" s="83"/>
     </row>
     <row r="140" spans="19:24" ht="15.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="S140" s="1">
         <v>5</v>
       </c>
-      <c r="T140" s="51">
-        <v>0.49583333333333329</v>
-      </c>
-      <c r="V140" s="80"/>
-      <c r="W140" s="81"/>
-      <c r="X140" s="82"/>
+      <c r="T140" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="V140" s="82"/>
+      <c r="W140" s="70"/>
+      <c r="X140" s="83"/>
     </row>
     <row r="141" spans="19:24" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="V141" s="80"/>
-      <c r="W141" s="81"/>
-      <c r="X141" s="82"/>
+      <c r="V141" s="82"/>
+      <c r="W141" s="70"/>
+      <c r="X141" s="83"/>
     </row>
     <row r="142" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V142" s="80"/>
-      <c r="W142" s="81"/>
-      <c r="X142" s="82"/>
+      <c r="V142" s="82"/>
+      <c r="W142" s="70"/>
+      <c r="X142" s="83"/>
     </row>
     <row r="143" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V143" s="80"/>
-      <c r="W143" s="81"/>
-      <c r="X143" s="82"/>
+      <c r="V143" s="82"/>
+      <c r="W143" s="70"/>
+      <c r="X143" s="83"/>
     </row>
     <row r="144" spans="19:24" x14ac:dyDescent="0.35">
-      <c r="V144" s="80"/>
-      <c r="W144" s="81"/>
-      <c r="X144" s="82"/>
+      <c r="V144" s="82"/>
+      <c r="W144" s="70"/>
+      <c r="X144" s="83"/>
     </row>
     <row r="145" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V145" s="80"/>
-      <c r="W145" s="81"/>
-      <c r="X145" s="82"/>
+      <c r="V145" s="82"/>
+      <c r="W145" s="70"/>
+      <c r="X145" s="83"/>
     </row>
     <row r="146" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V146" s="80"/>
-      <c r="W146" s="81"/>
-      <c r="X146" s="82"/>
+      <c r="V146" s="82"/>
+      <c r="W146" s="70"/>
+      <c r="X146" s="83"/>
     </row>
     <row r="147" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V147" s="80"/>
-      <c r="W147" s="81"/>
-      <c r="X147" s="82"/>
+      <c r="V147" s="82"/>
+      <c r="W147" s="70"/>
+      <c r="X147" s="83"/>
     </row>
     <row r="148" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V148" s="80"/>
-      <c r="W148" s="81"/>
-      <c r="X148" s="82"/>
+      <c r="V148" s="82"/>
+      <c r="W148" s="70"/>
+      <c r="X148" s="83"/>
     </row>
     <row r="149" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V149" s="80"/>
-      <c r="W149" s="81"/>
-      <c r="X149" s="82"/>
+      <c r="V149" s="82"/>
+      <c r="W149" s="70"/>
+      <c r="X149" s="83"/>
     </row>
     <row r="150" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V150" s="80"/>
-      <c r="W150" s="81"/>
-      <c r="X150" s="82"/>
+      <c r="V150" s="82"/>
+      <c r="W150" s="70"/>
+      <c r="X150" s="83"/>
     </row>
     <row r="151" spans="22:24" x14ac:dyDescent="0.35">
-      <c r="V151" s="80"/>
-      <c r="W151" s="81"/>
-      <c r="X151" s="82"/>
+      <c r="V151" s="82"/>
+      <c r="W151" s="70"/>
+      <c r="X151" s="83"/>
     </row>
     <row r="152" spans="22:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="V152" s="83"/>
-      <c r="W152" s="84"/>
-      <c r="X152" s="85"/>
+      <c r="V152" s="84"/>
+      <c r="W152" s="85"/>
+      <c r="X152" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -7143,348 +7179,348 @@
       <c r="B9" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
     </row>
     <row r="13" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="107" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="104"/>
-      <c r="F14" s="107" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="104"/>
+      <c r="B14" s="109" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="106"/>
+      <c r="F14" s="109" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="106"/>
     </row>
     <row r="15" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="105" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="104"/>
-      <c r="F15" s="105" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="104"/>
+      <c r="B15" s="107" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="106"/>
+      <c r="F15" s="107" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="106"/>
     </row>
     <row r="16" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="104"/>
-      <c r="F16" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="104"/>
+      <c r="B16" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="106"/>
+      <c r="F16" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="106"/>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="108" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="104"/>
-      <c r="F17" s="108" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="104"/>
+      <c r="B17" s="110" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="106"/>
+      <c r="F17" s="110" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="106"/>
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="19" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="106" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="104"/>
+        <v>34</v>
+      </c>
+      <c r="C19" s="108" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="106"/>
       <c r="F19" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="106" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="104"/>
+        <v>34</v>
+      </c>
+      <c r="G19" s="108" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" s="106"/>
     </row>
     <row r="20" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="100">
+      <c r="B20" s="102">
         <v>1</v>
       </c>
-      <c r="C20" s="77" t="e">
+      <c r="C20" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="F20" s="100">
+      <c r="D20" s="81"/>
+      <c r="F20" s="102">
         <v>1</v>
       </c>
-      <c r="G20" s="77" t="e">
+      <c r="G20" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H20" s="79"/>
+      <c r="H20" s="81"/>
     </row>
     <row r="21" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="101"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="82"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="82"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="83"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="83"/>
     </row>
     <row r="22" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="101"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="82"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="82"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="83"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="83"/>
     </row>
     <row r="23" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="101"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="82"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="82"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="83"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="83"/>
     </row>
     <row r="24" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="101"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="82"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="82"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="83"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="83"/>
     </row>
     <row r="25" spans="2:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="102"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="85"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="85"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="86"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="86"/>
     </row>
     <row r="26" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="100">
+      <c r="B26" s="102">
         <v>2</v>
       </c>
-      <c r="C26" s="77" t="e">
+      <c r="C26" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D26" s="79"/>
-      <c r="F26" s="100">
+      <c r="D26" s="81"/>
+      <c r="F26" s="102">
         <v>2</v>
       </c>
-      <c r="G26" s="77" t="e">
+      <c r="G26" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H26" s="79"/>
+      <c r="H26" s="81"/>
     </row>
     <row r="27" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="101"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="82"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="82"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="83"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="83"/>
     </row>
     <row r="28" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="101"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="82"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="82"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="83"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="83"/>
     </row>
     <row r="29" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="101"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="82"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="82"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="83"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="83"/>
     </row>
     <row r="30" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="101"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="82"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="82"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="83"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="83"/>
     </row>
     <row r="31" spans="2:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="102"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="85"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="85"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="86"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="86"/>
     </row>
     <row r="32" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="100">
+      <c r="B32" s="102">
         <v>3</v>
       </c>
-      <c r="C32" s="77" t="e">
+      <c r="C32" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="79"/>
-      <c r="F32" s="100">
+      <c r="D32" s="81"/>
+      <c r="F32" s="102">
         <v>3</v>
       </c>
-      <c r="G32" s="77" t="e">
+      <c r="G32" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H32" s="79"/>
+      <c r="H32" s="81"/>
     </row>
     <row r="33" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="101"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="82"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="82"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="82"/>
+      <c r="D33" s="83"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="83"/>
     </row>
     <row r="34" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="101"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="82"/>
-      <c r="F34" s="101"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="82"/>
+      <c r="B34" s="103"/>
+      <c r="C34" s="82"/>
+      <c r="D34" s="83"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="83"/>
     </row>
     <row r="35" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="101"/>
-      <c r="C35" s="80"/>
-      <c r="D35" s="82"/>
-      <c r="F35" s="101"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="82"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="82"/>
+      <c r="D35" s="83"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="83"/>
     </row>
     <row r="36" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="101"/>
-      <c r="C36" s="80"/>
-      <c r="D36" s="82"/>
-      <c r="F36" s="101"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="82"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="83"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="83"/>
     </row>
     <row r="37" spans="2:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="102"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="85"/>
-      <c r="F37" s="102"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="85"/>
+      <c r="B37" s="104"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="86"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="86"/>
     </row>
     <row r="38" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="100">
+      <c r="B38" s="102">
         <v>4</v>
       </c>
-      <c r="C38" s="77" t="e">
+      <c r="C38" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D38" s="79"/>
-      <c r="F38" s="100">
+      <c r="D38" s="81"/>
+      <c r="F38" s="102">
         <v>4</v>
       </c>
-      <c r="G38" s="77" t="e">
+      <c r="G38" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H38" s="79"/>
+      <c r="H38" s="81"/>
     </row>
     <row r="39" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="101"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="82"/>
-      <c r="F39" s="101"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="82"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="83"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="83"/>
     </row>
     <row r="40" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="101"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="82"/>
-      <c r="F40" s="101"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="82"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="83"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="83"/>
     </row>
     <row r="41" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="101"/>
-      <c r="C41" s="80"/>
-      <c r="D41" s="82"/>
-      <c r="F41" s="101"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="82"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="83"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="83"/>
     </row>
     <row r="42" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="101"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="82"/>
-      <c r="F42" s="101"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="82"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="82"/>
+      <c r="D42" s="83"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="83"/>
     </row>
     <row r="43" spans="2:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="102"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="85"/>
-      <c r="F43" s="102"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="85"/>
+      <c r="B43" s="104"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="86"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="86"/>
     </row>
     <row r="44" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="100">
+      <c r="B44" s="102">
         <v>5</v>
       </c>
-      <c r="C44" s="77" t="e">
+      <c r="C44" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D44" s="79"/>
-      <c r="F44" s="100">
+      <c r="D44" s="81"/>
+      <c r="F44" s="102">
         <v>5</v>
       </c>
-      <c r="G44" s="77" t="e">
+      <c r="G44" s="79" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="H44" s="79"/>
+      <c r="H44" s="81"/>
     </row>
     <row r="45" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="101"/>
-      <c r="C45" s="80"/>
-      <c r="D45" s="82"/>
-      <c r="F45" s="101"/>
-      <c r="G45" s="80"/>
-      <c r="H45" s="82"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="82"/>
+      <c r="D45" s="83"/>
+      <c r="F45" s="103"/>
+      <c r="G45" s="82"/>
+      <c r="H45" s="83"/>
     </row>
     <row r="46" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="101"/>
-      <c r="C46" s="80"/>
-      <c r="D46" s="82"/>
-      <c r="F46" s="101"/>
-      <c r="G46" s="80"/>
-      <c r="H46" s="82"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="82"/>
+      <c r="D46" s="83"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="82"/>
+      <c r="H46" s="83"/>
     </row>
     <row r="47" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="101"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="82"/>
-      <c r="F47" s="101"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="82"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="82"/>
+      <c r="D47" s="83"/>
+      <c r="F47" s="103"/>
+      <c r="G47" s="82"/>
+      <c r="H47" s="83"/>
     </row>
     <row r="48" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="101"/>
-      <c r="C48" s="80"/>
-      <c r="D48" s="82"/>
-      <c r="F48" s="101"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="82"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="82"/>
+      <c r="D48" s="83"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="82"/>
+      <c r="H48" s="83"/>
     </row>
     <row r="49" spans="2:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="102"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="85"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="85"/>
+      <c r="B49" s="104"/>
+      <c r="C49" s="84"/>
+      <c r="D49" s="86"/>
+      <c r="F49" s="104"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -7546,35 +7582,35 @@
     <row r="1" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="25" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="M2" s="31"/>
       <c r="N2" s="31"/>
     </row>
     <row r="3" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="120" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D3" s="28">
         <v>46090</v>
@@ -7593,33 +7629,33 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="101"/>
+      <c r="B4" s="103"/>
       <c r="C4" s="26" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="M4" s="36"/>
       <c r="N4" s="36"/>
       <c r="O4" s="36"/>
     </row>
     <row r="5" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="101"/>
+      <c r="B5" s="103"/>
       <c r="C5" s="27" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D5" s="28">
         <v>46090</v>
@@ -7638,33 +7674,33 @@
       </c>
     </row>
     <row r="6" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="101"/>
+      <c r="B6" s="103"/>
       <c r="C6" s="26" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="M6" s="36"/>
       <c r="N6" s="36"/>
       <c r="O6" s="36"/>
     </row>
     <row r="7" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="101"/>
+      <c r="B7" s="103"/>
       <c r="C7" s="27" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D7" s="28">
         <v>46090</v>
@@ -7688,10 +7724,10 @@
     <row r="9" spans="2:15" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:15" ht="29.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="29" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C10" s="111" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="D10" s="112"/>
       <c r="E10" s="112"/>
@@ -7704,55 +7740,55 @@
       <c r="C11" s="114" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
       <c r="F11" s="115"/>
       <c r="O11" s="36"/>
     </row>
     <row r="12" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="101"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
       <c r="F12" s="116"/>
       <c r="O12" s="36"/>
     </row>
     <row r="13" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="101"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
       <c r="F13" s="116"/>
       <c r="N13" s="36"/>
       <c r="O13" s="37"/>
     </row>
     <row r="14" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="101"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
       <c r="F14" s="116"/>
       <c r="N14" s="36"/>
       <c r="O14" s="36"/>
     </row>
     <row r="15" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="101"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
       <c r="F15" s="116"/>
       <c r="N15" s="36"/>
       <c r="O15" s="36"/>
     </row>
     <row r="16" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="101"/>
-      <c r="C16" s="80"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
       <c r="F16" s="116"/>
     </row>
     <row r="17" spans="2:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="102"/>
+      <c r="B17" s="104"/>
       <c r="C17" s="117"/>
       <c r="D17" s="118"/>
       <c r="E17" s="118"/>
